--- a/outputs/并购案例一览_20260513_20260520.xlsx
+++ b/outputs/并购案例一览_20260513_20260520.xlsx
@@ -13,7 +13,7 @@
     <sheet name="原始候选" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'周度并购案例'!$A$1:$P$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'周度并购案例'!$A$1:$P$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'原始候选'!$A$1:$G$161</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -568,7 +568,7 @@
     <row r="2" ht="44" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>上市公司控股权并购</t>
+          <t>整合一级资产+资本化</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
@@ -576,32 +576,32 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Ares Management</t>
+          <t>绿通科技</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Whitestone REIT</t>
+          <t>诚瑞科技</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>房地产</t>
+          <t>专用设备制造</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>另类资产管理</t>
+          <t>电动高尔夫球车等场地电动车的研发、生产和销售</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>房地产投资信托</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>Ares以17亿美元收购Whitestone REIT，扩大不动产管理规模</t>
+          <t>绿通科技跨界收购诚瑞科技，拓展业务版图</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>17亿美元</t>
+          <t>1.2亿元</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
@@ -621,17 +621,17 @@
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>跨界并购</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>kavout</t>
+          <t>东方财富</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPMDR4QmR6eFFfeWZOaVhxN1NBcEp3dnB5OUxQaTd6TW9yTVZTaGdPUWRMTTNSUDhpcUpubEhHUnZQcEtUdFlmZFRyV1Q3VW12dHZ1bjVqMXVMN2UxVGdUM01kdmgwTWxjOXQtSC1fZlc1OHZkYXEyYVlJUnVnaVRSdEJwb3pmWl9zRGpsOU1wbUlDcURUNXRsMjg2ZGE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTFBwWG85NDZ4ZEFmZUxndEktQ2hHUlJka0RTbTJZSTF5emtzN3VveWVBTFg0SVNENEJfRF9DajdMeE5lQzJXT0IwU3NPdXdVb05OVzVPbzBDSThzVDFFX182Sg?oc=5</t>
         </is>
       </c>
       <c r="O2" s="3" t="inlineStr">
@@ -641,14 +641,14 @@
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>中国</t>
         </is>
       </c>
     </row>
     <row r="3" ht="44" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>依托上市平台持续整合同类资产</t>
+          <t>上市公司控股权并购</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -656,42 +656,42 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>NextEra Energy</t>
+          <t>Ares Management</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Dominion Energy</t>
+          <t>Whitestone REIT</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>电力公用事业</t>
+          <t>房地产投资信托（REIT）</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>清洁能源发电</t>
+          <t>另类资产管理</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>电力和天然气公用事业</t>
+          <t>商业地产REIT</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>NextEra与Dominion达成670亿美元历史性合并交易，强化清洁能源布局。</t>
+          <t>Ares以17亿美元收购Whitestone REIT，扩大房地产投资组合</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>670亿美元</t>
+          <t>17亿美元</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -706,17 +706,17 @@
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>Google News</t>
+          <t>Kavout</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPTnJaMVpFTHlZNG1aaHhWalNTV1h1MUlrNy1tY0NoOW11TDFkQVNPVGozaDFSS2NqNFprWkh0WTFPeHdpYkFlaGVRVmR6WnRXY3N4NFJUbW1wbjZJVnVpV09KSmJybUlYejFHRzFxMi1EOUpxQk84NklvcFZjZEVlUEt0M2tFSlFRV1ZhdDRQUGU2NGxY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPMDR4QmR6eFFfeWZOaVhxN1NBcEp3dnB5OUxQaTd6TW9yTVZTaGdPUWRMTTNSUDhpcUpubEhHUnZQcEtUdFlmZFRyV1Q3VW12dHZ1bjVqMXVMN2UxVGdUM01kdmgwTWxjOXQtSC1fZlc1OHZkYXEyYVlJUnVnaVRSdEJwb3pmWl9zRGpsOU1wbUlDcURUNXRsMjg2ZGE?oc=5</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
@@ -728,7 +728,7 @@
     <row r="4" ht="44" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>依托上市平台持续整合同类资产</t>
+          <t>整合一级资产+资本化</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -736,32 +736,32 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>InMed Pharmaceuticals</t>
+          <t>北京利尔</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Mentari Therapeutics</t>
+          <t>联创锂能</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>制药</t>
+          <t>新能源材料</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>偏头痛治疗药物研发</t>
+          <t>耐火材料</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>偏头痛预防疗法开发</t>
+          <t>锂离子电池材料</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>InMed与Mentari全股票合并，推进偏头痛预防疗法。</t>
+          <t>北京利尔拟9.9亿元收购联创锂能65%股权，布局新能源材料领域。</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -771,27 +771,27 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>9.9亿元</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>意向</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>PR Newswire</t>
+          <t>mrjjxw.com</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxNRW16RTEzdXZxU2FSVGRzMC1vSlJMOFFqU3gwcEVTSEt6RWVycElmZElkajVQWlhUa3Fpelp1cGZ0X3dtaDM4Z01LM3JwRHFXak5lVUhRQV9xYTRsMUVoc284eXRuZnhNVzhrN2pRWHpfR1NIRDlWNG9pRjQydkFQNkctbjROaS0tb1IxTXVubVVtMHVmaGVrdFZRTDlCNjgxRUNKU2dNX2NlTjNvZkp0NmZMM1dvOGstTUFuOTFVX3FiSGlHUFFOTTAwcWNXWDJGbDBtVU5VMHoyNV9SYXpSUWVzT055WnpRS2JjSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTFAxMWtfNEVKanRJT0E0em12UDdkWjkzbTZ6Znc3b0dxbVIzSzBScm9VTUxqUWRZbFNGRTFhLVc4dDg3RHMyX2F0d1Z2Ri11UFYzbTZLNHZJeUhJRVdndFFwODZYdFRHQQ?oc=5</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -801,14 +801,14 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>全球</t>
+          <t>中国</t>
         </is>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>上市公司控股权并购</t>
+          <t>整合一级资产+资本化</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -816,32 +816,32 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>NextEra Energy</t>
+          <t>奕帆传动</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Dominion Energy</t>
+          <t>北京和利时</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>工业自动化</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>清洁能源发电与能源基础设施</t>
+          <t>传动设备</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>电力与天然气输送及配送</t>
+          <t>工业自动化系统</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>NextEra全股票670亿美元收购Dominion，打造全球最大公用事业公司</t>
+          <t>奕帆传动终止原重组改为8400万元收购北京和利时40%股权，调整收购方案。</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>670亿美元</t>
+          <t>8400万元</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -861,27 +861,27 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>原重组终止</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>axios</t>
+          <t>新浪财经</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFAxblNXdTJxRDRxSXZYM21FdUdfVVhHOHdNUkVDWlZDd3NMOFRqNEZZMVpZVm9WWUwtTWpab3AwX1RoMkxfamxhdFp5SW50anFKWWJad1FEVG5VVEg4OG5EX1hZcVNHMHY2cHBtR1ZMcEU0T2RSZ3hFNW1jT1YtdFk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE9kWmZWM09nbThRTEtBT2x5ODhTcGRyMlQ3bHFpcTJ2ZlBxMkM0YVk1RS1xVElraHFaemZFMldCSWNWN3QzRDY1Um13M2NlNHVWY0lpWUtXVlNCQURNOWs3NDk4Tm45a0FGNFlDVUdSRjAzd2ZwVS1Beg</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19T12:36:11+08:00</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>美国</t>
+          <t>中国</t>
         </is>
       </c>
     </row>
@@ -896,32 +896,32 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Neurocrine Biosciences</t>
+          <t>NextEra Energy</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Soleno Therapeutics</t>
+          <t>Dominion Energy</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>生物医药</t>
+          <t>能源</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>神经科学领域药物开发</t>
+          <t>可再生能源</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>罕见病治疗药物研发</t>
+          <t>发电与输电</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>Neurocrine以29亿美元收购Soleno，扩充罕见病产品线</t>
+          <t>NextEra Energy与Dominion Energy宣布670亿美元历史性合并。</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>29亿美元</t>
+          <t>670亿美元</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>意向</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -946,17 +946,17 @@
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>pulse 2.0</t>
+          <t>evrim ağacı</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNNl9HQkJxcDZCN3lTLWVnZVpaWUFmM2MyUWtJaFZyNFpNa1RZcVlRWnBNM0w5VWpUM0pzMHFDT2pvNHM0Z0VkWkJuV3ZhMHZrZlY0bmtyTXdUYkszVjFINzZ6RXAwOE1CYjZ2czFLOVVJLWVac3FyQ1pIR0hvWldNUExEYVJ5NHFjSmg0VXh2RjRwTHluVFRUNllWQUVIalJKYWhmRmwxV0dRRFFUQjBoTVVYSy1xc2pG0gG-AUFVX3lxTE55V3VTck9tMUZFVUctSEVKVWlJUUtOUF9ycHdiVU1icDdDVzNGOWlGT3JzbzNPdU5yTGlRWDVwZGkzRktiUDFDcm0xcUo2YUNFNkF5ejRlejdkT3QwVVVTWHBVdVlJM1dJUGRtRUl3dzVaenduMDM0dVpSWTY3Q1RyOXNmRG8zdWxBTzNUU1I5R05vS2pCaHRjWUYwcEExOFZNalJaREUzVHpPckY4aS1JeWZjenJlYUJyRFduMVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPTnJaMVpFTHlZNG1aaHhWalNTV1h1MUlrNy1tY0NoOW11TDFkQVNPVGozaDFSS2NqNFprWkh0WTFPeHdpYkFlaGVRVmR6WnRXY3N4NFJUbW1wbjZJVnVpV09KSmJybUlYejFHRzFxMi1EOUpxQk84NklvcFZjZEVlUEt0M2tFSlFRV1ZhdDRQUGU2NGxY?oc=5</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19T01:14:29+08:00</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
@@ -968,7 +968,7 @@
     <row r="7" ht="44" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>依托上市平台持续整合同类资产</t>
+          <t>上市公司控股权并购</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
@@ -976,32 +976,32 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>RB Global</t>
+          <t>InMed Pharmaceuticals</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>BigIron</t>
+          <t>Mentari</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>农业科技</t>
+          <t>生物医药</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>全球工业设备拍卖及市场平台</t>
+          <t>大麻素药物研发</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>美国农业设备在线拍卖</t>
+          <t>制药</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>RB Global完成收购BigIron，拓展美国农业设备交易业务</t>
+          <t>InMed与Mentari宣布全股票合并交易。</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>已完成</t>
+          <t>意向</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
@@ -1026,17 +1026,17 @@
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>stock titan</t>
+          <t>seeking alpha</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOLXBvYkZJM1pRYUpJNm1JT1UxVlJtcnZObUtVbTN5NHpkZzVWZE9GMEF2ZFQ2WG51bTVVd1ZVZFNMaEJpZW1HM1JFMFJOSy00QUtHamdXdTBxNll6WTNoM3ladEdBcFF4VUpTcWxwNFBObXRnblgzX2lCN0NWWVdDSEVzY0Z3LW9BbGV5VDhXNHBUeXhNZ0x0UTg2d3U0Ym9SRWdv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQWkhBT2x0QktTaFptZVlDejltT1RWZ3lXaDRyemlnSG1jRHhqLS1PZjBtM1ZlbFdPSWdyc2JyUzc5LW1Gb2habmgzVWZoWGVSWFRIbXRrcEh6RWpJVDI4ZXNtNHZuTWhoRDhVcFNlUTBYSzQtNmQxTURnSWV6UWVUN3JpVTlESk8wOGRJYk9KVQ?oc=5</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19T04:30:28+08:00</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
@@ -1048,7 +1048,7 @@
     <row r="8" ht="44" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>SPAC</t>
+          <t>依托上市平台持续整合同类资产</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Iron Horse (IRHO)</t>
+          <t>腾讯音乐</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Electra AI</t>
+          <t>喜马拉雅</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>人工智能</t>
+          <t>互联网音频</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>SPAC（特殊目的收购公司）</t>
+          <t>在线音乐和音频娱乐平台</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>AI 技术研发与应用</t>
+          <t>音频内容分享平台</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>Iron Horse与Electra AI推进2.5亿美元De-SPAC合并</t>
+          <t>腾讯音乐完成收购喜马拉雅，整合音频内容生态，强化行业领先地位。</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -1091,44 +1091,44 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>2.5亿美元</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>通过股份和现金收购</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>stock titan</t>
+          <t>中国新闻广域 - Google News RSS / 新浪财经</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQUkFXWjVUUHhKeGdJbG1aaThKeWpNb0NnZE5CNjhvYnpET241TFpFUE05Qmp5Z3RHbnBiZmhPSEY0RFE3ZXZ1bmF6WUlUOEZ0V0xKZEFWV0UzWEpjXzZPdXNuM0UxT2d0Vjd0aFR2WjlNdDZWNE81VkZBbGtvNGctRzYzaVhpaVRUeFZsY3ZHdGVxZXQ4NjZXaHZTOHJsVFFpcGJ1bVgtNnBTV0NqTF9PWnVPOXY3dll4cUVj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE1HVFVCNDBFUHlITURsczAzd2ZxdXNfbWNhX1JDaS01VnE1Sy1oYVpxQWwzWVIxTnlLS1Uwb2FoSUtmVktDdHhVNG5hSlhEbE00ZUhwci0wSnd1RGt6SEhub2p6LWZQSVB1Xzdic0FzRQ?oc=5</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19T04:31:32+08:00</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>全球</t>
+          <t>中国</t>
         </is>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>上市公司控股权并购</t>
+          <t>跨境并购</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
@@ -1136,32 +1136,32 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Equinox Gold</t>
+          <t>Evoke</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Orla Mining</t>
+          <t>Bally's Intralot</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>矿业（黄金）</t>
+          <t>博彩</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>黄金开采与生产</t>
+          <t>博彩和游戏运营</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>黄金矿业开发</t>
+          <t>博彩技术和服务提供商</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Equinox Gold与Orla Mining合并，创建185亿美元黄金生产商</t>
+          <t>Evoke延长对Bally's Intralot的收购要约截止日，推进跨境整合。</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>185亿美元</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
@@ -1181,22 +1181,22 @@
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>要约收购延期</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>discovery alert</t>
+          <t>Google News - Global M&amp;A / igamingbusiness.com</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPVkFxX2hpQkNNMmlJWEI3MElJWUtJTERVZTZjdk5NVVExcnIwcGRnU3NJUG90Qll4ajlWbjlFLXMtM2xoenUxTEtLYUhBbTBySHpQTXdMMUFwbGZWUnZSS0dBRm5aRkpNTThpTGk4NXpHa0pWZDE0alBvSmhLM0MybXhwUlI0bmI5VEtSejBMTGhFazBM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOZFhIbWhGdTRkSHV6cTRuLUs0c2hjV20zZ0VGNGFvbWxhODNWSm9CZTV5dEpIVi1hRU5LZUFjUUVxeWpIeDRlTW9CRkVFa2I0TW5pYXBybVNsM2tET2N0LTdaTGlJdG1va3FLa2NxTW5ldlNfTUVXYUhvT0ttVE1HTC1BbXp0RzB5N0RlSlloVmdhb1ZjamRESF9NdE1Udw?oc=5</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19T14:59:34+08:00</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
@@ -1216,77 +1216,1197 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>Equinox Gold</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Orla Mining</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>矿业</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>黄金开采</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>黄金开采</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Equinox Gold与Orla Mining合并创建185亿美元黄金生产商</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>合并后估值185亿美元</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Google News - Global M&amp;A / discovery alert</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPVkFxX2hpQkNNMmlJWEI3MElJWUtJTERVZTZjdk5NVVExcnIwcGRnU3NJUG90Qll4ajlWbjlFLXMtM2xoenUxTEtLYUhBbTBySHpQTXdMMUFwbGZWUnZSS0dBRm5aRkpNTThpTGk4NXpHa0pWZDE0alBvSmhLM0MybXhwUlI0bmI5VEtSejBMTGhFazBM?oc=5</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-19T14:59:34+08:00</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>全球</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="44" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>整合一级资产+资本化</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>延江股份</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>半导体材料商（未披露）</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>纸尿裤材料/半导体材料</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>纸尿裤材料等无纺布</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>半导体材料</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>延江股份跨界收购半导体材料商终止，股价跌停</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>终止</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>目标公司名称未公开</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNaDlLMEF1clFQcC1scENieHFzTFkzdVRjUzBNc25la2lsNGwzeGNMNzliX2VuZzNHZTdoYUJXbEJLSDNqeVhjZ0pjQ0plaDUwTmpaRlZqSDhiOWd1cWxhdUZQRXdyeWVMUnJMV29ObjFTbjVzT2tDbVQ4dUVtNVNXVDlKbVhjeWpwLTVfQXFJSWQ2N1ZXMHZydQ?oc=5</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-19T11:56:14+08:00</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="44" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>上市公司控股权并购</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>雪峰科技</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>民爆</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>民爆产品</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>雪峰科技发布详式权益变动报告书，涉及控制权变更</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>收购方未明确</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>中财网</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE5wTmUwSkEwZTIxU1lSY0l2VXdEOW04dUFlTGJsOExWNngydVNTY1JyZGJQMUd3b3Y3c0hjZjNaOHFDdUNSaFFwZVRKYWV3LThGc2VtZHdn?oc=5</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-19T12:20:41+08:00</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="44" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>跨境并购</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>裕信银行（UniCredit）</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>德国商业银行（Commerzbank）</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>银行业</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>裕信银行要约收购德国商业银行，后者建议股东拒绝</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>收购邀约被建议拒绝</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingJBVV95cUxQQzVvWFlDa3FROWpDajdSUE9sTjcxdW1Za1M2Y1N3UkoxdTJlVUliQkQtQ1NQa21IaVBtZWxkcnZQd1ZmWnQxZS1xZDhnZWtxcWhGT1RydkZvdEtqME8yNWdqRE1UZkxvbmQ2UXVXZ1RZSnBaR2xzQlZ0M084N3g1bkltRzdUejJpaVNzaURTR3B6ZnBkWl81R3k5dDJjb3ZYbm1rZm5DTzJZRy1tWG40U3hzVzhLZWdjY1N3WXhmb3JqMFFRN04tRm5MN3NNS2NDRmNMc1hZMFRKdnBtclA4dG11UWd0Y24yak1qeXYtV3BzTDdYNUxmd1Ywazd6VTdncm9iY0JfWUZIM0ZndWtMQmlvRVJhbklnS2VnX1Jn?oc=5</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-19T10:30:59+08:00</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>跨境</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="44" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>依托上市平台持续整合同类资产</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>中芯国际</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>中芯北方</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>半导体</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>集成电路制造</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>集成电路制造</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>中芯国际406亿元全资收购中芯北方，创科创板最大资产收购案</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>406亿元</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>虎嗅</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOell5eVZkZkVOV1VTcnFOV2ZYRDZndGVSR0RFVnZxa3pyVjlRdW9iOVJ1dzZNWWdXQjltUWc3aTV3dmVScVZsQzZDN0ZuNjVxWWZrbVhKaUI5b1lJVlc5ZlE0ZVVtcmJOM3c4SXNKeTl0em5ldzEwaXh3X25SYXBBOVdXbWFleUFUTHA0?oc=5</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-19T09:17:22+08:00</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="44" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>整合一级资产+资本化</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>腾讯控股</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>喜马拉雅</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>互联网/音频</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>社交、游戏、金融科技</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>在线音频平台</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>腾讯以186亿元完成收购喜马拉雅，布局音频领域</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>186亿元</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>jiemian.com</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE45T21Rd3RLTVRic2c1dlJITVIyU0FwRVdCaDVZUzdhVTQ0ZWhnQlhuWUlnSzkwQ1pVTktWZGlEVWFwZGJCcUNkZWduVlF0ZlpvOUR1cjE5ejI?oc=5</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-19T08:05:33+08:00</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="44" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>上市公司控股权并购</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>NextEra Energy</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Dominion Energy</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>电力</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>可再生能源</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>电力公用事业</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>NextEra以668亿美元并购Dominion，创建美国电力巨无霸</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>668亿美元</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>新浪财经</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE5ONzl2cmlZWUtFTHVrRHpOaXNycXNxOVBlMURZVDU3SjNOVGZsWDB6RWxMWXA2dkFBX21DS1QzYmxIX2JHNVdaQ2d6MnAwWW1mMVFhbFkwSzhLSVdOSXhLOW93c2Ixd3N6N1RhblhR?oc=5</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-19T07:54:03+08:00</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>全球</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="44" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>跨境并购</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>特斯拉（Tesla）</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>比亚迪（BYD）</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>汽车</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>电动汽车</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>电动汽车、电池</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>特斯拉拟收购比亚迪20%股份，推进战略合作</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>意向</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>传闻，尚未确认</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>朝鮮日報中文版</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQVG1BNmNkempjX3phTjVtcEU5TnRTaHVpdHJMNTJodkJBdVFDcFQzbUpFUk9jTVJnbmdLSnVlNFprREtRLTdodmpXUkFUa0xqekxOUWFyY0ptbDg5T1BwaF9NVjdBU1BsNjlJZG11azhmM0NNNW8tVlg0QVFJVU9jME1QWXhVQjlobkxZMW0tWkRhdw?oc=5</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-19T05:07:03+08:00</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>跨境</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="44" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>SPAC</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Iron Horse (IRHO)</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Electra AI</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>人工智能</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>特殊目的收购公司</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>AI数据分析</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Iron Horse与Electra AI推进2.5亿美元SPAC合并</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>2.5亿美元</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>stock titan</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPMXJZNmd2UU5Vdl9QTmM0elI5VEt4RUp6aXZBRWJ3QlBZeDB3bDE4MF94UDNGUTlWMy1yQllTV2l4U2s3VlZ0OEhWTnNFV1pFaFJIMUhCcVZVcGxqZFQwcW5pOXFOVzk5dTlCaklOR1I5REZFeEZWa1dRUjlwT0ZYdEVHYS1tNXNXVGdkS09xdnVOLUxYVDdSM2RjY2V4UmtfNldyc19fQTdDbGJlaTlwYURlY1NYUHQyeVU0MTNZYmlSZzhpYk9CQ1pvSQ?oc=5</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-19T04:32:44+08:00</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>全球</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="44" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>依托上市平台持续整合同类资产</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>RB Global (NYSE: RBA)</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>BigIron</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>农业设备/拍卖</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>农业和重型设备拍卖及市场平台</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>农业设备拍卖</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>RB Global完成收购BigIron，扩大美国农业设备拍卖业务</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>Google News - Global M&amp;A / stock titan</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOLXBvYkZJM1pRYUpJNm1JT1UxVlJtcnZObUtVbTN5NHpkZzVWZE9GMEF2ZFQ2WG51bTVVd1ZVZFNMaEJpZW1HM1JFMFJOSy00QUtHamdXdTBxNll6WTNoM3ladEdBcFF4VUpTcWxwNFBObXRnblgzX2lCN0NWWVdDSEVzY0Z3LW9BbGV5VDhXNHBUeXhNZ0x0UTg2d3U0Ym9SRWdv?oc=5</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-19T04:30:28+08:00</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>全球</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="44" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>上市公司控股权并购</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>NextEra Energy</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Dominion Energy</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>公用事业/能源</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>可再生能源和电力公用事业</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>电力公用事业</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>NextEra以670亿美元全股票收购Dominion，打造全球最大公用事业公司</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>670亿美元（全股票）</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>Fortune</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQTlBuZGtXdXpRbzE5Vm53LWI2X0JXMkphVnVCTklWejVZdDg4eGtmaEI0eXM5RWJIa3RhZ2JVLVFxZXdpVGJYN2hfRW5PUWJOcUdrd05LQkNZVUoxa2xiS0d5M1p2VndaSVJvSmZyWjY5aG5VcDY0dnFnWVpCbXhWT3hVSzJLcFozQTQ0ajFRcUxPbU9VejdTb0dvNEpRRWlfRW5fNVRB?oc=5</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-19T04:29:00+08:00</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>全球</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="44" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>SPAC</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Starry Sea Acquisition</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Forever Young International</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>SPAC/医疗美容</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>特殊目的收购公司（SPAC）</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>抗衰老/医疗美容</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Starry Sea Acquisition终止与Forever Young International的合并计划</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>终止</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>ends proposed merger</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>Investing.com</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxPUV9NSzY1NFE4aFV6LTdYNWE0bzBrOUZnQVhCN1pIb0MtU3JkdnVJbmhxQlRRZWtRUnpZNm0ySDV4Si1NNzRLeERVSFBLRnpEcWNQUUlfNVVXMUF1S3djVkx6YlVIOGRNeDFUbHZ6Q3phNUNQZ2lUMmFxUVBTamZyUjBIb2QxWlhGZXAtTXh2SUFna2laSEY5M3p2WTdoTU8yZGUyeGVLU1B0RmttS0NwUVJRbDNTMC13UWtuNTlNZGQ5SkVyN2lpX1pIVkFHU253UTlkTGg2cw?oc=5</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-19T03:02:00+08:00</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>全球</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="44" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>整合一级资产+资本化</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>延江股份（上市公司）</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>集成电路资产（未披露具体名称）</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>半导体/集成电路</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>非织造布（卫生材料）</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>延江股份因关键条款未谈妥终止收购集成电路资产</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>终止</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>关键条款未谈妥</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>东方财富</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTFBzZC00dzY0alVZOTJ4bVF0cEZhOU5IeHFHSml1dmVxeENWQl9LYWhiSW5nT2NvRnVOb19xTGdsMFVpZ29ib3VBMzhCU0FsT0h3VE5mUG5KaDF6bzJaeWFFOQ?oc=5</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-19T02:49:55+08:00</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="44" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>上市公司控股权并购</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
           <t>中国国际金融股份有限公司（中金公司）</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>东兴证券股份有限公司、信达证券股份有限公司</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>金融（证券）</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>投资银行、证券经纪、资产管理、自营投资等综合证券业务</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>证券经纪、投资银行、资产管理等综合证券业务</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>中金公司换股吸收合并东兴证券和信达证券，打造头部券商整合平台</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>金融/证券</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>投资银行、证券经纪等</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>证券业务</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>中金公司换股吸收合并东兴证券和信达证券，打造万亿级券商</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>未知</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
         <is>
           <t>进行中</t>
         </is>
       </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>吸收合并完成后，东兴证券和信达证券将注销法人资格</t>
-        </is>
-      </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>巨潮资讯网</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225314592.PDF</t>
-        </is>
-      </c>
-      <c r="O10" s="3" t="inlineStr">
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>报告书草案摘要</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>上海证券报电子版</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE1OdkhQT2ZmUmtJdk9uQnJXZXlKZnExclZQbjlMZDRsM1NtU25ZU0dfYWxOQmFEaS10NnUwWkQ3NXBiY21JRFlIRE8yX3Vmc2lueEs1VGx0SzRQUU81M3VXeUYzUkJGQzVPSG4zUHZR?oc=5</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-19T02:22:13+08:00</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="44" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>上市公司控股权并购</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Neurocrine Biosciences</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Soleno Therapeutics</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>生物医药</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>神经科学领域药物开发</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>罕见病药物开发</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Neurocrine以29亿美元收购Soleno，扩展罕见病产品线</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="P10" s="3" t="inlineStr">
-        <is>
-          <t>中国</t>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>29亿美元</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>Pulse 2.0</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNNl9HQkJxcDZCN3lTLWVnZVpaWUFmM2MyUWtJaFZyNFpNa1RZcVlRWnBNM0w5VWpUM0pzMHFDT2pvNHM0Z0VkWkJuV3ZhMHZrZlY0bmtyTXdUYkszVjFINzZ6RXAwOE1CYjZ2czFLOVVJLWVac3FyQ1pIR0hvWldNUExEYVJ5NHFjSmg0VXh2RjRwTHluVFRUNllWQUVIalJKYWhmRmwxV0dRRFFUQjBoTVVYSy1xc2pG0gG-AUFVX3lxTE55V3VTck9tMUZFVUctSEVKVWlJUUtOUF9ycHdiVU1icDdDVzNGOWlGT3JzbzNPdU5yTGlRWDVwZGkzRktiUDFDcm0xcUo2YUNFNkF5ejRlejdkT3QwVVVTWHBVdVlJM1dJUGRtRUl3dzVaenduMDM0dVpSWTY3Q1RyOXNmRG8zdWxBTzNUU1I5R05vS2pCaHRjWUYwcEExOFZNalJaREUzVHpPckY4aS1JeWZjenJlYUJyRFduMVE?oc=5</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-19T01:14:29+08:00</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>全球</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P10"/>
+  <autoFilter ref="A1:P24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1324,7 +2444,7 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>2026-05-13 15:30 至 2026-05-20 15:30（北京时间，最近 1 周）</t>
+          <t>2026-05-13 15:56 至 2026-05-20 15:56（北京时间，最近 1 周）</t>
         </is>
       </c>
     </row>
@@ -1335,7 +2455,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
@@ -1356,7 +2476,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2026-05-20T15:34:34</t>
+          <t>2026-05-20T16:04:13</t>
         </is>
       </c>
     </row>
@@ -1395,7 +2515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1595,22 +2715,22 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>上海证券交易所 - 并购重组披露栏目</t>
+          <t>巨潮资讯网 - 要约收购关键词</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>google_news_site</t>
+          <t>cninfo_api</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>上交所上市公司并购重组审核披露</t>
+          <t>要约收购与要约结果</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>审核/注册/进展</t>
+          <t>宣告/交割</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -1620,34 +2740,34 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>https://www.sse.com.cn/listing/disclosure/ma/</t>
+          <t>https://www.cninfo.com.cn/new/index.jsp</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>重组审核公告；项目信息；问询回复；重大资产重组</t>
+          <t>要约收购；要约收购报告书；要约收购结果公告</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>上交所上市公司公告 - 重大资产重组</t>
+          <t>巨潮资讯网 - 发行股份购买资产关键词</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>google_news_site</t>
+          <t>cninfo_api</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>沪市主板/科创板公司公告</t>
+          <t>发行股份/可转债购买资产</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>宣告/进展/交割</t>
+          <t>宣告/审核/注册</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -1657,34 +2777,34 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>https://www.sse.com.cn/disclosure/listedinfo/announcement/</t>
+          <t>https://www.cninfo.com.cn/new/index.jsp</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>重大资产重组；购买资产；出售资产；发行股份购买资产</t>
+          <t>发行股份购买资产；配套融资；重组报告书</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>上交所上市公司公告 - 收购/权益变动</t>
+          <t>巨潮资讯网 - 资产出售/资产置换关键词</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>google_news_site</t>
+          <t>cninfo_api</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>沪市公司控制权和股权变动</t>
+          <t>资产剥离、置出、重大资产出售</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>权益变动/控制权</t>
+          <t>宣告/交割</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -1694,19 +2814,19 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>https://www.sse.com.cn/disclosure/listedinfo/announcement/</t>
+          <t>https://www.cninfo.com.cn/new/index.jsp</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>收购报告书；权益变动报告书；实际控制人变更；协议转让</t>
+          <t>重大资产出售；资产置换；置入置出；资产出售</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>深圳证券交易所 - 上市公司公告入口</t>
+          <t>上海证券交易所 - 并购重组披露栏目</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -1716,12 +2836,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>深市主板/创业板公司公告</t>
+          <t>上交所上市公司并购重组审核披露</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>宣告/进展/交割</t>
+          <t>审核/注册/进展</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -1731,19 +2851,19 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>https://www.szse.cn/disclosure/listed/notice/index.html</t>
+          <t>https://www.sse.com.cn/listing/disclosure/ma/</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>并购；重组；收购；权益变动；重大资产重组</t>
+          <t>重组审核公告；项目信息；问询回复；重大资产重组</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>深圳证券交易所 - 发行上市/并购重组入口</t>
+          <t>上交所上市公司公告 - 重大资产重组</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -1753,34 +2873,34 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>深市重组审核、规则、项目动态</t>
+          <t>沪市主板/科创板公司公告</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>审核/注册/进展</t>
+          <t>宣告/进展/交割</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>每周</t>
+          <t>每日/每周</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>https://www.szse.cn/listing/</t>
+          <t>https://www.sse.com.cn/disclosure/listedinfo/announcement/</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>重组委；审核公告；项目动态；发行股份购买资产</t>
+          <t>重大资产重组；购买资产；出售资产；发行股份购买资产</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>深交所公告 - 重大资产重组关键词</t>
+          <t>上交所上市公司公告 - 收购/权益变动</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -1790,34 +2910,34 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>深市重大资产重组公告</t>
+          <t>沪市公司控制权和股权变动</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>宣告/审核/终止</t>
+          <t>权益变动/控制权</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>每日/每周</t>
+          <t>每周</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>https://www.szse.cn/disclosure/listed/notice/index.html</t>
+          <t>https://www.sse.com.cn/disclosure/listedinfo/announcement/</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>重组预案；重组草案；重组报告书；终止重组</t>
+          <t>收购报告书；权益变动报告书；实际控制人变更；协议转让</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>深交所公告 - 收购/权益变动关键词</t>
+          <t>深圳证券交易所 - 上市公司公告入口</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -1827,17 +2947,17 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>深市收购与权益变动</t>
+          <t>深市主板/创业板公司公告</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>权益变动/控制权</t>
+          <t>宣告/进展/交割</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>每周</t>
+          <t>每日/每周</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -1847,14 +2967,14 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>收购报告书；权益变动报告书；协议转让；控制权变更</t>
+          <t>并购；重组；收购；权益变动；重大资产重组</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>北京证券交易所 - 上市公司公告</t>
+          <t>深圳证券交易所 - 发行上市/并购重组入口</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -1864,12 +2984,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>北交所上市公司公告</t>
+          <t>深市重组审核、规则、项目动态</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>宣告/进展/交割</t>
+          <t>审核/注册/进展</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1879,19 +2999,19 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>https://www.bse.cn/disclosure/announcement.html</t>
+          <t>https://www.szse.cn/listing/</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>重组；收购；要约；权益变动；重大资产重组</t>
+          <t>重组委；审核公告；项目动态；发行股份购买资产</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>全国股转系统 - 挂牌公司公告</t>
+          <t>深交所公告 - 重大资产重组关键词</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -1901,34 +3021,34 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>新三板挂牌公司公告</t>
+          <t>深市重大资产重组公告</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>宣告/权益变动</t>
+          <t>宣告/审核/终止</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>每周</t>
+          <t>每日/每周</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>https://www.neeq.com.cn/disclosure/announcement.html</t>
+          <t>https://www.szse.cn/disclosure/listed/notice/index.html</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>收购；重组；定增并购；权益变动</t>
+          <t>重组预案；重组草案；重组报告书；终止重组</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>全国股转系统 - 并购重组类规则/公告</t>
+          <t>深交所公告 - 收购/权益变动关键词</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -1938,62 +3058,247 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>新三板并购重组业务规则和相关公告</t>
+          <t>深市收购与权益变动</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>规则/审核</t>
+          <t>权益变动/控制权</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>每月/按需</t>
+          <t>每周</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>https://www.neeq.com.cn/node/484.html</t>
+          <t>https://www.szse.cn/disclosure/listed/notice/index.html</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>并购重组；重大资产重组；权益变动；收购规则</t>
+          <t>收购报告书；权益变动报告书；协议转让；控制权变更</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
+          <t>北京证券交易所 - 上市公司公告</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>google_news_site</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>北交所上市公司公告</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>宣告/进展/交割</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>每周</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>https://www.bse.cn/disclosure/announcement.html</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>重组；收购；要约；权益变动；重大资产重组</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>北交所公告 - 重大资产重组关键词</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>google_news_site</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>北交所上市公司重大资产重组</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>宣告/审核/终止</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>每周</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>https://www.bse.cn/disclosure/announcement.html</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>重大资产重组；发行股份购买资产</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>全国股转系统 - 挂牌公司公告</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>google_news_site</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>新三板挂牌公司公告</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>宣告/权益变动</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>每周</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>https://www.neeq.com.cn/disclosure/announcement.html</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>收购；重组；定增并购；权益变动</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>全国股转系统 - 并购重组类规则/公告</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>google_news_site</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>新三板并购重组业务规则和相关公告</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>规则/审核</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>每月/按需</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>https://www.neeq.com.cn/node/484.html</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>并购重组；重大资产重组；权益变动；收购规则</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>全国股转系统 - 收购/要约关键词</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>google_news_site</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>新三板收购、要约、权益变动</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>权益变动/收购</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>每周</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>https://www.neeq.com.cn/disclosure/announcement.html</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>收购报告书；要约收购；权益变动报告书</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
           <t>Google News - Global M&amp;A</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>google_news_rss</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>全球并购新闻</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>宣告/进展/交割</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>每周</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>https://news.google.com/</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>global M&amp;A / acquisition / merger / takeover</t>
         </is>
@@ -2062,165 +3367,165 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>kevin wang admitted as partner of allen &amp; gledhill - allen &amp; gledhill</t>
+          <t>关于 发行 股份 及支付现金 购买 资产 并募集配套资金暨关联交易事项的进展公告</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>Google News - Global M&amp;A / allen &amp; gledhill</t>
+          <t>巨潮资讯网 - 全市场公告入口</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>2026-05-20T12:21:12+08:00</t>
+          <t>2026-05-20T15:40:12+08:00</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>全球</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>cross-border acquisition Chinese company announced</t>
+          <t>发行股份购买资产</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNVGU0NVJJeVNwNVI0dng3eVZ2V0RlcHBkMFZfdERGQVZKd094ZXpXMzRQM0NQcnZEWHB3X2VFX2lLMHo3RlZTLThKUHliRkdhSDJuZUpUSGhNdTBIRjVjRGc3R2o0U2lqS09Ic2NaM2JNOHRRVlF1UjdyTWJDaWZPV1k5WnpUcGtlN1MwTF9rZnBxOXlCOGR4dEJmeFZQc2RtV3l4TlhkdFo4a0ljNjlvZlVn?oc=5</t>
+          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225318605.PDF</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>kevin wang admitted as partner of allen &amp; gledhill allen &amp; gledhill</t>
+          <t>证券简称：海泰科</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>what's driving whitestone reit's $1.7 billion takeover by ares? - kavout</t>
+          <t>关于发行股份及支付现金 购买 资产 并募集配套资金暨关联交易事项的进展公告</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Google News - Global M&amp;A / kavout</t>
+          <t>巨潮资讯网 - 全市场公告入口</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>2026-05-20T08:03:33+08:00</t>
+          <t>2026-05-20T15:40:12+08:00</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>全球</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>takeover offer acquisition announced</t>
+          <t>购买资产</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPMDR4QmR6eFFfeWZOaVhxN1NBcEp3dnB5OUxQaTd6TW9yTVZTaGdPUWRMTTNSUDhpcUpubEhHUnZQcEtUdFlmZFRyV1Q3VW12dHZ1bjVqMXVMN2UxVGdUM01kdmgwTWxjOXQtSC1fZlc1OHZkYXEyYVlJUnVnaVRSdEJwb3pmWl9zRGpsOU1wbUlDcURUNXRsMjg2ZGE?oc=5</t>
+          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225318605.PDF</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>what's driving whitestone reit's $1.7 billion takeover by ares? kavout</t>
+          <t>证券简称：海泰科</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>paramount skydance corporation announces: offer to purchase for cash any and all of the identified notes in each series of existing tender offer notes and offer to exchange for newly issued notes of paramount skydance corporation ("new psky notes") - tradingview</t>
+          <t>制度红利持续释放 并购重组市场活力显著提升 - 搜狐网</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Google News - Global M&amp;A / tradingview</t>
+          <t>中国新闻广域 - Google News RSS / 搜狐网</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>2026-05-20T05:06:00+08:00</t>
+          <t>2026-05-20T14:46:43+08:00</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>全球</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>global merger acquisition announced company deal</t>
+          <t>中国 并购重组 收购 重大资产重组 交易完成</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwVBVV95cUxNQmUxaF9ERW9UMXRFMlJEUVdkb00taGdSeTFPdE5Gd2MxRGgxaHVtdFhsRThsR3hQREFXc0Q0eUVIQ3pPakt2TkYtdU1RdjdDRmZIVGdRYmRvcVJTODBpcmlQM0hpVVkzSk1LLUF4eTlSRUNJMUhlOEZtRThXWUhKQmMxaDJPajhhYjU0clNIVHFLUTlnNnBoZ0NvSV9hXzJWQldWWUdob3M3OWlxLVNsUFdCWXdZaDJVV25GWjVXOHd5NEUxY1BLdTBjOVNkdTZnV1pHNC1mS3BaRFJtcG90eENhclZjYzl4aHo1Mjg4V0hzNkxiM0Q1am9fNmpQTURBckpQWXQzQzc3aWFUYnQ2TWw5MGtXX19RcWFMbUZnZXFlWUFFS0JXOGxFZFRoUDZ4QzRHUExqSFozVlpkVHZKSExicnlsOXJpVzlaLWZMREZMNm1KNmthWXdDWEdBMXdKXy1BSlc1SlppM3R5WEVkQnpzZ0h1Umlkc2x2NklHMVRWTElOa0lmeUc4bXBfU0xwYmhfbFBxaWNTNkd6NTFaSUp6TVl0NmV6UW12Y05GUWN6TS04RWtRMEJIM0hXd1BMeTBnNFVSM1hsbGg3ZHAyeFluZFV4YzlPWUNscUtXNXRwYklDMnRPblQ4RkZiaFhLUTRXZGhoUDJPUV9pREdEdUdESkhkQXlicjVVbzRwYnBRSEY0QnMwSnNZZlJ3Tmw4NmRwS0NJQ3ZfN3MxTVN1LWFIT05NVXFuM2NhZFhfUXgta2dfNElRcjRaWU95R1Z5R2hBbG5fc3VQbmpmYWFjOFd0ZUt1bDVJZEM2UXNMZFNuUmJ4ejVHdk13Y3ZXcG14YlJxbjNTb0c4Qlk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxPOXM4LVpnakxYRmtsX19ETmpSdjVOU0VjQThIbWFWVU12SHp2d29tQmlxblhSZnlFcFJqckJMaWxVX0N5dGRKWXppTktYYU9EOVhsRVBFZnY1Tm81WmRLU2ZsSWFkX1RPZVh2dmtCOVdXdE81ME8wN1RQcmg1ZUNJbEVtWjhTQ1RqaFdSUzh6Q2FNaVg1MmozN1NLSWFMTEh3YjRhRXd2aHNJeXdraXR0bVpPeVVlLURQeGFTcHN3eDFmS05ILXIyQ0VSYkI1NklYUWJtNHJSbWJ1NWVpZXExaDRtX3dPM1k?oc=5</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>paramount skydance corporation announces: offer to purchase for cash any and all of the identified notes in each series of existing tender offer notes and offer to exchange for newly issued notes of paramount skydance corporation ("new psky notes") tradingview</t>
+          <t>制度红利持续释放 并购重组市场活力显著提升 搜狐网</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>exascale partners with compal for computex (bcar) — june 2–5, 2026 - stock titan</t>
+          <t>跨界并购！300069，301322，一字涨停 - 同花顺财经</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Google News - Global M&amp;A / stock titan</t>
+          <t>财经媒体/专业资讯 - 中国并购 / 同花顺财经</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>2026-05-20T04:31:39+08:00</t>
+          <t>2026-05-20T14:18:19+08:00</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>全球</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>SPAC merger announced acquisition</t>
+          <t>每日经济新闻 并购重组 收购</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQaF96UHdJY0VnRVpXV3ZMLUhsT1J0V2RZc2xHNWd6SWo2ZXJkTmt6emFzU0s1ZU1oSDNkWFk2WDd0N3hMOUpfY2JHN2xBV29pdHhnRUxEVDloRVIyaVM5NWdSZTZ4VFU5RFlob2lJSEpqZl9YYUxwUVVDbHRKd1FjOHRVczJTcTQyQWUteVFoYkJfMkVUcTBaMVJ5dFBFTEJFMWducGxxUEpDSHRyNHFDMHBhc3V2SFBWREhsY1hCRWtSS2tyRDFJOTBlOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXkFVX3lxTE9Fbl9LVGdFU0xxbllqTm16VUY4a0Z2bnlydG9Balk4cW9ya1dWUHdRTHpSVGotcFgxVUMybDI5SVBURnFYRHZjbUhRNVV0RDdWNEpqdTRKY2pMUVA2WUE?oc=5</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>exascale partners with compal for computex (bcar) — june 2–5, 2026 stock titan</t>
+          <t>跨界并购！300069，301322，一字涨停 同花顺财经</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>shreya acquisition group (sagu) allows separate trading of shares, warrants and rights - stock titan</t>
+          <t>kevin wang admitted as partner of allen &amp; gledhill - allen &amp; gledhill</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Google News - Global M&amp;A / stock titan</t>
+          <t>Google News - Global M&amp;A / allen &amp; gledhill</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>2026-05-20T04:15:16+08:00</t>
+          <t>2026-05-20T12:21:12+08:00</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -2230,108 +3535,108 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>SPAC merger announced acquisition</t>
+          <t>cross-border acquisition Chinese company announced</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQbnNETjJnQTJEZzIxMnRNM2EybkZwV0F4Z1VpRjdUWGlWLXZGY3NDbnpRQ3VueXVzWHdmeUV6ZWo4cWhHcWx1aHJmWklUQ0xGTzRoZkF6b1hhVHlnSVFWLWNsS25CWV9kcndjUVpYeEJMZVFETGJER2tpbXdITl9GanVyQmhGUk1WeTdneHlObGtmS0tzZ2dfQVh4NmpQYTZUQU1DT2lfLWdXcVQ2cFdWSHdBNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisgFBVV95cUxNVGU0NVJJeVNwNVI0dng3eVZ2V0RlcHBkMFZfdERGQVZKd094ZXpXMzRQM0NQcnZEWHB3X2VFX2lLMHo3RlZTLThKUHliRkdhSDJuZUpUSGhNdTBIRjVjRGc3R2o0U2lqS09Ic2NaM2JNOHRRVlF1UjdyTWJDaWZPV1k5WnpUcGtlN1MwTF9rZnBxOXlCOGR4dEJmeFZQc2RtV3l4TlhkdFo4a0ljNjlvZlVn?oc=5</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>shreya acquisition group (sagu) allows separate trading of shares, warrants and rights stock titan</t>
+          <t>kevin wang admitted as partner of allen &amp; gledhill allen &amp; gledhill</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>global mergers and acquisitions still cannot fully recover in the 1st quarter - lnginnorthernbc.ca</t>
+          <t>09:28:07【竞价看龙头】 - 财联社</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Google News - Global M&amp;A / lnginnorthernbc.ca</t>
+          <t>财经媒体/专业资讯 - 中国并购 / 财联社</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>2026-05-20T02:30:19+08:00</t>
+          <t>2026-05-20T09:28:07+08:00</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>全球</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>global merger acquisition announced company deal</t>
+          <t>财联社 并购重组 收购</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNV0NfSFQzOEluNEtfcF9sZ2FhMXJkQmFMWkthR0Zpb2dDSVZqUkY3THQ3YUMxVUthal9YVnZVS09PWG9VMHhwOHY1N3pfV1dNQ2RGRUZxYnljYlNvMUZvMW1jdDJJS1MwM0QzU1RfREJxMWZCUUpVR3VWRmdjMDJnNlV5bE1RYkJ3aGVEVURnTlBvWjlqUGdnZ3NZTW95Y3BDY081b0NVYkotYzJnR0xvdlIwUGpzVFk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiSEFVX3lxTE5QUTdHdVgwMHR0eXBHY2RPNnQ1Sld5QkdkWmp6X1VYdmxocEx0dUYwcHYwc3l3NVVHV2JfMWFkcUh6Zk9XVFh2MQ?oc=5</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>global mergers and acquisitions still cannot fully recover in the 1st quarter lnginnorthernbc.ca</t>
+          <t>09:28:07【竞价看龙头】 财联社</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>sec exemptive order authorizes accelerated tender offers - wilmerhale</t>
+          <t>又一a股进军商业航天领域！跨界并购预案公布 - 东方财富</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Google News - Global M&amp;A / wilmerhale</t>
+          <t>财经媒体/专业资讯 - 中国并购 / 东方财富</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>2026-05-20T02:17:33+08:00</t>
+          <t>2026-05-20T08:07:27+08:00</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>全球</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>takeover offer acquisition announced</t>
+          <t>东方财富 并购重组 收购</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNcnhpMS0tWV9IWnhkWVJ2Z3JiWmdHZ3VtOU45R1RubnJCaG9ZYUpRTklEd1RGLThjM2t4TVc3eGJucDZ4NUxObTd2c3RBTkVRWXRrNGxHTDJZUnh0QnRxbjFzRXNsUzQ2ZlQ5OHhDZlcxM2dVRnVnR0d4dGtLTDdGNTNFNzF0dm5PX0FWcGlHSG1fWnRfUUVzRTEwTGFwRl9SbnlIY3N1YU9XN3RENWhDS0t0eXc5TEdF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE55eEVPT2tfTVFLb3A1aVMyZzd0dGItaWF1YTJoRzZwdWNTWDNzbEFkUWxaVS1UNEZERnI1N3dPWUkxZWY5bTYya25Kajh1NHhDUTdWQkY0Z1lKdU16ejFpTDZnTWxCZw?oc=5</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>sec exemptive order authorizes accelerated tender offers wilmerhale</t>
+          <t>又一a股进军商业航天领域！跨界并购预案公布 东方财富</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>scenes from d ceo’s 2026 mergers &amp; acquisitions awards - d magazine</t>
+          <t>what's driving whitestone reit's $1.7 billion takeover by ares? - kavout</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Google News - Global M&amp;A / d magazine</t>
+          <t>Google News - Global M&amp;A / kavout</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>2026-05-20T02:14:43+08:00</t>
+          <t>2026-05-20T08:03:33+08:00</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -2346,177 +3651,177 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQWFE4aUdkdE5PeHhrS1dJM3VKY0FRb1ZxeDQ2b0VoSEVlbjRLSzQ1ckIzYS1nOEhtT0ZzTzhnbFBFQTZ2c2hneS0wRTRJcGFNMkxneTdEcVNCNWprVExIQmxqQUw2T3B0bjFFMmdzZUJTOWxuQk5zLV8wdjBGYW5fTV9PSlVrbWJlVzQwZmpqdDlWZHV4alAyRnAyeC1ySkdkM0haOWdB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPMDR4QmR6eFFfeWZOaVhxN1NBcEp3dnB5OUxQaTd6TW9yTVZTaGdPUWRMTTNSUDhpcUpubEhHUnZQcEtUdFlmZFRyV1Q3VW12dHZ1bjVqMXVMN2UxVGdUM01kdmgwTWxjOXQtSC1fZlc1OHZkYXEyYVlJUnVnaVRSdEJwb3pmWl9zRGpsOU1wbUlDcURUNXRsMjg2ZGE?oc=5</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>scenes from d ceo’s 2026 mergers &amp; acquisitions awards d magazine</t>
+          <t>what's driving whitestone reit's $1.7 billion takeover by ares? kavout</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>广州洁特生物过滤股份有限公司关于股份回购实施结果暨股份变动的公告 - 上海证券交易所科创板</t>
+          <t>paramount skydance corporation announces: offer to purchase for cash any and all of the identified notes in each series of existing tender offer notes and offer to exchange for newly issued notes of paramount skydance corporation ("new psky notes") - tradingview</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>上交所上市公司公告 - 收购/权益变动 / 上海证券交易所科创板</t>
+          <t>Google News - Global M&amp;A / tradingview</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>2026-05-20T02:10:17+08:00</t>
+          <t>2026-05-20T05:06:00+08:00</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>全球</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>site:sse.com.cn/disclosure/listedinfo/announcement 权益变动报告书</t>
+          <t>global merger acquisition announced company deal</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPUnJQYWJCYUFWU3NndWhDWEJkR2lJVXdHY00xSlRLeUh3VzQ1dndVajROd21RMG5JMlBLdFpCWUpSdjRtUDJSdzZtZmp6aVhseVlrYzlJMVF6Q1pNX1NpNVdwTUI0S1VoaV9senBYMzc0d0xSSG55UUpsR2VjcG83U3pST2tSNS1UUmdDZFpTeThiWHcyRVZGdUFxUy1IeHZrWEE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwVBVV95cUxNQmUxaF9ERW9UMXRFMlJEUVdkb00taGdSeTFPdE5Gd2MxRGgxaHVtdFhsRThsR3hQREFXc0Q0eUVIQ3pPakt2TkYtdU1RdjdDRmZIVGdRYmRvcVJTODBpcmlQM0hpVVkzSk1LLUF4eTlSRUNJMUhlOEZtRThXWUhKQmMxaDJPajhhYjU0clNIVHFLUTlnNnBoZ0NvSV9hXzJWQldWWUdob3M3OWlxLVNsUFdCWXdZaDJVV25GWjVXOHd5NEUxY1BLdTBjOVNkdTZnV1pHNC1mS3BaRFJtcG90eENhclZjYzl4aHo1Mjg4V0hzNkxiM0Q1am9fNmpQTURBckpQWXQzQzc3aWFUYnQ2TWw5MGtXX19RcWFMbUZnZXFlWUFFS0JXOGxFZFRoUDZ4QzRHUExqSFozVlpkVHZKSExicnlsOXJpVzlaLWZMREZMNm1KNmthWXdDWEdBMXdKXy1BSlc1SlppM3R5WEVkQnpzZ0h1Umlkc2x2NklHMVRWTElOa0lmeUc4bXBfU0xwYmhfbFBxaWNTNkd6NTFaSUp6TVl0NmV6UW12Y05GUWN6TS04RWtRMEJIM0hXd1BMeTBnNFVSM1hsbGg3ZHAyeFluZFV4YzlPWUNscUtXNXRwYklDMnRPblQ4RkZiaFhLUTRXZGhoUDJPUV9pREdEdUdESkhkQXlicjVVbzRwYnBRSEY0QnMwSnNZZlJ3Tmw4NmRwS0NJQ3ZfN3MxTVN1LWFIT05NVXFuM2NhZFhfUXgta2dfNElRcjRaWU95R1Z5R2hBbG5fc3VQbmpmYWFjOFd0ZUt1bDVJZEM2UXNMZFNuUmJ4ejVHdk13Y3ZXcG14YlJxbjNTb0c4Qlk?oc=5</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>广州洁特生物过滤股份有限公司关于股份回购实施结果暨股份变动的公告 上海证券交易所科创板</t>
+          <t>paramount skydance corporation announces: offer to purchase for cash any and all of the identified notes in each series of existing tender offer notes and offer to exchange for newly issued notes of paramount skydance corporation ("new psky notes") tradingview</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>关于终止筹划 重大 资产重组 并变更为一般股权投资的公告</t>
+          <t>exascale partners with compal for computex (bcar) — june 2–5, 2026 - stock titan</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>Google News - Global M&amp;A / stock titan</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>2026-05-20T00:00:00+08:00</t>
+          <t>2026-05-20T04:31:39+08:00</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>全球</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>重大资产重组</t>
+          <t>SPAC merger announced acquisition</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225317889.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxQaF96UHdJY0VnRVpXV3ZMLUhsT1J0V2RZc2xHNWd6SWo2ZXJkTmt6emFzU0s1ZU1oSDNkWFk2WDd0N3hMOUpfY2JHN2xBV29pdHhnRUxEVDloRVIyaVM5NWdSZTZ4VFU5RFlob2lJSEpqZl9YYUxwUVVDbHRKd1FjOHRVczJTcTQyQWUteVFoYkJfMkVUcTBaMVJ5dFBFTEJFMWducGxxUEpDSHRyNHFDMHBhc3V2SFBWREhsY1hCRWtSS2tyRDFJOTBlOA?oc=5</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>证券简称：奕帆传动</t>
+          <t>exascale partners with compal for computex (bcar) — june 2–5, 2026 stock titan</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>关于筹划本次 重大 资产重组 停牌前一个交易日前十大股东和前十大流通股股东持股情况的公告</t>
+          <t>global mergers and acquisitions still cannot fully recover in the 1st quarter - lnginnorthernbc.ca</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>Google News - Global M&amp;A / lnginnorthernbc.ca</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>2026-05-20T00:00:00+08:00</t>
+          <t>2026-05-20T02:30:19+08:00</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>全球</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>重大资产重组</t>
+          <t>global merger acquisition announced company deal</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225317251.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNV0NfSFQzOEluNEtfcF9sZ2FhMXJkQmFMWkthR0Zpb2dDSVZqUkY3THQ3YUMxVUthal9YVnZVS09PWG9VMHhwOHY1N3pfV1dNQ2RGRUZxYnljYlNvMUZvMW1jdDJJS1MwM0QzU1RfREJxMWZCUUpVR3VWRmdjMDJnNlV5bE1RYkJ3aGVEVURnTlBvWjlqUGdnZ3NZTW95Y3BDY081b0NVYkotYzJnR0xvdlIwUGpzVFk?oc=5</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>证券简称：金利华电</t>
+          <t>global mergers and acquisitions still cannot fully recover in the 1st quarter lnginnorthernbc.ca</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>董事会关于本次交易符合《上市公司监管指引第9号——上市公司筹划和实施 重大 资产重组 的监管要求》第四条规定的说明</t>
+          <t>scenes from d ceo’s 2026 mergers &amp; acquisitions awards - d magazine</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>Google News - Global M&amp;A / d magazine</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>2026-05-20T00:00:00+08:00</t>
+          <t>2026-05-20T02:14:43+08:00</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>全球</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>重大资产重组</t>
+          <t>M&amp;A acquisition merger deal announced last week</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225317244.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQWFE4aUdkdE5PeHhrS1dJM3VKY0FRb1ZxeDQ2b0VoSEVlbjRLSzQ1ckIzYS1nOEhtT0ZzTzhnbFBFQTZ2c2hneS0wRTRJcGFNMkxneTdEcVNCNWprVExIQmxqQUw2T3B0bjFFMmdzZUJTOWxuQk5zLV8wdjBGYW5fTV9PSlVrbWJlVzQwZmpqdDlWZHV4alAyRnAyeC1ySkdkM0haOWdB?oc=5</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>证券简称：金利华电</t>
+          <t>scenes from d ceo’s 2026 mergers &amp; acquisitions awards d magazine</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>董事会关于公司本次交易符合《上市公司 重大 资产重组 管理办法》第十一条、第四十三条和第四十四条规定的说明</t>
+          <t>广州洁特生物过滤股份有限公司关于股份回购实施结果暨股份变动的公告 - 上海证券交易所科创板</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>上交所上市公司公告 - 收购/权益变动 / 上海证券交易所科创板</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>2026-05-20T00:00:00+08:00</t>
+          <t>2026-05-20T02:10:17+08:00</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -2526,34 +3831,34 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>重大资产重组</t>
+          <t>site:sse.com.cn/disclosure/listedinfo/announcement 权益变动报告书</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225317243.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPUnJQYWJCYUFWU3NndWhDWEJkR2lJVXdHY00xSlRLeUh3VzQ1dndVajROd21RMG5JMlBLdFpCWUpSdjRtUDJSdzZtZmp6aVhseVlrYzlJMVF6Q1pNX1NpNVdwTUI0S1VoaV9senBYMzc0d0xSSG55UUpsR2VjcG83U3pST2tSNS1UUmdDZFpTeThiWHcyRVZGdUFxUy1IeHZrWEE?oc=5</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>证券简称：金利华电</t>
+          <t>广州洁特生物过滤股份有限公司关于股份回购实施结果暨股份变动的公告 上海证券交易所科创板</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>董事会关于本次交易符合《创业板上市公司持续监管办法（试行）》 第十八条、第二十一条以及《深圳证券交易所上市公司 重大 资产重组 审核规则》第八条规定的说明</t>
+          <t>绿通科技再推跨界并购，拟斥资1.2亿元揽入诚瑞科技 - 东方财富</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>财经媒体/专业资讯 - 中国并购 / 东方财富</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>2026-05-20T00:00:00+08:00</t>
+          <t>2026-05-20T01:01:41+08:00</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -2563,34 +3868,34 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>重大资产重组</t>
+          <t>东方财富 并购重组 收购</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225317242.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTFBwWG85NDZ4ZEFmZUxndEktQ2hHUlJka0RTbTJZSTF5emtzN3VveWVBTFg0SVNENEJfRF9DajdMeE5lQzJXT0IwU3NPdXdVb05OVzVPbzBDSThzVDFFX182Sg?oc=5</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>证券简称：金利华电</t>
+          <t>绿通科技再推跨界并购，拟斥资1.2亿元揽入诚瑞科技 东方财富</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>董事会关于本次交易是否构成 重大 资产重组 、关联交易及重组上市的说明</t>
+          <t>绿通科技再推跨界并购，拟斥资1.2亿元揽入诚瑞科技 - mrjjxw.com</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>财经媒体/专业资讯 - 中国并购 / mrjjxw.com</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>2026-05-20T00:00:00+08:00</t>
+          <t>2026-05-20T00:27:00+08:00</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -2600,24 +3905,24 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>重大资产重组</t>
+          <t>每日经济新闻 并购重组 收购</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225317240.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTE4zQ0xCRnJud29QbXMyUno4bFczMGRHd0RnLUdiMWprYjNSc3hkcmdnWEdydHBtUmpsZll5aGdKREJ2YmNqSTd0ZHpUWHhoMjJyY3pidGhwNVdZQlk3Z2p4LVBTNDZtZw?oc=5</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>证券简称：金利华电</t>
+          <t>绿通科技再推跨界并购，拟斥资1.2亿元揽入诚瑞科技 mrjjxw.com</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>关于延期回复上海证券交易所《关于对永杰新材料股份有限公司 重大 资产重组 草案的问询函》的公告</t>
+          <t>关于终止筹划 重大 资产重组 并变更为一般股权投资的公告</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -2642,19 +3947,19 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225315580.PDF</t>
+          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225317889.PDF</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>证券简称：永杰新材</t>
+          <t>证券简称：奕帆传动</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>上市公司关于 发行 股份 及支付现金 购买 资产 并募集配套资金暨关联交易事项的一般风险提示暨公司股票复牌的提示性公告</t>
+          <t>关于筹划本次 重大 资产重组 停牌前一个交易日前十大股东和前十大流通股股东持股情况的公告</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -2674,12 +3979,12 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>发行股份购买资产</t>
+          <t>重大资产重组</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225317248.PDF</t>
+          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225317251.PDF</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -2691,7 +3996,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>金利华电气 股份 有限公司 发行 股份 及支付现金 购买 资产 并募集配套资金暨关联交易预案摘要</t>
+          <t>董事会关于本次交易符合《上市公司监管指引第9号——上市公司筹划和实施 重大 资产重组 的监管要求》第四条规定的说明</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -2711,12 +4016,12 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>发行股份购买资产</t>
+          <t>重大资产重组</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225317239.PDF</t>
+          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225317244.PDF</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
@@ -2728,7 +4033,7 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>金利华电气 股份 有限公司 发行 股份 及支付现金 购买 资产 并募集配套资金暨关联交易预案</t>
+          <t>董事会关于公司本次交易符合《上市公司 重大 资产重组 管理办法》第十一条、第四十三条和第四十四条规定的说明</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -2748,12 +4053,12 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>发行股份购买资产</t>
+          <t>重大资产重组</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225317236.PDF</t>
+          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225317243.PDF</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
@@ -2765,7 +4070,7 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>中国国际金融 股份 有限公司关于武汉三镇实业控股 股份 有限公司终止 发行 股份 及支付现金 购买 资产 并募集配套资金暨关联交易事项的核查意见_vs</t>
+          <t>董事会关于本次交易符合《创业板上市公司持续监管办法（试行）》 第十八条、第二十一条以及《深圳证券交易所上市公司 重大 资产重组 审核规则》第八条规定的说明</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -2785,24 +4090,24 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>发行股份购买资产</t>
+          <t>重大资产重组</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225317031.PDF</t>
+          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225317242.PDF</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>证券简称：武汉控股</t>
+          <t>证券简称：金利华电</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>武汉三镇实业控股 股份 有限公司关于终止 发行 股份 及支付现金 购买 资产 并募集配套资金暨关联交易事项并撤回申请文件的公告</t>
+          <t>董事会关于本次交易是否构成 重大 资产重组 、关联交易及重组上市的说明</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -2822,24 +4127,24 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>发行股份购买资产</t>
+          <t>重大资产重组</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225317030.PDF</t>
+          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225317240.PDF</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>证券简称：武汉控股</t>
+          <t>证券简称：金利华电</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>德马科技关于 发行 股份 及支付现金 购买 资产 暨关联交易之业绩承诺期届满减值测试情况的公告</t>
+          <t>关于延期回复上海证券交易所《关于对永杰新材料股份有限公司 重大 资产重组 草案的问询函》的公告</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -2859,24 +4164,24 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>发行股份购买资产</t>
+          <t>重大资产重组</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225316177.PDF</t>
+          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225315580.PDF</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>证券简称：德马科技</t>
+          <t>证券简称：永杰新材</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>国金证券 股份 有限公司关于德马科技集团 股份 有限公司 发行 股份 及支付现金 购买 资产 暨关联交易之业绩承诺期届满减值测试情况的核查意见</t>
+          <t>上市公司关于 发行 股份 及支付现金 购买 资产 并募集配套资金暨关联交易事项的一般风险提示暨公司股票复牌的提示性公告</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -2901,19 +4206,19 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225316169.PDF</t>
+          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225317248.PDF</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>证券简称：德马科技</t>
+          <t>证券简称：金利华电</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>中信证券 股份 有限公司关于沈阳机床 股份 有限公司 发行 股份 购买 资产 并募集配套资金暨关联交易之2025年度持续督导意见</t>
+          <t>金利华电气 股份 有限公司 发行 股份 及支付现金 购买 资产 并募集配套资金暨关联交易预案摘要</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -2938,19 +4243,19 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225315561.PDF</t>
+          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225317239.PDF</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>证券简称：沈阳机床</t>
+          <t>证券简称：金利华电</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>关于全资子公司拟 购买 资产 的公告</t>
+          <t>金利华电气 股份 有限公司 发行 股份 及支付现金 购买 资产 并募集配套资金暨关联交易预案</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
@@ -2970,24 +4275,24 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>购买资产</t>
+          <t>发行股份购买资产</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225318035.PDF</t>
+          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225317236.PDF</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>证券简称：珠海中富</t>
+          <t>证券简称：金利华电</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>上市公司关于发行股份及支付现金 购买 资产 并募集配套资金暨关联交易事项的一般风险提示暨公司股票复牌的提示性公告</t>
+          <t>中国国际金融 股份 有限公司关于武汉三镇实业控股 股份 有限公司终止 发行 股份 及支付现金 购买 资产 并募集配套资金暨关联交易事项的核查意见_vs</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -3007,24 +4312,24 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>购买资产</t>
+          <t>发行股份购买资产</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225317248.PDF</t>
+          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225317031.PDF</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>证券简称：金利华电</t>
+          <t>证券简称：武汉控股</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>董事会关于本次交易前十二个月内上市公司 购买 、出售 资产 情况的说明</t>
+          <t>武汉三镇实业控股 股份 有限公司关于终止 发行 股份 及支付现金 购买 资产 并募集配套资金暨关联交易事项并撤回申请文件的公告</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -3044,24 +4349,24 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>购买资产</t>
+          <t>发行股份购买资产</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225317246.PDF</t>
+          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225317030.PDF</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>证券简称：金利华电</t>
+          <t>证券简称：武汉控股</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>金利华电气股份有限公司发行股份及支付现金 购买 资产 并募集配套资金暨关联交易预案摘要</t>
+          <t>德马科技关于 发行 股份 及支付现金 购买 资产 暨关联交易之业绩承诺期届满减值测试情况的公告</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -3081,24 +4386,24 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>购买资产</t>
+          <t>发行股份购买资产</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225317239.PDF</t>
+          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225316177.PDF</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>证券简称：金利华电</t>
+          <t>证券简称：德马科技</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>金利华电气股份有限公司发行股份及支付现金 购买 资产 并募集配套资金暨关联交易预案</t>
+          <t>国金证券 股份 有限公司关于德马科技集团 股份 有限公司 发行 股份 及支付现金 购买 资产 暨关联交易之业绩承诺期届满减值测试情况的核查意见</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
@@ -3118,24 +4423,24 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>购买资产</t>
+          <t>发行股份购买资产</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225317236.PDF</t>
+          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225316169.PDF</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>证券简称：金利华电</t>
+          <t>证券简称：德马科技</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司关于武汉三镇实业控股股份有限公司终止发行股份及支付现金 购买 资产 并募集配套资金暨关联交易事项的核查意见_vs</t>
+          <t>中信证券 股份 有限公司关于沈阳机床 股份 有限公司 发行 股份 购买 资产 并募集配套资金暨关联交易之2025年度持续督导意见</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -3155,24 +4460,24 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>购买资产</t>
+          <t>发行股份购买资产</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225317031.PDF</t>
+          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225315561.PDF</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>证券简称：武汉控股</t>
+          <t>证券简称：沈阳机床</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>武汉三镇实业控股股份有限公司关于终止发行股份及支付现金 购买 资产 并募集配套资金暨关联交易事项并撤回申请文件的公告</t>
+          <t>关于全资子公司拟 购买 资产 的公告</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -3197,19 +4502,19 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225317030.PDF</t>
+          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225318035.PDF</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>证券简称：武汉控股</t>
+          <t>证券简称：珠海中富</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>德马科技关于发行股份及支付现金 购买 资产 暨关联交易之业绩承诺期届满减值测试情况的公告</t>
+          <t>上市公司关于发行股份及支付现金 购买 资产 并募集配套资金暨关联交易事项的一般风险提示暨公司股票复牌的提示性公告</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
@@ -3234,19 +4539,19 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225316177.PDF</t>
+          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225317248.PDF</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>证券简称：德马科技</t>
+          <t>证券简称：金利华电</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>国金证券股份有限公司关于德马科技集团股份有限公司发行股份及支付现金 购买 资产 暨关联交易之业绩承诺期届满减值测试情况的核查意见</t>
+          <t>董事会关于本次交易前十二个月内上市公司 购买 、出售 资产 情况的说明</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
@@ -3271,19 +4576,19 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225316169.PDF</t>
+          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225317246.PDF</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>证券简称：德马科技</t>
+          <t>证券简称：金利华电</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司关于沈阳机床股份有限公司发行股份 购买 资产 并募集配套资金暨关联交易之2025年度持续督导意见</t>
+          <t>金利华电气股份有限公司发行股份及支付现金 购买 资产 并募集配套资金暨关联交易预案摘要</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
@@ -3308,19 +4613,19 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225315561.PDF</t>
+          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225317239.PDF</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>证券简称：沈阳机床</t>
+          <t>证券简称：金利华电</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>浙江大胜达包装股份有限公司关于 购买 资产 及与关联方共同对外投资的进展公告</t>
+          <t>金利华电气股份有限公司发行股份及支付现金 购买 资产 并募集配套资金暨关联交易预案</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
@@ -3345,19 +4650,19 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225315529.PDF</t>
+          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225317236.PDF</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>证券简称：大胜达</t>
+          <t>证券简称：金利华电</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>董事会关于本次交易前十二个月内上市公司购买、 出售 资产 情况的说明</t>
+          <t>中国国际金融股份有限公司关于武汉三镇实业控股股份有限公司终止发行股份及支付现金 购买 资产 并募集配套资金暨关联交易事项的核查意见_vs</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
@@ -3377,24 +4682,24 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>出售资产</t>
+          <t>购买资产</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225317246.PDF</t>
+          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225317031.PDF</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>证券简称：金利华电</t>
+          <t>证券简称：武汉控股</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>本钢板材股份有限公司关于重大 资产 置换 暨关联交易的进展公告</t>
+          <t>武汉三镇实业控股股份有限公司关于终止发行股份及支付现金 购买 资产 并募集配套资金暨关联交易事项并撤回申请文件的公告</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
@@ -3414,24 +4719,24 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>资产置换</t>
+          <t>购买资产</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225317228.PDF</t>
+          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225317030.PDF</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>证券简称：本钢板材</t>
+          <t>证券简称：武汉控股</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>关于终止筹划重大 资产重组 并变更为一般股权投资的公告</t>
+          <t>德马科技关于发行股份及支付现金 购买 资产 暨关联交易之业绩承诺期届满减值测试情况的公告</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
@@ -3451,24 +4756,24 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>资产重组</t>
+          <t>购买资产</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225317889.PDF</t>
+          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225316177.PDF</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>证券简称：奕帆传动</t>
+          <t>证券简称：德马科技</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>关于筹划本次重大 资产重组 停牌前一个交易日前十大股东和前十大流通股股东持股情况的公告</t>
+          <t>国金证券股份有限公司关于德马科技集团股份有限公司发行股份及支付现金 购买 资产 暨关联交易之业绩承诺期届满减值测试情况的核查意见</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
@@ -3488,24 +4793,24 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>资产重组</t>
+          <t>购买资产</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225317251.PDF</t>
+          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225316169.PDF</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>证券简称：金利华电</t>
+          <t>证券简称：德马科技</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>董事会关于本次交易符合《上市公司监管指引第9号——上市公司筹划和实施重大 资产重组 的监管要求》第四条规定的说明</t>
+          <t>中信证券股份有限公司关于沈阳机床股份有限公司发行股份 购买 资产 并募集配套资金暨关联交易之2025年度持续督导意见</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
@@ -3525,24 +4830,24 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>资产重组</t>
+          <t>购买资产</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225317244.PDF</t>
+          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225315561.PDF</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>证券简称：金利华电</t>
+          <t>证券简称：沈阳机床</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>董事会关于公司本次交易符合《上市公司重大 资产重组 管理办法》第十一条、第四十三条和第四十四条规定的说明</t>
+          <t>浙江大胜达包装股份有限公司关于 购买 资产 及与关联方共同对外投资的进展公告</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
@@ -3562,24 +4867,24 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>资产重组</t>
+          <t>购买资产</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225317243.PDF</t>
+          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225315529.PDF</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>证券简称：金利华电</t>
+          <t>证券简称：大胜达</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>董事会关于本次交易符合《创业板上市公司持续监管办法（试行）》 第十八条、第二十一条以及《深圳证券交易所上市公司重大 资产重组 审核规则》第八条规定的说明</t>
+          <t>董事会关于本次交易前十二个月内上市公司购买、 出售 资产 情况的说明</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
@@ -3599,12 +4904,12 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>资产重组</t>
+          <t>出售资产</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225317242.PDF</t>
+          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225317246.PDF</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -3616,7 +4921,7 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>董事会关于本次交易是否构成重大 资产重组 、关联交易及重组上市的说明</t>
+          <t>本钢板材股份有限公司关于重大 资产 置换 暨关联交易的进展公告</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
@@ -3636,24 +4941,24 @@
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>资产重组</t>
+          <t>资产置换</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225317240.PDF</t>
+          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225317228.PDF</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>证券简称：金利华电</t>
+          <t>证券简称：本钢板材</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>关于延期回复上海证券交易所《关于对永杰新材料股份有限公司重大 资产重组 草案的问询函》的公告</t>
+          <t>关于终止筹划重大 资产重组 并变更为一般股权投资的公告</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
@@ -3678,19 +4983,19 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225315580.PDF</t>
+          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225317889.PDF</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>证券简称：永杰新材</t>
+          <t>证券简称：奕帆传动</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>简式 权益 变动 报告书</t>
+          <t>关于筹划本次重大 资产重组 停牌前一个交易日前十大股东和前十大流通股股东持股情况的公告</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
@@ -3710,24 +5015,24 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>权益变动报告书</t>
+          <t>资产重组</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225317712.PDF</t>
+          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225317251.PDF</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>证券简称：国发股份</t>
+          <t>证券简称：金利华电</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>关于持股5%以上股东逝世、股份完成司法继承过户暨 权益 变动 触及5%刻度并披露简式 权益 变动 报告书 的提示性公告</t>
+          <t>董事会关于本次交易符合《上市公司监管指引第9号——上市公司筹划和实施重大 资产重组 的监管要求》第四条规定的说明</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
@@ -3747,24 +5052,24 @@
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>权益变动报告书</t>
+          <t>资产重组</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225316830.PDF</t>
+          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225317244.PDF</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>证券简称：*st沐邦</t>
+          <t>证券简称：金利华电</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>江西沐邦高科股份有限公司简式 权益 变动 报告书</t>
+          <t>董事会关于公司本次交易符合《上市公司重大 资产重组 管理办法》第十一条、第四十三条和第四十四条规定的说明</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
@@ -3784,24 +5089,24 @@
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>权益变动报告书</t>
+          <t>资产重组</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225316810.PDF</t>
+          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225317243.PDF</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>证券简称：*st沐邦</t>
+          <t>证券简称：金利华电</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>四川汇源光通信股份有限公司简式 权益 变动 报告书</t>
+          <t>董事会关于本次交易符合《创业板上市公司持续监管办法（试行）》 第十八条、第二十一条以及《深圳证券交易所上市公司重大 资产重组 审核规则》第八条规定的说明</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
@@ -3821,29 +5126,29 @@
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>权益变动报告书</t>
+          <t>资产重组</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225315562.PDF</t>
+          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225317242.PDF</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>证券简称：汇源通信</t>
+          <t>证券简称：金利华电</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>关于延期回复上海证券交易所《关于对永杰新材料股份有限公司重大资产 重组 草案 的问询函》的公告</t>
+          <t>董事会关于本次交易是否构成重大 资产重组 、关联交易及重组上市的说明</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 重大资产重组关键词</t>
+          <t>巨潮资讯网 - 全市场公告入口</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
@@ -3858,29 +5163,29 @@
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>重组草案</t>
+          <t>资产重组</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225315580.PDF</t>
+          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225317240.PDF</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>证券简称：永杰新材</t>
+          <t>证券简称：金利华电</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>关于 终止 筹划重大资产 重组 并变更为一般股权投资的公告</t>
+          <t>关于延期回复上海证券交易所《关于对永杰新材料股份有限公司重大 资产重组 草案的问询函》的公告</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 重大资产重组关键词</t>
+          <t>巨潮资讯网 - 全市场公告入口</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -3895,29 +5200,29 @@
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>终止重组</t>
+          <t>资产重组</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225317889.PDF</t>
+          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225315580.PDF</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>证券简称：奕帆传动</t>
+          <t>证券简称：永杰新材</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>关于持股5%以上股东逝世、股份完成司法继承过户暨 权益 变动 触及5%刻度并披露 简式 权益 变动 报告书 的提示性公告</t>
+          <t>简式 权益 变动 报告书</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 权益变动报告书关键词</t>
+          <t>巨潮资讯网 - 全市场公告入口</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
@@ -3932,293 +5237,293 @@
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>简式权益变动报告书</t>
+          <t>权益变动报告书</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225316830.PDF</t>
+          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225317712.PDF</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>证券简称：*st沐邦</t>
+          <t>证券简称：国发股份</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>nextera and dominion announce historic $67 billion merger - evrim ağacı</t>
+          <t>关于持股5%以上股东逝世、股份完成司法继承过户暨 权益 变动 触及5%刻度并披露简式 权益 变动 报告书 的提示性公告</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Google News - Global M&amp;A / evrim ağacı</t>
+          <t>巨潮资讯网 - 全市场公告入口</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T23:46:28+08:00</t>
+          <t>2026-05-20T00:00:00+08:00</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>全球</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>takeover offer acquisition announced</t>
+          <t>权益变动报告书</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPTnJaMVpFTHlZNG1aaHhWalNTV1h1MUlrNy1tY0NoOW11TDFkQVNPVGozaDFSS2NqNFprWkh0WTFPeHdpYkFlaGVRVmR6WnRXY3N4NFJUbW1wbjZJVnVpV09KSmJybUlYejFHRzFxMi1EOUpxQk84NklvcFZjZEVlUEt0M2tFSlFRV1ZhdDRQUGU2NGxY?oc=5</t>
+          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225316830.PDF</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>nextera and dominion announce historic $67 billion merger evrim ağacı</t>
+          <t>证券简称：*st沐邦</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>bank acquisitions, merger announced in five states - aba banking journal</t>
+          <t>江西沐邦高科股份有限公司简式 权益 变动 报告书</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>Google News - Global M&amp;A / aba banking journal</t>
+          <t>巨潮资讯网 - 全市场公告入口</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T23:28:10+08:00</t>
+          <t>2026-05-20T00:00:00+08:00</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>全球</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>M&amp;A acquisition merger deal announced last week</t>
+          <t>权益变动报告书</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPXzBNeXFHREZjTnlZcmpiV0JsMC11S2F6MVBpTnlZamp5WTl3SndKcWlZdzRUMUk2M2xfNk50M1pYVVg1Q0RaQUhhbVZ0Qk9VZmFheUVnSkQ2cDYzcHkwSnZQU3RkVEJBdVJoaFVpVHVWaGV4ZEpLZ0FNVUpfaWtqRWVQMXEwQnY4TGJTM2RCbkxHR1E?oc=5</t>
+          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225316810.PDF</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>bank acquisitions, merger announced in five states aba banking journal</t>
+          <t>证券简称：*st沐邦</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>xpel inc stock (us98422w1036): $110 million manufacturing push from texas to china puts growth strat - ad hoc news</t>
+          <t>四川汇源光通信股份有限公司简式 权益 变动 报告书</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Google News - Global M&amp;A / ad hoc news</t>
+          <t>巨潮资讯网 - 全市场公告入口</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T22:27:37+08:00</t>
+          <t>2026-05-20T00:00:00+08:00</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>全球</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>cross-border acquisition Chinese company announced</t>
+          <t>权益变动报告书</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNS2stbDMySHNCSXgyMEVFTkpPSlUtUUd5OEpRZGxOV0dSakZ3Y2lnTzBjdmItdkdsVjZ1SlByc0pLZ2N3ckxpLXJCbnhweml0MzB0RkRKbXNlQUR6Mk9wdkdPcGVsbnV5TDBoQmRvN0htV2Vra1hoWGI0d2gxbktBY1hMc1pQUTlZVzczQjI4MThyNXFHMk5oWlZycF91ZzJpc0xKSUpCX015NnhQMmx6SnhKVkJUR0VCWnBVSkFBdXFKTmlmOU4w?oc=5</t>
+          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225315562.PDF</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>xpel inc stock (us98422w1036): $110 million manufacturing push from texas to china puts growth strat ad hoc news</t>
+          <t>证券简称：汇源通信</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>the merger and acquisition transactions that are heating up mining in latin america - bnamericas</t>
+          <t>关于延期回复上海证券交易所《关于对永杰新材料股份有限公司重大资产 重组 草案 的问询函》的公告</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>Google News - Global M&amp;A / bnamericas</t>
+          <t>巨潮资讯网 - 重大资产重组关键词</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T22:16:28+08:00</t>
+          <t>2026-05-20T00:00:00+08:00</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>全球</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>global merger acquisition announced company deal</t>
+          <t>重组草案</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOTmhsakNoVEM3dXY2NEQzSkNpYlJZODRXUlVuYU9tb29rS0ZjMjJBaDZENjUzSV81LW8wdFhiMFFpaXRMN3N2dkd5dXl6VzJpZEtEcU15Q1liVzJld24xWGdZdG4wMGNqcWdncmduMnM1R2d5SU9pVlJUVV91R05CVzg4Uk5RM1J3V0JhbGJjMlA3bW5DMTgtVkl1cWpvTGlwYkNfYm9MWWZqdmVGZC0tejVZY2FnaDBPejB4R0RJaw?oc=5</t>
+          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225315580.PDF</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>the merger and acquisition transactions that are heating up mining in latin america bnamericas</t>
+          <t>证券简称：永杰新材</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>srs acquiom welcomes sallie krawcheck and philip vasan to board of directors - business wire</t>
+          <t>关于 终止 筹划重大资产 重组 并变更为一般股权投资的公告</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Google News - Global M&amp;A / business wire</t>
+          <t>巨潮资讯网 - 重大资产重组关键词</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T21:00:00+08:00</t>
+          <t>2026-05-20T00:00:00+08:00</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>全球</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>global merger acquisition announced company deal</t>
+          <t>终止重组</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOdGJtLUtPaFVySnJGWGhQb3NtaXFYY3ExRVpELUhuMjBpWHZnZHA5bmpDTTNkVUtVUDVQUy05eHZUaml3TC1WU1U3OUhVVXdacFhhV1FRTnRWb3N3LVNySTRSTVF3ejA4cHVfLWgtbU9rS2Rmc2YzQ0ZISnN3dlpLOEZUX0ktLTgwVFlrNHR6bnhRYWpyQi1IS0tCdDFVcnJUMW91LUVaSDZyRmpvSkdaTFdsMHFNNzVSNGg3NG8zdVFSQ25rZlByNHBvWllnQQ?oc=5</t>
+          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225317889.PDF</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>srs acquiom welcomes sallie krawcheck and philip vasan to board of directors business wire</t>
+          <t>证券简称：奕帆传动</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>inmed and mentari announce all-stock merger deal (inm:nasdaq) - seeking alpha</t>
+          <t>关于持股5%以上股东逝世、股份完成司法继承过户暨 权益 变动 触及5%刻度并披露 简式 权益 变动 报告书 的提示性公告</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>Google News - Global M&amp;A / seeking alpha</t>
+          <t>巨潮资讯网 - 权益变动报告书关键词</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T20:51:35+08:00</t>
+          <t>2026-05-20T00:00:00+08:00</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>全球</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>M&amp;A acquisition merger deal announced last week</t>
+          <t>简式权益变动报告书</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQWkhBT2x0QktTaFptZVlDejltT1RWZ3lXaDRyemlnSG1jRHhqLS1PZjBtM1ZlbFdPSWdyc2JyUzc5LW1Gb2habmgzVWZoWGVSWFRIbXRrcEh6RWpJVDI4ZXNtNHZuTWhoRDhVcFNlUTBYSzQtNmQxTURnSWV6UWVUN3JpVTlESk8wOGRJYk9KVQ?oc=5</t>
+          <t>https://static.cninfo.com.cn/finalpage/2026-05-20/1225316830.PDF</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>inmed and mentari announce all-stock merger deal (inm:nasdaq) seeking alpha</t>
+          <t>证券简称：*st沐邦</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>how residential real estate consolidated (timeline) - inman real estate news</t>
+          <t>并购重组活力持续释放 产业集中度与协同性提升 - 新浪财经</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Google News - Global M&amp;A / inman real estate news</t>
+          <t>中国新闻广域 - Google News RSS / 新浪财经</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T20:20:57+08:00</t>
+          <t>2026-05-20T00:00:00+08:00</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>全球</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>M&amp;A acquisition merger deal announced last week</t>
+          <t>中国 并购重组 收购 重大资产重组 交易完成</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNaDdmMmVnMDRpVWRWejA2dGUtNFlFbnBaZGZzZHB0SWJqWGw3enlmWWJ5bmJCQndnMzdLUER6ZnNva21MQWlNWTA5NWJ2dzg3TDBmb3BldVpwWUM5dzZkalFOV05reURyYnJ2NzhNLTJiNzYzMm0yS2lQQWJQY19iNHNoSkhqSDBTSUkzWkRuWFVOTDM3RVZCZTBR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTFBrOVVmT0xsblkyMTEwaUUtTVhRZ0NZdHFiQVozc3RVMTd1UDkxRll3blJJMlVUT0FiQmxFcFNSdk13b1VxTExISHFVbTdvZUpzaHY5Z19PSmtpY1l5YS1pQnd3cU5HV0hxdjA2bmxrRQ?oc=5</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>how residential real estate consolidated (timeline) inman real estate news</t>
+          <t>并购重组活力持续释放 产业集中度与协同性提升 新浪财经</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>inmed pharmaceuticals &amp; mentari therapeutics announce merger to advance migraine prevention therapies - pr newswire</t>
+          <t>nextera and dominion announce historic $67 billion merger - evrim ağacı</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>Google News - Global M&amp;A / pr newswire</t>
+          <t>Google News - Global M&amp;A / evrim ağacı</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T20:00:00+08:00</t>
+          <t>2026-05-19T23:46:28+08:00</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
@@ -4233,29 +5538,29 @@
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxNRW16RTEzdXZxU2FSVGRzMC1vSlJMOFFqU3gwcEVTSEt6RWVycElmZElkajVQWlhUa3Fpelp1cGZ0X3dtaDM4Z01LM3JwRHFXak5lVUhRQV9xYTRsMUVoc284eXRuZnhNVzhrN2pRWHpfR1NIRDlWNG9pRjQydkFQNkctbjROaS0tb1IxTXVubVVtMHVmaGVrdFZRTDlCNjgxRUNKU2dNX2NlTjNvZkp0NmZMM1dvOGstTUFuOTFVX3FiSGlHUFFOTTAwcWNXWDJGbDBtVU5VMHoyNV9SYXpSUWVzT055WnpRS2JjSQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPTnJaMVpFTHlZNG1aaHhWalNTV1h1MUlrNy1tY0NoOW11TDFkQVNPVGozaDFSS2NqNFprWkh0WTFPeHdpYkFlaGVRVmR6WnRXY3N4NFJUbW1wbjZJVnVpV09KSmJybUlYejFHRzFxMi1EOUpxQk84NklvcFZjZEVlUEt0M2tFSlFRV1ZhdDRQUGU2NGxY?oc=5</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>inmed pharmaceuticals &amp; mentari therapeutics announce merger to advance migraine prevention therapies pr newswire</t>
+          <t>nextera and dominion announce historic $67 billion merger evrim ağacı</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>white &amp; case: sašo kraner joins new york office to expand global m&amp;a practice - pulse 2.0</t>
+          <t>bank acquisitions, merger announced in five states - aba banking journal</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>Google News - Global M&amp;A / pulse 2.0</t>
+          <t>Google News - Global M&amp;A / aba banking journal</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T19:44:23+08:00</t>
+          <t>2026-05-19T23:28:10+08:00</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
@@ -4265,108 +5570,108 @@
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>global merger acquisition announced company deal</t>
+          <t>M&amp;A acquisition merger deal announced last week</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPbEFJVkJ2aXFfUVRqdXVMbzM2bFlXcUhIcE5Mem1oNTA1YUxpTnRYNTlMaDQ1TGFueU5jVk9zUUkzblBDR0lCNGtrQWNpNHZJcUxqZy1TU2dfVFQ2N1RJaGZIaGVfazZfdkhQWjZhNU1LelhlNlNLRHlXZEIteFFmaGZhMWhlTGl4RVd0d2thTXNzRXktZGxBT9IBngFBVV95cUxPRm5Xd2EyNGYyOWp5bGoxSlBlSjRjOTViN2ZHUTlFTGM4T1JvT2xpZXc1c0pxNTgydy1lX2VaLXp0UnJuRVQwRndabUU0QzhmMy1pdG1ITFgwS245T1lkUFJwNkNPLVFVWFlUZ3FuZGgtVHVsN0tSajBObThNUE9FbnBpay1kV19pbFBvVEQyNHR0d3Z6QzBneTF4Z0xvQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxPXzBNeXFHREZjTnlZcmpiV0JsMC11S2F6MVBpTnlZamp5WTl3SndKcWlZdzRUMUk2M2xfNk50M1pYVVg1Q0RaQUhhbVZ0Qk9VZmFheUVnSkQ2cDYzcHkwSnZQU3RkVEJBdVJoaFVpVHVWaGV4ZEpLZ0FNVUpfaWtqRWVQMXEwQnY4TGJTM2RCbkxHR1E?oc=5</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>white &amp; case: sašo kraner joins new york office to expand global m&amp;a practice pulse 2.0</t>
+          <t>bank acquisitions, merger announced in five states aba banking journal</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>简式 权益 变动 报告书 （受让方）</t>
+          <t>xpel inc stock (us98422w1036): $110 million manufacturing push from texas to china puts growth strat - ad hoc news</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>Google News - Global M&amp;A / ad hoc news</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T19:28:10+08:00</t>
+          <t>2026-05-19T22:27:37+08:00</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>全球</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>权益变动报告书</t>
+          <t>cross-border acquisition Chinese company announced</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225317623.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxNS2stbDMySHNCSXgyMEVFTkpPSlUtUUd5OEpRZGxOV0dSakZ3Y2lnTzBjdmItdkdsVjZ1SlByc0pLZ2N3ckxpLXJCbnhweml0MzB0RkRKbXNlQUR6Mk9wdkdPcGVsbnV5TDBoQmRvN0htV2Vra1hoWGI0d2gxbktBY1hMc1pQUTlZVzczQjI4MThyNXFHMk5oWlZycF91ZzJpc0xKSUpCX015NnhQMmx6SnhKVkJUR0VCWnBVSkFBdXFKTmlmOU4w?oc=5</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>证券简称：方直科技</t>
+          <t>xpel inc stock (us98422w1036): $110 million manufacturing push from texas to china puts growth strat ad hoc news</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>简式 权益 变动 报告书 （转让方及其一致行动人）</t>
+          <t>the merger and acquisition transactions that are heating up mining in latin america - bnamericas</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>Google News - Global M&amp;A / bnamericas</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T19:28:10+08:00</t>
+          <t>2026-05-19T22:16:28+08:00</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>全球</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>权益变动报告书</t>
+          <t>global merger acquisition announced company deal</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225317622.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOTmhsakNoVEM3dXY2NEQzSkNpYlJZODRXUlVuYU9tb29rS0ZjMjJBaDZENjUzSV81LW8wdFhiMFFpaXRMN3N2dkd5dXl6VzJpZEtEcU15Q1liVzJld24xWGdZdG4wMGNqcWdncmduMnM1R2d5SU9pVlJUVV91R05CVzg4Uk5RM1J3V0JhbGJjMlA3bW5DMTgtVkl1cWpvTGlwYkNfYm9MWWZqdmVGZC0tejVZY2FnaDBPejB4R0RJaw?oc=5</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>证券简称：方直科技</t>
+          <t>the merger and acquisition transactions that are heating up mining in latin america bnamericas</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>持股5%以上股东 协议 转让 公司部分股份暨权益变动的提示性公告</t>
+          <t>北京利尔拟斥资9.9亿元收购联创锂能超65%股权；*st仕净因涉嫌信息披露违法违规等，被中国证监会立案｜公告精选 - mrjjxw.com</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>中国新闻广域 - Google News RSS / mrjjxw.com</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T19:28:10+08:00</t>
+          <t>2026-05-19T22:10:00+08:00</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
@@ -4376,34 +5681,34 @@
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>协议转让</t>
+          <t>中国 并购重组 收购 重大资产重组 交易完成</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225317624.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTFAxMWtfNEVKanRJT0E0em12UDdkWjkzbTZ6Znc3b0dxbVIzSzBScm9VTUxqUWRZbFNGRTFhLVc4dDg3RHMyX2F0d1Z2Ri11UFYzbTZLNHZJeUhJRVdndFFwODZYdFRHQQ?oc=5</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>证券简称：方直科技</t>
+          <t>北京利尔拟斥资9.9亿元收购联创锂能超65%股权；*st仕净因涉嫌信息披露违法违规等，被中国证监会立案｜公告精选 mrjjxw.com</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>关于控股股东、实际控制人及其一致行动人 权益 变动 触及1%及5%整数倍暨披露简式 权益 变动 报告书 的提示性公告</t>
+          <t>公告精选 | 超8家集体披露并购公告 东北证券因“4.7操纵期货市场案”被提起公诉 - 搜狐网</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>中国新闻广域 - Google News RSS / 搜狐网</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T19:10:10+08:00</t>
+          <t>2026-05-19T21:37:23+08:00</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
@@ -4413,34 +5718,34 @@
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>权益变动报告书</t>
+          <t>中国 并购重组 收购 重大资产重组 交易完成</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225317486.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxOaERhS3o4MUZ1ME0tU1JsX21uSERHeXYwVGhWUThHTFNCaUEyWURDdUdvNFZhY2pMUlN2dlQwWDlhUmxKUmJSVFpyR1lDaE9YSGZIUHhyWFVYdk1LM2lUb0pXWlBoTEtyVWFxQU9wWjM5QmR6ODFfQnVTV25faF9YLXlveHRQRW9MN0lQak1ESE1ydS1ydjQyZzdlRkF6cXVreUJGWXEwclQ3TjVNQ1dqS1RaSFRwUUt4M3BaMlBhc2d6bW5sckR2ZW8wYnV4b3ZuOU03WkNkc2V0eWM0b0M5MlluUDVlQ2Zuak5N?oc=5</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>证券简称：天阳科技</t>
+          <t>公告精选 | 超8家集体披露并购公告 东北证券因“4.7操纵期货市场案”被提起公诉 搜狐网</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>简式 权益 变动 报告书 （欧阳建平）</t>
+          <t>调整收购方案！奕帆传动终止87.07%股权收购，改为8400万元拿下北京和利时40%股权 - 新浪财经</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>财经媒体/专业资讯 - 中国并购 / 新浪财经</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T19:10:08+08:00</t>
+          <t>2026-05-19T21:27:00+08:00</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
@@ -4450,71 +5755,71 @@
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>权益变动报告书</t>
+          <t>财联社 并购重组 收购</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225317485.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE9kWmZWM09nbThRTEtBT2x5ODhTcGRyMlQ3bHFpcTJ2ZlBxMkM0YVk1RS1xVElraHFaemZFMldCSWNWN3QzRDY1Um13M2NlNHVWY0lpWUtXVlNCQURNOWs3NDk4Tm45a0FGNFlDVUdSRjAzd2ZwVS1Beg?oc=5</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>证券简称：天阳科技</t>
+          <t>调整收购方案！奕帆传动终止87.07%股权收购，改为8400万元拿下北京和利时40%股权 新浪财经</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>evoke extends deadline for bally’s intralot acquisition offer to 8 june - igamingbusiness.com</t>
+          <t>调整收购方案！奕帆传动终止87.07%股权收购，改为8400万元拿下北京和利时40%股权 - 证券时报</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>Google News - Global M&amp;A / igamingbusiness.com</t>
+          <t>财经媒体/专业资讯 - 中国并购 / 证券时报</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T18:49:49+08:00</t>
+          <t>2026-05-19T21:22:00+08:00</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>全球</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>takeover offer acquisition announced</t>
+          <t>证券时报 并购重组 收购 重大资产重组</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOZFhIbWhGdTRkSHV6cTRuLUs0c2hjV20zZ0VGNGFvbWxhODNWSm9CZTV5dEpIVi1hRU5LZUFjUUVxeWpIeDRlTW9CRkVFa2I0TW5pYXBybVNsM2tET2N0LTdaTGlJdG1va3FLa2NxTW5ldlNfTUVXYUhvT0ttVE1HTC1BbXp0RzB5N0RlSlloVmdhb1ZjamRESF9NdE1Udw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE1Fekk3eXNDUWZKUjgwLXFyVkZLOGZNRVB5bFRmcnhCcl8yNjJYOXpfdlR3b3ZVM2doN3VvS09qaW9WZ21sb0V4VTVoSmlwY19fZFpnZWxKcWtUalB4?oc=5</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>evoke extends deadline for bally’s intralot acquisition offer to 8 june igamingbusiness.com</t>
+          <t>调整收购方案！奕帆传动终止87.07%股权收购，改为8400万元拿下北京和利时40%股权 证券时报</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>简式 权益 变动 报告书</t>
+          <t>【超短实盘】5/19 尾盘伏击t+1 策略笔记 - 财富号</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>财经媒体/专业资讯 - 中国并购 / 财富号</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T18:42:11+08:00</t>
+          <t>2026-05-19T21:09:00+08:00</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
@@ -4524,108 +5829,108 @@
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>权益变动报告书</t>
+          <t>东方财富 并购重组 收购</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225316987.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxOR1dXZjFBZ3lLTFVnNllwU1RqeWFZQUtOaDd6UnJxVTUzTk5EaEQ2bmVWWVhsY3Zhc1d5MlplN2RyZUljaVcxbm5Ob0wxQ192R3UzS2REdlo2NG42djEyYmhUdTVJeTZGYzU5RGN3cklXNmI3UG83cDFLNzlzUVllRS1DLWVRSXRUdVlDUUQ0N3F5MEtoVC1EaGR4MVVvNjZGbENWYUVHNTdLbkozZ1RWVmZsTzJiOGRjQzd6aFFOTmVHOXBGOHdRVlc0REVNMFV4Zk9rUUZ4WUhqM2ZtajgzYnRMZDJsSWFkcnZIZ21QZGVMUkFsT19adk1B?oc=5</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>证券简称：海昌新材</t>
+          <t>【超短实盘】5/19 尾盘伏击t+1 策略笔记 财富号</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>关于股东询价转让结果 报告书 暨控股股东、实际控制人及一致行动人股东 权益 变动 触及5%整数倍的提示性公告</t>
+          <t>srs acquiom welcomes sallie krawcheck and philip vasan to board of directors - business wire</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>Google News - Global M&amp;A / business wire</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T18:42:10+08:00</t>
+          <t>2026-05-19T21:00:00+08:00</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>全球</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>权益变动报告书</t>
+          <t>global merger acquisition announced company deal</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225316989.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOdGJtLUtPaFVySnJGWGhQb3NtaXFYY3ExRVpELUhuMjBpWHZnZHA5bmpDTTNkVUtVUDVQUy05eHZUaml3TC1WU1U3OUhVVXdacFhhV1FRTnRWb3N3LVNySTRSTVF3ejA4cHVfLWgtbU9rS2Rmc2YzQ0ZISnN3dlpLOEZUX0ktLTgwVFlrNHR6bnhRYWpyQi1IS0tCdDFVcnJUMW91LUVaSDZyRmpvSkdaTFdsMHFNNzVSNGg3NG8zdVFSQ25rZlByNHBvWllnQQ?oc=5</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>证券简称：海昌新材</t>
+          <t>srs acquiom welcomes sallie krawcheck and philip vasan to board of directors business wire</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>简式 权益 变动 报告书 （任俊江）</t>
+          <t>inmed and mentari announce all-stock merger deal (inm:nasdaq) - seeking alpha</t>
         </is>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>Google News - Global M&amp;A / seeking alpha</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T18:14:10+08:00</t>
+          <t>2026-05-19T20:51:35+08:00</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>全球</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>权益变动报告书</t>
+          <t>M&amp;A acquisition merger deal announced last week</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225316091.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQWkhBT2x0QktTaFptZVlDejltT1RWZ3lXaDRyemlnSG1jRHhqLS1PZjBtM1ZlbFdPSWdyc2JyUzc5LW1Gb2habmgzVWZoWGVSWFRIbXRrcEh6RWpJVDI4ZXNtNHZuTWhoRDhVcFNlUTBYSzQtNmQxTURnSWV6UWVUN3JpVTlESk8wOGRJYk9KVQ?oc=5</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>证券简称：电连技术</t>
+          <t>inmed and mentari announce all-stock merger deal (inm:nasdaq) seeking alpha</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>关于董事会完成换届选举及聘任高级管理人员、证券事务代表暨公司 控制权 变更 的公告</t>
+          <t>300069重大资产重组，明日复牌！北向资金大幅净买入股出炉 - 证券时报</t>
         </is>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>财经媒体/专业资讯 - 中国并购 / 证券时报</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T18:12:10+08:00</t>
+          <t>2026-05-19T20:38:00+08:00</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
@@ -4635,34 +5940,34 @@
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>控制权变更</t>
+          <t>证券时报 并购重组 收购 重大资产重组</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225316027.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE5mUDNNOURMbzJsamZFOHlPdkE1U3hKZW1hdFY4SkcwM3lZbVduTmhGd1JuWHVyVzh6UkFXR2N5NUZyYjYwdVY2TEllcktuOUxzU3JZU0IzenVWTGpS?oc=5</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>证券简称：易事特</t>
+          <t>300069重大资产重组，明日复牌！北向资金大幅净买入股出炉 证券时报</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>苏州华兴源创科技股份有限公司关于“华兴转债”赎回结果暨股份变动的公告 - 上海证券交易所科创板</t>
+          <t>腾讯音乐：完成收购喜马拉雅 - 新浪财经</t>
         </is>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>上交所上市公司公告 - 重大资产重组 / 上海证券交易所科创板</t>
+          <t>中国新闻广域 - Google News RSS / 新浪财经</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T18:12:08+08:00</t>
+          <t>2026-05-19T20:29:01+08:00</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
@@ -4672,34 +5977,34 @@
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>site:sse.com.cn/disclosure/listedinfo/announcement 购买资产</t>
+          <t>中国 (并购 OR 收购 OR 合并 OR 股权转让 OR 交易完成)</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOaml0V1g5QkFqM2ZhMlhlcFNQb2JDcEdGaGZxaUxjbUgwZXlVNWlJcHlmNXhDd05RVU90TmY0bTdKc0NtLWh0RTRGdkZUMXFmRUFHTDc3bF9Zc2g4TUd0NkxNOVA2MXdHUkJiLW1NRVZrT2o4YjFncS1QV2Y2VE1IclZwRGRJUF84Mm40ZXlBbTBlOEl6WUY1dURIZkRNRDFHQkE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTE1HVFVCNDBFUHlITURsczAzd2ZxdXNfbWNhX1JDaS01VnE1Sy1oYVpxQWwzWVIxTnlLS1Uwb2FoSUtmVktDdHhVNG5hSlhEbE00ZUhwci0wSnd1RGt6SEhub2p6LWZQSVB1Xzdic0FzRQ?oc=5</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>苏州华兴源创科技股份有限公司关于“华兴转债”赎回结果暨股份变动的公告 上海证券交易所科创板</t>
+          <t>腾讯音乐：完成收购喜马拉雅 新浪财经</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>lvpai group limited 2025 annual report: business overview, risks, and regulatory challenges for china-based holding companies - minichart</t>
+          <t>how residential real estate consolidated (timeline) - inman real estate news</t>
         </is>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>Google News - Global M&amp;A / minichart</t>
+          <t>Google News - Global M&amp;A / inman real estate news</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T16:42:00+08:00</t>
+          <t>2026-05-19T20:20:57+08:00</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
@@ -4709,71 +6014,71 @@
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>China company acquires overseas asset merger acquisition</t>
+          <t>M&amp;A acquisition merger deal announced last week</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxNVG1iVkRucXd2dzJrek13TlNKbjdJb1l6aXozTEgyTnlsMHBFSXZKUnhiQmdxOXpLTzFsSEZQcEVCNUhZc0tVNERucWlSdjdWR0tTc1pCblZweDNIR2J3bEUzWGk3WXJwUXlLWG1Pdjh3WWdVOTBtZVYxWVRYYXl4TEQyNUlDRUpGNzVMZzFlU1owLS1iMzhJcktJdGFuaURNck1VYjRJTERMU1VxdkZ4aDJub0FuV0JiS0RqNTUwVUJuVTlad1B4d1Nkcm9XYUxNMGNxUDJqaHZ2aE91bHFHZlpfSFU4aDhxbTNmMkdpNGdoYmhHVnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNaDdmMmVnMDRpVWRWejA2dGUtNFlFbnBaZGZzZHB0SWJqWGw3enlmWWJ5bmJCQndnMzdLUER6ZnNva21MQWlNWTA5NWJ2dzg3TDBmb3BldVpwWUM5dzZkalFOV05reURyYnJ2NzhNLTJiNzYzMm0yS2lQQWJQY19iNHNoSkhqSDBTSUkzWkRuWFVOTDM3RVZCZTBR?oc=5</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>lvpai group limited 2025 annual report: business overview, risks, and regulatory challenges for china-based holding companies minichart</t>
+          <t>how residential real estate consolidated (timeline) inman real estate news</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>关于乌兰察布ppp项目提前 终止 及债务 重组 的公告</t>
+          <t>inmed pharmaceuticals &amp; mentari therapeutics announce merger to advance migraine prevention therapies - pr newswire</t>
         </is>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 重大资产重组关键词</t>
+          <t>Google News - Global M&amp;A / pr newswire</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T16:26:10+08:00</t>
+          <t>2026-05-19T20:00:00+08:00</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>全球</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>终止重组</t>
+          <t>takeover offer acquisition announced</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225315496.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxNRW16RTEzdXZxU2FSVGRzMC1vSlJMOFFqU3gwcEVTSEt6RWVycElmZElkajVQWlhUa3Fpelp1cGZ0X3dtaDM4Z01LM3JwRHFXak5lVUhRQV9xYTRsMUVoc284eXRuZnhNVzhrN2pRWHpfR1NIRDlWNG9pRjQydkFQNkctbjROaS0tb1IxTXVubVVtMHVmaGVrdFZRTDlCNjgxRUNKU2dNX2NlTjNvZkp0NmZMM1dvOGstTUFuOTFVX3FiSGlHUFFOTTAwcWNXWDJGbDBtVU5VMHoyNV9SYXpSUWVzT055WnpRS2JjSQ?oc=5</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>证券简称：蒙草生态</t>
+          <t>inmed pharmaceuticals &amp; mentari therapeutics announce merger to advance migraine prevention therapies pr newswire</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>new $11b gold deal tests asx loophole before door slams shut - afr</t>
+          <t>white &amp; case: sašo kraner joins new york office to expand global m&amp;a practice - pulse 2.0</t>
         </is>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>Google News - Global M&amp;A / afr</t>
+          <t>Google News - Global M&amp;A / pulse 2.0</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T16:05:00+08:00</t>
+          <t>2026-05-19T19:44:23+08:00</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
@@ -4783,330 +6088,330 @@
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>M&amp;A acquisition merger deal announced last week</t>
+          <t>global merger acquisition announced company deal</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxObzREZzhNY2lMaVY0eVJFV0ZrTmx4c0x2WVlCUlRYeGtYZUtBZ2o2MXN1XzlnRkM1eDJtd1dYcUVPX1otOG5wWkNXME11bE5VWTBNNVBZLTVtYkZWQnBGbEhJM19IY0pSNXg1YVRKcWpGVXZTYVk5QURZd29aZEkxdjZNaExrS25Rc0NfdURpOFAwV3Fwa3poN29OS2tac250ZzFPXzA0QWw1OXM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPbEFJVkJ2aXFfUVRqdXVMbzM2bFlXcUhIcE5Mem1oNTA1YUxpTnRYNTlMaDQ1TGFueU5jVk9zUUkzblBDR0lCNGtrQWNpNHZJcUxqZy1TU2dfVFQ2N1RJaGZIaGVfazZfdkhQWjZhNU1LelhlNlNLRHlXZEIteFFmaGZhMWhlTGl4RVd0d2thTXNzRXktZGxBT9IBngFBVV95cUxPRm5Xd2EyNGYyOWp5bGoxSlBlSjRjOTViN2ZHUTlFTGM4T1JvT2xpZXc1c0pxNTgydy1lX2VaLXp0UnJuRVQwRndabUU0QzhmMy1pdG1ITFgwS245T1lkUFJwNkNPLVFVWFlUZ3FuZGgtVHVsN0tSajBObThNUE9FbnBpay1kV19pbFBvVEQyNHR0d3Z6QzBneTF4Z0xvQQ?oc=5</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>new $11b gold deal tests asx loophole before door slams shut afr</t>
+          <t>white &amp; case: sašo kraner joins new york office to expand global m&amp;a practice pulse 2.0</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>dominion surges, nextera falls after $67b utility merger deal - msn</t>
+          <t>金利华电重大资产重组！公司股票明日复牌 - 证券时报</t>
         </is>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>Google News - Global M&amp;A / msn</t>
+          <t>财经媒体/专业资讯 - 中国并购 / 证券时报</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T15:23:43+08:00</t>
+          <t>2026-05-19T19:29:00+08:00</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>全球</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>takeover offer acquisition announced</t>
+          <t>证券时报 并购重组 收购 重大资产重组</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxNTzdSejRFTXp3MzJwaWRxdHVqX1hkTF8ySlY0WmtRWEcyZm42ckVPbWQtLWNVN2ZVaEtMZEs5LU9GZDFZSk9yZGQ1Q0NNOUk2T0FIcVVVZXBOM3JVaEsxMG9wcE9fa3RhTTVNUFQ2Z2M2WEVJLW1TUzI2ejVlRWhURUJlMExPb3l0Rm52cWRpdHRMTWpfN1hFQmlIODZ3R1FDRzExOVBWSFJranhCcV91eTNzdUM5REhuYWV3UF9BeDl1X3pvekJCX3FqY3pxdWdzMEk2N1MzUEh0QzhzVXhoTlJ5WQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE9zWTRBU0taOW40ZnNHSEZJTmpwM0hxYWFXMU5OOENTczFVVlp6Yi0wU1lVSzhfUExYR1VBVlZEekFSdTEtY3ZsdXBPTGo5NUNIQ2NvclFidThtN21M?oc=5</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>dominion surges, nextera falls after $67b utility merger deal msn</t>
+          <t>金利华电重大资产重组！公司股票明日复牌 证券时报</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>equinox gold and orla mining merger: creating an $18.5b producer - discovery alert</t>
+          <t>简式 权益 变动 报告书 （受让方）</t>
         </is>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>Google News - Global M&amp;A / discovery alert</t>
+          <t>巨潮资讯网 - 全市场公告入口</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T14:59:34+08:00</t>
+          <t>2026-05-19T19:28:10+08:00</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>全球</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>M&amp;A acquisition merger deal announced last week</t>
+          <t>权益变动报告书</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPVkFxX2hpQkNNMmlJWEI3MElJWUtJTERVZTZjdk5NVVExcnIwcGRnU3NJUG90Qll4ajlWbjlFLXMtM2xoenUxTEtLYUhBbTBySHpQTXdMMUFwbGZWUnZSS0dBRm5aRkpNTThpTGk4NXpHa0pWZDE0alBvSmhLM0MybXhwUlI0bmI5VEtSejBMTGhFazBM?oc=5</t>
+          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225317623.PDF</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>equinox gold and orla mining merger: creating an $18.5b producer discovery alert</t>
+          <t>证券简称：方直科技</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>nextera, dominion announce merger to create u.s. power behemoth - axios</t>
+          <t>简式 权益 变动 报告书 （转让方及其一致行动人）</t>
         </is>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>Google News - Global M&amp;A / axios</t>
+          <t>巨潮资讯网 - 全市场公告入口</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T12:36:11+08:00</t>
+          <t>2026-05-19T19:28:10+08:00</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>全球</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>global merger acquisition announced company deal</t>
+          <t>权益变动报告书</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFAxblNXdTJxRDRxSXZYM21FdUdfVVhHOHdNUkVDWlZDd3NMOFRqNEZZMVpZVm9WWUwtTWpab3AwX1RoMkxfamxhdFp5SW50anFKWWJad1FEVG5VVEg4OG5EX1hZcVNHMHY2cHBtR1ZMcEU0T2RSZ3hFNW1jT1YtdFk?oc=5</t>
+          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225317622.PDF</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>nextera, dominion announce merger to create u.s. power behemoth axios</t>
+          <t>证券简称：方直科技</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>breakingviews - china's outbound m&amp;a spree has staying power - reuters</t>
+          <t>持股5%以上股东 协议 转让 公司部分股份暨权益变动的提示性公告</t>
         </is>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>Google News - Global M&amp;A / reuters</t>
+          <t>巨潮资讯网 - 全市场公告入口</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T11:39:00+08:00</t>
+          <t>2026-05-19T19:28:10+08:00</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>全球</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>China company acquires overseas asset merger acquisition</t>
+          <t>协议转让</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNV2pEck9zNmRzNzdvTDMwUE5lODgxQlFIaVZVTHFIY1NrYnFlOHdKOFZnS2puM0hzRUJySTNzQXJER0h2U3ZpT0JOVUVLNUJIbktYSGJSNmROZ09UYzFaU1RycS15Rm13ajdYZnFoY3VpT2txRlBaUmlMYW5YX0JkcG5EX0lQbWVhTEpHRV9qU05Rc2V6Q2JobnQ4NWdxRUtYeGprSXBB?oc=5</t>
+          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225317624.PDF</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>breakingviews - china's outbound m&amp;a spree has staying power reuters</t>
+          <t>证券简称：方直科技</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>the next phase of china’s beauty expansion - arc group</t>
+          <t>跌停！百亿并购告吹！这家老牌房企国资首考“不及格” - 新浪财经</t>
         </is>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>Google News - Global M&amp;A / arc group</t>
+          <t>财经媒体/专业资讯 - 中国并购 / 新浪财经</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T10:58:37+08:00</t>
+          <t>2026-05-19T19:22:00+08:00</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>全球</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>cross-border acquisition Chinese company announced</t>
+          <t>第一财经 并购 收购 重组</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiYkFVX3lxTE81WEU3TnNfUzhKWmpyUU5BZlJKUmJZVHNuVmduejV4bGFVdm9ldXFsVnlrZnRIRmlNc1RHRERlalZPZDByanZ1LXREdTJFRDQzLUxDNmJmdFN3aFpITElXV1h3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTFBGRkFUZVZTMHh5czl0ZnpxU3V0ZGVPZ01WZHhiaDEtUmd3MHlUQ1ZtRmVYZFhOdzR2czhHQW9zaTlDd1ROOGR0UkVORHIzck9VYmJ1eXlCeDlYVzExUHFfV0RfLTZ5TURPaktTVnE5cExWek41?oc=5</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>the next phase of china’s beauty expansion arc group</t>
+          <t>跌停！百亿并购告吹！这家老牌房企国资首考“不及格” 新浪财经</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>featuring, a global sns data analysis company, announced on the 19th that it has attracted 15.3 bill.. - 매일경제</t>
+          <t>关于控股股东、实际控制人及其一致行动人 权益 变动 触及1%及5%整数倍暨披露简式 权益 变动 报告书 的提示性公告</t>
         </is>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>Google News - Global M&amp;A / 매일경제</t>
+          <t>巨潮资讯网 - 全市场公告入口</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T09:38:42+08:00</t>
+          <t>2026-05-19T19:10:10+08:00</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>全球</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>cross-border acquisition Chinese company announced</t>
+          <t>权益变动报告书</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiS0FVX3lxTE5MTTF4c1lHLW5pUzFfUUZzZVRGWTBZc0VhbW96RnUtZldrcUdNV2R4X2Rsa3ZWT1FCR3BnU2VqRm1SNDBtWDZQQzlPUQ?oc=5</t>
+          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225317486.PDF</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>featuring, a global sns data analysis company, announced on the 19th that it has attracted 15.3 bill.. 매일경제</t>
+          <t>证券简称：天阳科技</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>south carolina customers included in dominion, nextera merger proposal - wach.com</t>
+          <t>简式 权益 变动 报告书 （欧阳建平）</t>
         </is>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>Google News - Global M&amp;A / wach.com</t>
+          <t>巨潮资讯网 - 全市场公告入口</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T06:38:58+08:00</t>
+          <t>2026-05-19T19:10:08+08:00</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>全球</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>takeover offer acquisition announced</t>
+          <t>权益变动报告书</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQVUp4TXJzeDFiUXJZZGRnN3Frem5LVGI1R1RLSUNwNEdXb2Ruc1k1dHZ0MGFYVEdQUkR5ZEhnWVd5aVNUbURxX0JYVVU0bGJWMEF2WnMyMFJ0STYzSGpIQS1hOU5OTFg2YlBnWk0xUXgxQ25kanRleEpoZk9NUlZ5Z1FOR3pvN0ZIT3Y2eTZBZUdJUy1wYWRZTTFma3ZlOHdGYU9Ua3d0c01nZ3pV?oc=5</t>
+          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225317485.PDF</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>south carolina customers included in dominion, nextera merger proposal wach.com</t>
+          <t>证券简称：天阳科技</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>why you should care about 2 power companies merging. hint: affordability - npr</t>
+          <t>聚焦硬科技企业收并购，张江实战沙龙构建对接枢纽 - 新浪财经</t>
         </is>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>Google News - Global M&amp;A / npr</t>
+          <t>中国新闻广域 - Google News RSS / 新浪财经</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T06:00:12+08:00</t>
+          <t>2026-05-19T18:53:00+08:00</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>全球</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>takeover offer acquisition announced</t>
+          <t>产业整合 并购 收购 中国</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQV2NOekpiWDItV2pLWERWY3RHY0ZremVibVdlNENvTURadmZ4cGlzU2VmcTRobDBxaG0xOUVkU0VrMXFaZ1NmT0Y1N2RWZzBNWUFGYnFIRUpsd3NZY2UtY0FNUG9WS0xmT0gxQ240NjFxQjVaRzhMUTlFdTkzaGR2Ty15SnlpYVZFeHJDOVJKeG45aGtEYmVEVmwtVGpEQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTE9Md19YMGh6cVFDS1BKbE1WMDRzUkplWkxsM1BKVUJ0ZEE1WjhDc2oxZ256WkRFMWt3dU9DZmU1Ym5ubkFwSWMwUHNFOE5ZQVBXa0MtNHYtX0pKTHhjemExcFc0RWFyY0FPMkVuU1NmTGR0MGsx?oc=5</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>why you should care about 2 power companies merging. hint: affordability npr</t>
+          <t>聚焦硬科技企业收并购，张江实战沙龙构建对接枢纽 新浪财经</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>swamped by data center demands, dominion energy just opted for a megamerger - the washington post</t>
+          <t>evoke extends deadline for bally’s intralot acquisition offer to 8 june - igamingbusiness.com</t>
         </is>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>Google News - Global M&amp;A / the washington post</t>
+          <t>Google News - Global M&amp;A / igamingbusiness.com</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T05:36:35+08:00</t>
+          <t>2026-05-19T18:49:49+08:00</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
@@ -5121,436 +6426,436 @@
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOMVZHY1I4blV2ZjJMcTFqOXBvUU5ua2pjVnJOQ00yc3ZQQTZSOUE2RG5vd1pST1NZbVdOTm9YNWQ3aDhLaFRKMkQ3aWxwUDlYT1NxMW9wMDhNMVpKRG5oTzlwbWw4dGFXbnhITnc3M1prU1E1RzdMSTNZOVI1UDQwUlFtOHpPTXNxUjNQMlpPd1QyTkJHN0NKRHJuM0JMTFNYc0VJeHRLaXZnZVpEczJ5aUxGMmNucXh3SExRUXJndW5OaDJ6aFJKdGhjLWhvUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxOZFhIbWhGdTRkSHV6cTRuLUs0c2hjV20zZ0VGNGFvbWxhODNWSm9CZTV5dEpIVi1hRU5LZUFjUUVxeWpIeDRlTW9CRkVFa2I0TW5pYXBybVNsM2tET2N0LTdaTGlJdG1va3FLa2NxTW5ldlNfTUVXYUhvT0ttVE1HTC1BbXp0RzB5N0RlSlloVmdhb1ZjamRESF9NdE1Udw?oc=5</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
-          <t>swamped by data center demands, dominion energy just opted for a megamerger the washington post</t>
+          <t>evoke extends deadline for bally’s intralot acquisition offer to 8 june igamingbusiness.com</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>what nextera and dominion’s giant utility merger means for your electric bill - marketwatch</t>
+          <t>腾讯音乐完成对喜马拉雅的收购 - or新媒体</t>
         </is>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>Google News - Global M&amp;A / marketwatch</t>
+          <t>中国新闻广域 - Google News RSS / or新媒体</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T05:12:00+08:00</t>
+          <t>2026-05-19T18:43:00+08:00</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>全球</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>takeover offer acquisition announced</t>
+          <t>中国 (并购 OR 收购 OR 合并 OR 股权转让 OR 交易完成)</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOQ29nc1prWUd1VFJTRGRlMC1ubGw2cTBiR0pmNEU4VS1JRGlnRDJVNmtPdk9zbjIwTkVXMS15OHdjU2dOWk1MNGdqQW15NnZGLWtvWHFLMTZVRFpDSnpERGJPN3hSckZGeG9meHdyQXZZZkx3cFZqOHhaWXZ2aHVtMUplQjNqOERkSFEtM0U0ZW1aQzFNSmdyR3EzSkoyYnBlbk9SMGFvUklKWXVzTkN6Mnd4eWN0RTJNdWZV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiREFVX3lxTE1ndUszdWpobHpXTE9VUnZ0YmtGUFV3VkZEVWRIUjNPZWp0SW5MU0lJX3lOWW1fLXVWX0dWeUFEMWNLX2Vt?oc=5</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>what nextera and dominion’s giant utility merger means for your electric bill marketwatch</t>
+          <t>腾讯音乐完成对喜马拉雅的收购 or新媒体</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>your portfolio &amp; the nextera dominion merger - etf database</t>
+          <t>简式 权益 变动 报告书</t>
         </is>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>Google News - Global M&amp;A / etf database</t>
+          <t>巨潮资讯网 - 全市场公告入口</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T05:07:50+08:00</t>
+          <t>2026-05-19T18:42:11+08:00</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>全球</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>takeover offer acquisition announced</t>
+          <t>权益变动报告书</t>
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPRDFaaDRvX2VJUEpaYVpwTWp0dW1nWGtFNnUyV2NzRlJMVGVXOTk3NE40aFVyN1FEMlFrVE9VTjR6ZkdpclVFTGFTVFpvX29VRnNBWkQ5Y3FzS3c3RkZtem9INnZ2MFVDRGFrb2tIN2VfSzlyb2JJdmd0YW16QV81dEhKeW41dmZKUm16TFAtMThqOWF3?oc=5</t>
+          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225316987.PDF</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>your portfolio &amp; the nextera dominion merger etf database</t>
+          <t>证券简称：海昌新材</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>iron horse (irho) files s-4; amends merger agreement with electra (may 2026) - stock titan</t>
+          <t>关于股东询价转让结果 报告书 暨控股股东、实际控制人及一致行动人股东 权益 变动 触及5%整数倍的提示性公告</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>Google News - Global M&amp;A / stock titan</t>
+          <t>巨潮资讯网 - 全市场公告入口</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T04:32:44+08:00</t>
+          <t>2026-05-19T18:42:10+08:00</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>全球</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
         <is>
-          <t>M&amp;A acquisition merger deal announced last week</t>
+          <t>权益变动报告书</t>
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPMXJZNmd2UU5Vdl9QTmM0elI5VEt4RUp6aXZBRWJ3QlBZeDB3bDE4MF94UDNGUTlWMy1yQllTV2l4U2s3VlZ0OEhWTnNFV1pFaFJIMUhCcVZVcGxqZFQwcW5pOXFOVzk5dTlCaklOR1I5REZFeEZWa1dRUjlwT0ZYdEVHYS1tNXNXVGdkS09xdnVOLUxYVDdSM2RjY2V4UmtfNldyc19fQTdDbGJlaTlwYURlY1NYUHQyeVU0MTNZYmlSZzhpYk9CQ1pvSQ?oc=5</t>
+          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225316989.PDF</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>iron horse (irho) files s-4; amends merger agreement with electra (may 2026) stock titan</t>
+          <t>证券简称：海昌新材</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>electra ai and iron horse (nasdaq: irho) advance $250m spac merger plan - stock titan</t>
+          <t>一字跌停！“纸尿裤材料大王”延江股份跨界半导体告败，高盛重仓超500万股遭遇滑铁卢 - 新浪财经</t>
         </is>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>Google News - Global M&amp;A / stock titan</t>
+          <t>财经媒体/专业资讯 - 中国并购 / 新浪财经</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T04:31:32+08:00</t>
+          <t>2026-05-19T18:37:09+08:00</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>全球</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>SPAC merger announced acquisition</t>
+          <t>第一财经 并购 收购 重组</t>
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQUkFXWjVUUHhKeGdJbG1aaThKeWpNb0NnZE5CNjhvYnpET241TFpFUE05Qmp5Z3RHbnBiZmhPSEY0RFE3ZXZ1bmF6WUlUOEZ0V0xKZEFWV0UzWEpjXzZPdXNuM0UxT2d0Vjd0aFR2WjlNdDZWNE81VkZBbGtvNGctRzYzaVhpaVRUeFZsY3ZHdGVxZXQ4NjZXaHZTOHJsVFFpcGJ1bVgtNnBTV0NqTF9PWnVPOXY3dll4cUVj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTFBFT3VLamRIbDRSQUlqSHRISGxia2V6Zk80WmszQWNjcGI0RkJRQ3lCRDdqamNPMV9HMHRNWDRuZFF3WlljR3FnTFJfMk5fYVNlZkVtMkxPUG1rNkFFY2tvT3BxNEM1ekRNZDdCaWFFdw?oc=5</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
-          <t>electra ai and iron horse (nasdaq: irho) advance $250m spac merger plan stock titan</t>
+          <t>一字跌停！“纸尿裤材料大王”延江股份跨界半导体告败，高盛重仓超500万股遭遇滑铁卢 新浪财经</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>rb global (nyse: rba) closes bigiron deal to expand u.s. agriculture - stock titan</t>
+          <t>一字跌停！“纸尿裤材料大王”延江股份跨界半导体告败，高盛重仓超500万股遭遇滑铁卢 - 新浪财经</t>
         </is>
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>Google News - Global M&amp;A / stock titan</t>
+          <t>财经媒体/专业资讯 - 中国并购 / 新浪财经</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T04:30:28+08:00</t>
+          <t>2026-05-19T18:37:00+08:00</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>全球</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>global merger acquisition announced company deal</t>
+          <t>中国证券报 并购重组 收购</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOLXBvYkZJM1pRYUpJNm1JT1UxVlJtcnZObUtVbTN5NHpkZzVWZE9GMEF2ZFQ2WG51bTVVd1ZVZFNMaEJpZW1HM1JFMFJOSy00QUtHamdXdTBxNll6WTNoM3ladEdBcFF4VUpTcWxwNFBObXRnblgzX2lCN0NWWVdDSEVzY0Z3LW9BbGV5VDhXNHBUeXhNZ0x0UTg2d3U0Ym9SRWdv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTE8xNEtYWWZWTU1hRU0zT01sNHQ2WjVZaTVSZVhBaTN3RGlRS2JvOUFXUFlKWkJWRFQ5N2FWcDBvUjdsTVEzMWxhTzZIREZ4MWhjdUw4YzFpdnBEdHBxbTVBSWdIeV9TSmJ4WGMxUU9TOUJxRXp2MXJidA?oc=5</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>rb global (nyse: rba) closes bigiron deal to expand u.s. agriculture stock titan</t>
+          <t>一字跌停！“纸尿裤材料大王”延江股份跨界半导体告败，高盛重仓超500万股遭遇滑铁卢 新浪财经</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>nextera's $67 billion dominion takeover creates world's largest utility—just in time to win the ai data center power surge - fortune</t>
+          <t>好丽友发布一季度合并基准业绩，中国市场表现亮眼 - 中华网</t>
         </is>
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>Google News - Global M&amp;A / fortune</t>
+          <t>中国新闻广域 - Google News RSS / 中华网</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T04:29:00+08:00</t>
+          <t>2026-05-19T18:17:35+08:00</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>全球</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>takeover offer acquisition announced</t>
+          <t>中国 (并购 OR 收购 OR 合并 OR 股权转让 OR 交易完成)</t>
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQTlBuZGtXdXpRbzE5Vm53LWI2X0JXMkphVnVCTklWejVZdDg4eGtmaEI0eXM5RWJIa3RhZ2JVLVFxZXdpVGJYN2hfRW5PUWJOcUdrd05LQkNZVUoxa2xiS0d5M1p2VndaSVJvSmZyWjY5aG5VcDY0dnFnWVpCbXhWT3hVSzJLcFozQTQ0ajFRcUxPbU9VejdTb0dvNEpRRWlfRW5fNVRB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE5FOV9NeDJ2ME9DM1k1WnFMdGtKbXVRYzFOTzRlTUFneWlfb1VOazIzTHdPUGxUX0M4WjRSVndmVUwxcFRqRVJ5OWxpX2p6bUstM3VqLW5PbzBTV1RKMnV6dlFEVVJrV2hVMzJaVg?oc=5</t>
         </is>
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
-          <t>nextera's $67 billion dominion takeover creates world's largest utility—just in time to win the ai data center power surge fortune</t>
+          <t>好丽友发布一季度合并基准业绩，中国市场表现亮眼 中华网</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>deal watch: kirkland, mcguirewoods guide $67b energy deal - law.com</t>
+          <t>中国工商银行行长刘珺：国内外并购“三条路径”投资于物、投资于生态、投资于人 - 新浪财经</t>
         </is>
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>Google News - Global M&amp;A / law.com</t>
+          <t>中国新闻广域 - Google News RSS / 新浪财经</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T03:51:00+08:00</t>
+          <t>2026-05-19T18:17:32+08:00</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>全球</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>M&amp;A acquisition merger deal announced last week</t>
+          <t>中国 (并购 OR 收购 OR 合并 OR 股权转让 OR 交易完成)</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNOUU4b05mLWtUMGtKUWYyRGVnMktSMnE1RXVJeUhHX2FTYTBnQlQ4SEJFYXlSZ2YzalVFLTVSc0E3NFVaSjNpcWlwREF3dHpBZHU4enc5YWpvak9DbEs1WTZPdGc2TmowZGdLaEZhNTRvaTRwMzBDQmNwX3RVZmIyNThrR2RDdnA0WlJDVEZheTI1M0EwUWcydkpXeXNEQ2xiel9n?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwJBVV95cUxNQjJ5TnNSXzdiaGRkNkc2THhEREhqTXJmc3NwTlJJajBNd18tODVaWnYtOVdELWxnWTRNeUd2aWlTNDg5bEFvX3FUSFdUdmxBYnowUVFLSkNUWUpReC1IdlFfQmxud3RXOXJzb1U0YzZqSU5CUGc2X01zY0ZHMVFXclFmV0hrMzdoMTZvWWY3d3U5Wlh5Q1BlMERNU0l0cDJkMXJNQUdfLWt0VlRYbTkxa2lFeGh4R1lucG1VT2tFbndwNElVbHFLRmJrV1psZU11akFlUjlKWjQ2RVVwOWo3R3R0aHpyRDhPa2tHRVRFMUIyYmtRenlxc3Z1NkVJTk0yaklQUXdQcEpFMFc1MGE1dUcxQQ?oc=5</t>
         </is>
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>deal watch: kirkland, mcguirewoods guide $67b energy deal law.com</t>
+          <t>中国工商银行行长刘珺：国内外并购“三条路径”投资于物、投资于生态、投资于人 新浪财经</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>nigerian oil firms hunt growth beyond home market - marketing edge</t>
+          <t>简式 权益 变动 报告书 （任俊江）</t>
         </is>
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>Google News - Global M&amp;A / marketing edge</t>
+          <t>巨潮资讯网 - 全市场公告入口</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T03:41:21+08:00</t>
+          <t>2026-05-19T18:14:10+08:00</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>全球</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>cross-border acquisition Chinese company announced</t>
+          <t>权益变动报告书</t>
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxQeE82azU3c1pKQWl2Q1BJYlBGdmhSanI4bVdTR1h6dDY4bDgxNk5ZRzRWNjZJdm5UYTNPNE5URnVoMFZYaWk2TUNUdGhpb2pDeFRVQUFuNUZuY0FobTZwdzhIZ3NEaWpEOVBLOUNmVTR6cWFXa1VCckNFMmtzRDN6blRjYUNnUQ?oc=5</t>
+          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225316091.PDF</t>
         </is>
       </c>
       <c r="G92" s="5" t="inlineStr">
         <is>
-          <t>nigerian oil firms hunt growth beyond home market marketing edge</t>
+          <t>证券简称：电连技术</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>merger - dominion energy</t>
+          <t>关于董事会完成换届选举及聘任高级管理人员、证券事务代表暨公司 控制权 变更 的公告</t>
         </is>
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>Google News - Global M&amp;A / dominion energy</t>
+          <t>巨潮资讯网 - 全市场公告入口</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T03:38:02+08:00</t>
+          <t>2026-05-19T18:12:10+08:00</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>全球</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>takeover offer acquisition announced</t>
+          <t>控制权变更</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE40bFFBanVER3Q0WWw0N3ZLZHhQWW1TTlluYXJDb1NuUVl6c3BkUkZfNXpPbUxuZ0F0cjdkZUNESzhOMmRabG1mZ3VLbFYtZTRHNEVZckFudU1taUU?oc=5</t>
+          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225316027.PDF</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>merger dominion energy</t>
+          <t>证券简称：易事特</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>brodsky &amp; smith investigates fiduciary duty bre... | pluang – crypto, stocks, gold &amp; funds - pluang</t>
+          <t>苏州华兴源创科技股份有限公司关于“华兴转债”赎回结果暨股份变动的公告 - 上海证券交易所科创板</t>
         </is>
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>Google News - Global M&amp;A / pluang</t>
+          <t>上交所上市公司公告 - 重大资产重组 / 上海证券交易所科创板</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T03:32:46+08:00</t>
+          <t>2026-05-19T18:12:08+08:00</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>全球</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>global merger acquisition announced company deal</t>
+          <t>site:sse.com.cn/disclosure/listedinfo/announcement 购买资产</t>
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOS2J1elcxRWZfRHJ4V2JSLVAwR1drUG1qZnRLb2RuNl9jaTlHenlzYjdrNmdOTkktY2JsV3Q4Vl83elhLQ3dzTk1Ta0VuYU5NbC10UlVwRFdnR3JzbnZmQmJhdGVzX0RBX0ZTbE5aejVhS0I0TEtnX3hxS1RzQm10eWtoODhWU0l3XzN2bll1Qk56YkFuc1ozYVlBMVdMRU9oQmFtc2xtbl8?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxOaml0V1g5QkFqM2ZhMlhlcFNQb2JDcEdGaGZxaUxjbUgwZXlVNWlJcHlmNXhDd05RVU90TmY0bTdKc0NtLWh0RTRGdkZUMXFmRUFHTDc3bF9Zc2g4TUd0NkxNOVA2MXdHUkJiLW1NRVZrT2o4YjFncS1QV2Y2VE1IclZwRGRJUF84Mm40ZXlBbTBlOEl6WUY1dURIZkRNRDFHQkE?oc=5</t>
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>brodsky &amp; smith investigates fiduciary duty bre... | pluang – crypto, stocks, gold &amp; funds pluang</t>
+          <t>苏州华兴源创科技股份有限公司关于“华兴转债”赎回结果暨股份变动的公告 上海证券交易所科创板</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>nextera energy, dominion energy announce all-stock merger to create world's largest regulated utility - corridor business journal</t>
+          <t>电源管理芯片涨价潮蔓延，晶圆代工封测成本倒逼调价 - 电子工程专辑</t>
         </is>
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>Google News - Global M&amp;A / corridor business journal</t>
+          <t>中国新闻广域 - Google News RSS / 电子工程专辑</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T03:14:31+08:00</t>
+          <t>2026-05-19T17:07:42+08:00</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>全球</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
         <is>
-          <t>takeover offer acquisition announced</t>
+          <t>产业整合 并购 收购 中国</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNdzA2c3FES2diZFZXNllBWGxBMGc4dnh6QTFaNnFuRVlySklsaWJ5YVRFRzBUQjBPdXVzWFRiWmd6UGx2YzRPUk81eWw0QmIzMnhyYVdoV1NPMmNIZDNTdEo5SHp6djlXVVhDRy1OSlBRQUVXclNZR25HdE5Yb0lnQ3NVN0F6WURFbnhieUxIOU5JSUlyTGY2YlRCVVY5X0xWbGY0WG1qWHpBNUhMU2dPbjZaTWxOUjZ3SGxRYlhuLTFvVU5KUnlrLQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE9qOU5wYzBIRUZBRDN0dVZLazV1UGVpWTFQNHdhbC1NN214UEhJMjYya19IWmhXQjdXa0l4eU1iR05qMmo2YXpwYU1fanVvcHltbzR1S2N0WFg3Tmdv?oc=5</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>nextera energy, dominion energy announce all-stock merger to create world's largest regulated utility corridor business journal</t>
+          <t>电源管理芯片涨价潮蔓延，晶圆代工封测成本倒逼调价 电子工程专辑</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>neurocrine biosciences: $2.9 billion soleno therapeutics acquisition expands rare disease portfolio - pulse 2.0</t>
+          <t>lvpai group limited 2025 annual report: business overview, risks, and regulatory challenges for china-based holding companies - minichart</t>
         </is>
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>Google News - Global M&amp;A / pulse 2.0</t>
+          <t>Google News - Global M&amp;A / minichart</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T01:14:29+08:00</t>
+          <t>2026-05-19T16:42:00+08:00</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
@@ -5560,145 +6865,145 @@
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>takeover offer acquisition announced</t>
+          <t>China company acquires overseas asset merger acquisition</t>
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNNl9HQkJxcDZCN3lTLWVnZVpaWUFmM2MyUWtJaFZyNFpNa1RZcVlRWnBNM0w5VWpUM0pzMHFDT2pvNHM0Z0VkWkJuV3ZhMHZrZlY0bmtyTXdUYkszVjFINzZ6RXAwOE1CYjZ2czFLOVVJLWVac3FyQ1pIR0hvWldNUExEYVJ5NHFjSmg0VXh2RjRwTHluVFRUNllWQUVIalJKYWhmRmwxV0dRRFFUQjBoTVVYSy1xc2pG0gG-AUFVX3lxTE55V3VTck9tMUZFVUctSEVKVWlJUUtOUF9ycHdiVU1icDdDVzNGOWlGT3JzbzNPdU5yTGlRWDVwZGkzRktiUDFDcm0xcUo2YUNFNkF5ejRlejdkT3QwVVVTWHBVdVlJM1dJUGRtRUl3dzVaenduMDM0dVpSWTY3Q1RyOXNmRG8zdWxBTzNUU1I5R05vS2pCaHRjWUYwcEExOFZNalJaREUzVHpPckY4aS1JeWZjenJlYUJyRFduMVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxNVG1iVkRucXd2dzJrek13TlNKbjdJb1l6aXozTEgyTnlsMHBFSXZKUnhiQmdxOXpLTzFsSEZQcEVCNUhZc0tVNERucWlSdjdWR0tTc1pCblZweDNIR2J3bEUzWGk3WXJwUXlLWG1Pdjh3WWdVOTBtZVYxWVRYYXl4TEQyNUlDRUpGNzVMZzFlU1owLS1iMzhJcktJdGFuaURNck1VYjRJTERMU1VxdkZ4aDJub0FuV0JiS0RqNTUwVUJuVTlad1B4d1Nkcm9XYUxNMGNxUDJqaHZ2aE91bHFHZlpfSFU4aDhxbTNmMkdpNGdoYmhHVnc?oc=5</t>
         </is>
       </c>
       <c r="G96" s="5" t="inlineStr">
         <is>
-          <t>neurocrine biosciences: $2.9 billion soleno therapeutics acquisition expands rare disease portfolio pulse 2.0</t>
+          <t>lvpai group limited 2025 annual report: business overview, risks, and regulatory challenges for china-based holding companies minichart</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>dominion energy stock surges on a deal with nextera to make the world's biggest utility - business insider</t>
+          <t>关于乌兰察布ppp项目提前 终止 及债务 重组 的公告</t>
         </is>
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>Google News - Global M&amp;A / business insider</t>
+          <t>巨潮资讯网 - 重大资产重组关键词</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:49:00+08:00</t>
+          <t>2026-05-19T16:26:10+08:00</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>全球</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
         <is>
-          <t>takeover offer acquisition announced</t>
+          <t>终止重组</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQSjRxTWhSYTdNR3BNYVJuNUdWSmNzNVFvMUE4MkZsXzBabnRoN290LXkySlVVWTcyUHVUUnZDbW1zWldFakhQWWg1WWJBZ0tydExlaXZJSmN2M1d2bVlhRlk4VEVtbzl3clp4bS1JWGVXejMydlRmTEhyMDJiRGVoaWhUSjk1TnNNOEdRZFZicnJOZm5NWGIwRXZXZWpLZmlkTTJMbGpUTHI5Y2c?oc=5</t>
+          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225315496.PDF</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>dominion energy stock surges on a deal with nextera to make the world's biggest utility business insider</t>
+          <t>证券简称：蒙草生态</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>nextera to buy dominion in $67bn deal creating us utility giant - the guardian</t>
+          <t>周报丨国内一级市场投资、退出、并购事件共253起，涉及金额337.21亿元 - 新浪财经</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>Google News - Global M&amp;A / the guardian</t>
+          <t>财经媒体/专业资讯 - 中国并购 / 新浪财经</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:31:00+08:00</t>
+          <t>2026-05-19T16:15:28+08:00</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>全球</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>global merger acquisition announced company deal</t>
+          <t>清科 并购 市场 报告</t>
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNZkJfaDgwZ1I4dU1NZDgwbGk5Zk01Xzh6SWRDQnMxQUdlZF9ZdUZ4Qkk4LThodmRnSkw0aHMwQ1B0YW90LUM1eTl3Rzk3dnpfSXZIRUZ0aUxEVlZfRGhXTlg1ZGFBRUZyWnlhQzVjdzdPRUdSUTBEVG5KSjJPb2JjeWhDdWtHUWFRMmc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwJBVV95cUxPN1VBM1NCYTZRMXp2RFBfRWpwVU1mek1xNUtWdUdWci1jdlRpRUpwZEd1Z1d2UTBzSUN6TnFwSk80Y3Zad2tVOVY0VUxMT0hNNTQ1WGRTdk1HSlVWYURYbzFEQUpPdjJxY2paeGctSTdfd2hzQW1udndYS243VWVuc3Y4MVNqRnUtUWVEblN3YmJOWnUtMGNxdTVfb2ZmRjFOM1dKQWRzc0l2MGl3QmlYSE91LXhWWTl4TXk5dzdaZ1g4UjFzVzR3cHZNRmtWRkY5aXpkNUwyWUlvWkVUeUJlODNrR09vTF9kQ0NRRE1ySzFOcjZPUGFHNWlYVGduR3J4QVFXcm9Zck5EN1FUSFhVNG43amdnMzA?oc=5</t>
         </is>
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>nextera to buy dominion in $67bn deal creating us utility giant the guardian</t>
+          <t>周报丨国内一级市场投资、退出、并购事件共253起，涉及金额337.21亿元 新浪财经</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>dominion energy stock soars on $67 billion deal to be acquired by nextera - investopedia</t>
+          <t>工行北京分行以专业金融服务助力首都上市公司高质量发展 - 投资界</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>Google News - Global M&amp;A / investopedia</t>
+          <t>中国新闻广域 - Google News RSS / 投资界</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:25:20+08:00</t>
+          <t>2026-05-19T16:14:00+08:00</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>全球</t>
+          <t>中国</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
         <is>
-          <t>M&amp;A acquisition merger deal announced last week</t>
+          <t>产业整合 并购 收购 中国</t>
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPVG1rdWdjam0yMDk3Slk4azFPVWVORGw0TzZJd3p6RE5hM0hCZ3hDUTlvcFNTNHlwZzA0ZVM0bDV1WEl6d251amN0QXFUZlJ4dldYbzYzWDVUNm1KZnJBQmJVZkF1ZWtuSHpGYUtNT3NtQ1VBSzBzMjdVcC1rMHBoQnQ4OURnWEFZdy1PaWtuSThucDUxMFRVTXZuZVZ1MkxiNXdoUXBDZlNGZDlqZnBPTEpYVGpzdmVUbWpV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE9TS1IxQ25PYUxOS0s1dWg4bF90ZW9fMjFYQVZxVXIzOEw1aU5nUnNWUFpMZF9pd3RxODE4Sld6MFNCeE0tWEEzdU83VHZkdHJaaWRHQTV3?oc=5</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>dominion energy stock soars on $67 billion deal to be acquired by nextera investopedia</t>
+          <t>工行北京分行以专业金融服务助力首都上市公司高质量发展 投资界</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>dominion, nextera announce merger plan - cardinal news</t>
+          <t>new $11b gold deal tests asx loophole before door slams shut - afr</t>
         </is>
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>Google News - Global M&amp;A / cardinal news</t>
+          <t>Google News - Global M&amp;A / afr</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:15:49+08:00</t>
+          <t>2026-05-19T16:05:00+08:00</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
@@ -5708,34 +7013,34 @@
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>takeover offer acquisition announced</t>
+          <t>M&amp;A acquisition merger deal announced last week</t>
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxOZUlEU1hVVWV5QkVvSV83UmJVdG5wWUJEelhwNVE4VWZ5dXFLTF9KYzVBWlBfQXRBOUNTNTJfT3A1alU4WDhLVzFsWTdWcnhfX3lnYzJfaHNzRVVfZ0dPemlHdDQ4X1dlMjJueGpJVmZ4dktOU1JveC1SNkxBbUVJNQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxObzREZzhNY2lMaVY0eVJFV0ZrTmx4c0x2WVlCUlRYeGtYZUtBZ2o2MXN1XzlnRkM1eDJtd1dYcUVPX1otOG5wWkNXME11bE5VWTBNNVBZLTVtYkZWQnBGbEhJM19IY0pSNXg1YVRKcWpGVXZTYVk5QURZd29aZEkxdjZNaExrS25Rc0NfdURpOFAwV3Fwa3poN29OS2tac250ZzFPXzA0QWw1OXM?oc=5</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
-          <t>dominion, nextera announce merger plan cardinal news</t>
+          <t>new $11b gold deal tests asx loophole before door slams shut afr</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>信达证券董事会关于本次交易符合《上市公司 重大 资产重组 管理办法》第十一条规定的说明</t>
+          <t>中国车企瞄准欧洲工厂收购以规避关税 - moomoo</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>中国新闻广域 - Google News RSS / moomoo</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T15:58:03+08:00</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
@@ -5745,34 +7050,34 @@
       </c>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>重大资产重组</t>
+          <t>中国 (并购 OR 收购 OR 合并 OR 股权转让 OR 交易完成)</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225314643.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBkTVVrX1BHWDRmbmdtXzJmbi1iY0VPVmUzUHJZRHhTQURTMUxFTy0ySjJHNmpmWDc1alZUTnN4WUVlOU1EMmZNcmNjdTRKNThDUVBQRUNDYVRCdw?oc=5</t>
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>证券简称：信达证券</t>
+          <t>中国车企瞄准欧洲工厂收购以规避关税 moomoo</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>信达证券董事会关于本次交易符合《上市公司监管指引第9号——上市公司筹划和实施 重大 资产重组 的监管要求》第四条规定的说明</t>
+          <t>收购谈崩！5倍牛股延江股份20cm跌停，股价曾提前大涨，高盛重仓528万股 - 新浪财经</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>财经媒体/专业资讯 - 中国并购 / 新浪财经</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T15:57:00+08:00</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
@@ -5782,34 +7087,34 @@
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>重大资产重组</t>
+          <t>中国证券报 并购重组 收购</t>
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225314608.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxQM1R3ZTlIZW9aeUE1Z2wtZkI2YkNZOVFod0RXY3E0YjFlU2d4Mm41V1dpc18tQ0cxQTZ1djllZEdIX3d0eWtuRW1IdjdKTk1Tc1JmS094UVpUMzVPa0ZoVE0zd1haeXhhakNrenFhR245UlZfU1J6SlFpRHVxRk5JZDJBQ1g?oc=5</t>
         </is>
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
-          <t>证券简称：信达证券</t>
+          <t>收购谈崩！5倍牛股延江股份20cm跌停，股价曾提前大涨，高盛重仓528万股 新浪财经</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>中银国际证券股份有限公司关于本次交易相关主体不存在不得参与任何上市公司 重大 资产重组 情形的核查意见</t>
+          <t>收购谈崩！5倍牛股20cm跌停，股价曾提前大涨，高盛重仓528万股 - 新浪财经</t>
         </is>
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>中国新闻广域 - Google News RSS / 新浪财经</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T15:49:36+08:00</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
@@ -5819,34 +7124,34 @@
       </c>
       <c r="E103" s="5" t="inlineStr">
         <is>
-          <t>重大资产重组</t>
+          <t>中国 并购重组 收购 重大资产重组 交易完成</t>
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225314605.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMixwJBVV95cUxNdXo0VV9Zc2k4a3FHVm5lbms5NThCUm83eE5ZLTNkU1dyTk5Zd2phY2ZOV3ctNS1SczVSY1F6aVF1SENjbG5NX2FOaGF6VGZxSVk5bFdRMHhiTmVVUmJiRVpKZ2FyeVd5SXZOT2hPcFpNZlNzVFF3SWh2YWUyd09NQVp1dGZrNUY5WHBRYkFLUXpVU0tqMVd0cjEyTmVnb2NWUGx2bXNEbUpNdFFqaVJhWE5jS1NrT2JNY0ZMM2hWaE1GOFlUX1ZCZGFZVGJ6ZHZCZG9xWTc4ZG1fOXptaTM3QzYwcm5EZ21IWUJrTV9takJzLWdGSFEzWUR5ZmdtZVVrWG9ORk5ycFZzNGVISmEzNE81VXpGMzNLd0NjZjBiRzhTTG50dXpjU09Scnh2UkdtR1dhOVpIdFdqUk9qcWJ2cUVNZ0pkdm8?oc=5</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>证券简称：信达证券</t>
+          <t>收购谈崩！5倍牛股20cm跌停，股价曾提前大涨，高盛重仓528万股 新浪财经</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>信达证券董事会关于本次交易构成《上市公司 重大 资产重组 管理办法》第十二条规定的 重大 资产重组 但不构成第十三条规定的重组上市情形的说明</t>
+          <t>收购guess后，authentic任命中国大陆市场核心授权商 - cn.concall.com</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>中国新闻广域 - Google News RSS / cn.concall.com</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T15:38:00+08:00</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
@@ -5856,71 +7161,71 @@
       </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>重大资产重组</t>
+          <t>中国 (并购 OR 收购 OR 合并 OR 股权转让 OR 交易完成)</t>
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225314597.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMiY0FVX3lxTFBoNkExNVFhUFhZYVZpbUpBQ0d1M1prZFlXTFE2N3ZqUVM0OGU1M2R6czJJbTBKVm1nVGJDbllPblFVWGRISmRhdTN4eHpLU3VNU2hRVEZvcnpBcWtoRVdjNUpBWQ?oc=5</t>
         </is>
       </c>
       <c r="G104" s="5" t="inlineStr">
         <is>
-          <t>证券简称：信达证券</t>
+          <t>收购guess后，authentic任命中国大陆市场核心授权商 cn.concall.com</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>信达证券董事会关于本次交易相关主体不存在《上市公司监管指引第7号——上市公司 重大 资产重组 相关股票异常交易监管》第十二条及《上海证券交易所上市公司自律监管指引第6号—— 重大 资产重组 》第三十条情形的说明</t>
+          <t>dominion surges, nextera falls after $67b utility merger deal - msn</t>
         </is>
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>Google News - Global M&amp;A / msn</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T15:23:43+08:00</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>全球</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
         <is>
-          <t>重大资产重组</t>
+          <t>takeover offer acquisition announced</t>
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225314593.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxNTzdSejRFTXp3MzJwaWRxdHVqX1hkTF8ySlY0WmtRWEcyZm42ckVPbWQtLWNVN2ZVaEtMZEs5LU9GZDFZSk9yZGQ1Q0NNOUk2T0FIcVVVZXBOM3JVaEsxMG9wcE9fa3RhTTVNUFQ2Z2M2WEVJLW1TUzI2ejVlRWhURUJlMExPb3l0Rm52cWRpdHRMTWpfN1hFQmlIODZ3R1FDRzExOVBWSFJranhCcV91eTNzdUM5REhuYWV3UF9BeDl1X3pvekJCX3FqY3pxdWdzMEk2N1MzUEh0QzhzVXhoTlJ5WQ?oc=5</t>
         </is>
       </c>
       <c r="G105" s="5" t="inlineStr">
         <is>
-          <t>证券简称：信达证券</t>
+          <t>dominion surges, nextera falls after $67b utility merger deal msn</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>信达证券股份有限公司关于披露 重大 资产重组 报告书的一般风险提示公告</t>
+          <t>【投资视角】启示2026：中国算力行业投融资及兼并重组分析（附投融资事件、产业基金和兼并重组等） - 前瞻网</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>中国新闻广域 - Google News RSS / 前瞻网</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T15:09:00+08:00</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
@@ -5930,71 +7235,71 @@
       </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>重大资产重组</t>
+          <t>产业整合 并购 收购 中国</t>
         </is>
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225314586.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE9OY3RhZGo5MXZpN2ZvblZiU3NkREdsOGZPVldqdXdGYnFqZWhQX20wYzgwbWllVThLVFZGRFZBQVZiZWFGSWYwZjhMSktkRHpSdEppUXRTbnRsa002UUhHTHI4UXc3bHlpdkxTYjJObWRkUQ?oc=5</t>
         </is>
       </c>
       <c r="G106" s="5" t="inlineStr">
         <is>
-          <t>证券简称：信达证券</t>
+          <t>【投资视角】启示2026：中国算力行业投融资及兼并重组分析（附投融资事件、产业基金和兼并重组等） 前瞻网</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>东兴证券董事会关于本次交易相关主体不存在《上市公司监管指引第7号——上市公司 重大 资产重组 相关股票异常交易监管》第十二条及《上海证券交易所上市公司自律监管指引第6号—— 重大 资产重组 》第三十条情形的说明</t>
+          <t>equinox gold and orla mining merger: creating an $18.5b producer - discovery alert</t>
         </is>
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>Google News - Global M&amp;A / discovery alert</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T14:59:34+08:00</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>全球</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
         <is>
-          <t>重大资产重组</t>
+          <t>M&amp;A acquisition merger deal announced last week</t>
         </is>
       </c>
       <c r="F107" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225314256.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPVkFxX2hpQkNNMmlJWEI3MElJWUtJTERVZTZjdk5NVVExcnIwcGRnU3NJUG90Qll4ajlWbjlFLXMtM2xoenUxTEtLYUhBbTBySHpQTXdMMUFwbGZWUnZSS0dBRm5aRkpNTThpTGk4NXpHa0pWZDE0alBvSmhLM0MybXhwUlI0bmI5VEtSejBMTGhFazBM?oc=5</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>证券简称：东兴证券</t>
+          <t>equinox gold and orla mining merger: creating an $18.5b producer discovery alert</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>国投证券股份有限公司关于本次交易相关主体不存在不得参与任何上市公司 重大 资产重组 情形的核查意见</t>
+          <t>收购谈崩！5倍牛股20cm跌停，股价曾提前大涨，高盛重仓528万股 - 新浪财经</t>
         </is>
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>财经媒体/专业资讯 - 中国并购 / 新浪财经</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T13:58:00+08:00</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
@@ -6004,34 +7309,34 @@
       </c>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>重大资产重组</t>
+          <t>每日经济新闻 并购重组 收购</t>
         </is>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225314234.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTFBzakJCZmRLV3RHRUZKVnFmaEprU18tajFZcWUyVEFOTkkwZG1ZOVRYU0c2WkJsd01vWHc3Ul9GX2NNMGZ5clVFaVFGcWw2VlB4cXBUeDFHWE1USWs2N0lmMXhjd2dqeUp3TUprNU1wQXM5RmFtRHc?oc=5</t>
         </is>
       </c>
       <c r="G108" s="5" t="inlineStr">
         <is>
-          <t>证券简称：东兴证券</t>
+          <t>收购谈崩！5倍牛股20cm跌停，股价曾提前大涨，高盛重仓528万股 新浪财经</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>东兴证券董事会关于本次交易符合《上市公司监管指引第9号——上市公司筹划和实施 重大 资产重组 的监管要求》第四条规定的说明</t>
+          <t>跨界“造芯”折戟！“纸尿裤大王”20cm跌停 延江股份回应 - 东方财富</t>
         </is>
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>财经媒体/专业资讯 - 中国并购 / 东方财富</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T13:14:33+08:00</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
@@ -6041,34 +7346,34 @@
       </c>
       <c r="E109" s="5" t="inlineStr">
         <is>
-          <t>重大资产重组</t>
+          <t>东方财富 并购重组 收购</t>
         </is>
       </c>
       <c r="F109" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225314225.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTE5IbURWUGRiTWloQ2o1WlE3ZHlueWZNa2hQODdaZnluYXJyRHlEOUtVdVRzVU9CZDF6dHF5aFFmWmJCVkhtZURsa1dKNGMwT3JxOUhJWTBlOHZfYy0yUGpLRw?oc=5</t>
         </is>
       </c>
       <c r="G109" s="5" t="inlineStr">
         <is>
-          <t>证券简称：东兴证券</t>
+          <t>跨界“造芯”折戟！“纸尿裤大王”20cm跌停 延江股份回应 东方财富</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>东兴证券董事会关于本次交易构成《上市公司 重大 资产重组 管理办法》第十二条规定的 重大 资产重组 但不构成第十三条规定的重组上市情形的说明</t>
+          <t>2000亿市值巨头出手，拟收购对象一度跌超30% - 搜狐网</t>
         </is>
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>中国新闻广域 - Google News RSS / 搜狐网</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T13:01:54+08:00</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
@@ -6078,71 +7383,71 @@
       </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>重大资产重组</t>
+          <t>产业整合 并购 收购 中国</t>
         </is>
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225314222.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxNaVRXR3dwbUV1c3YybTNlMFZVc1JDTE8xMi02Zm53WndxeGtJR0dhVFR2clZWRGhCSDZkZ2gtY2RQTzVaMEJEZm9wejB5RnlvWkNMRVYyazd1anI4dnpBZVNOSThWNm5mYzdsZ2g0MGpoaVpPNEdCZThXdnlmS1R6Y1hxbVNYbDBwdEwyeg?oc=5</t>
         </is>
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>证券简称：东兴证券</t>
+          <t>2000亿市值巨头出手，拟收购对象一度跌超30% 搜狐网</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>东兴证券董事会关于本次交易符合《上市公司 重大 资产重组 管理办法》第十一条规定的说明</t>
+          <t>nextera, dominion announce merger to create u.s. power behemoth - axios</t>
         </is>
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>Google News - Global M&amp;A / axios</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T12:36:11+08:00</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>全球</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
         <is>
-          <t>重大资产重组</t>
+          <t>global merger acquisition announced company deal</t>
         </is>
       </c>
       <c r="F111" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225314214.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFAxblNXdTJxRDRxSXZYM21FdUdfVVhHOHdNUkVDWlZDd3NMOFRqNEZZMVpZVm9WWUwtTWpab3AwX1RoMkxfamxhdFp5SW50anFKWWJad1FEVG5VVEg4OG5EX1hZcVNHMHY2cHBtR1ZMcEU0T2RSZ3hFNW1jT1YtdFk?oc=5</t>
         </is>
       </c>
       <c r="G111" s="5" t="inlineStr">
         <is>
-          <t>证券简称：东兴证券</t>
+          <t>nextera, dominion announce merger to create u.s. power behemoth axios</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>东兴证券股份有限公司关于披露 重大 资产重组 报告书的一般风险提示公告</t>
+          <t>中芯国际(00981) - 最新资讯 - 雪球</t>
         </is>
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>财经媒体/专业资讯 - 中国并购 / 雪球</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T12:28:42+08:00</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
@@ -6152,34 +7457,34 @@
       </c>
       <c r="E112" s="5" t="inlineStr">
         <is>
-          <t>重大资产重组</t>
+          <t>格隆汇 并购重组 收购</t>
         </is>
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225314207.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMiRkFVX3lxTE0wT1lTb1I1VjRyeWYxYWYtZElRVjZFTjhsWnZ3dngxZTNqOFc5aEtodFYwLUwyQWRfNWFIaDdZTXRjTEdfRVE?oc=5</t>
         </is>
       </c>
       <c r="G112" s="5" t="inlineStr">
         <is>
-          <t>证券简称：东兴证券</t>
+          <t>中芯国际(00981) - 最新资讯 雪球</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>中金公司董事会关于本次交易构成《上市公司 重大 资产重组 管理办法》第十二条规定的 重大 资产重组 但不构成第十三条规定的重组上市情形的说明</t>
+          <t>雪峰科技(603227):新疆雪峰科技（集团）股份有限公司详式权益变动报告书 - 中财网</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>中国新闻广域 - Google News RSS / 中财网</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T12:20:41+08:00</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
@@ -6189,34 +7494,34 @@
       </c>
       <c r="E113" s="5" t="inlineStr">
         <is>
-          <t>重大资产重组</t>
+          <t>A股 并购重组 收购报告书 权益变动</t>
         </is>
       </c>
       <c r="F113" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225314014.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE5wTmUwSkEwZTIxU1lSY0l2VXdEOW04dUFlTGJsOExWNngydVNTY1JyZGJQMUd3b3Y3c0hjZjNaOHFDdUNSaFFwZVRKYWV3LThGc2VtZHdn?oc=5</t>
         </is>
       </c>
       <c r="G113" s="5" t="inlineStr">
         <is>
-          <t>证券简称：中金公司</t>
+          <t>雪峰科技(603227):新疆雪峰科技（集团）股份有限公司详式权益变动报告书 中财网</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>中金公司董事会关于本次交易符合《上市公司监管指引第9号——上市公司筹划和实施 重大 资产重组 的监管要求》第四条规定的说明</t>
+          <t>“纸尿裤材料大王”跨界梦碎！延江股份终止收购半导体材料商，高盛重仓逾500万股 - 新浪财经</t>
         </is>
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>财经媒体/专业资讯 - 中国并购 / 新浪财经</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T11:56:14+08:00</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
@@ -6226,71 +7531,71 @@
       </c>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>重大资产重组</t>
+          <t>每日经济新闻 并购重组 收购</t>
         </is>
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225314009.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxNaDlLMEF1clFQcC1scENieHFzTFkzdVRjUzBNc25la2lsNGwzeGNMNzliX2VuZzNHZTdoYUJXbEJLSDNqeVhjZ0pjQ0plaDUwTmpaRlZqSDhiOWd1cWxhdUZQRXdyeWVMUnJMV29ObjFTbjVzT2tDbVQ4dUVtNVNXVDlKbVhjeWpwLTVfQXFJSWQ2N1ZXMHZydQ?oc=5</t>
         </is>
       </c>
       <c r="G114" s="5" t="inlineStr">
         <is>
-          <t>证券简称：中金公司</t>
+          <t>“纸尿裤材料大王”跨界梦碎！延江股份终止收购半导体材料商，高盛重仓逾500万股 新浪财经</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>中金公司关于披露 重大 资产重组 报告书的一般风险提示公告</t>
+          <t>breakingviews - china's outbound m&amp;a spree has staying power - reuters</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>Google News - Global M&amp;A / reuters</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T11:39:00+08:00</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>全球</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
         <is>
-          <t>重大资产重组</t>
+          <t>China company acquires overseas asset merger acquisition</t>
         </is>
       </c>
       <c r="F115" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225313999.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNV2pEck9zNmRzNzdvTDMwUE5lODgxQlFIaVZVTHFIY1NrYnFlOHdKOFZnS2puM0hzRUJySTNzQXJER0h2U3ZpT0JOVUVLNUJIbktYSGJSNmROZ09UYzFaU1RycS15Rm13ajdYZnFoY3VpT2txRlBaUmlMYW5YX0JkcG5EX0lQbWVhTEpHRV9qU05Rc2V6Q2JobnQ4NWdxRUtYeGprSXBB?oc=5</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
-          <t>证券简称：中金公司</t>
+          <t>breakingviews - china's outbound m&amp;a spree has staying power reuters</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>中金公司董事会关于本次交易符合《上市公司 重大 资产重组 管理办法》第十一条、第四十三条和第四十四条规定的说明</t>
+          <t>a股异动丨终止重大资产重组，延江股份20cm跌停 - 新浪财经</t>
         </is>
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>财经媒体/专业资讯 - 中国并购 / 新浪财经</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T11:36:00+08:00</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
@@ -6300,34 +7605,34 @@
       </c>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>重大资产重组</t>
+          <t>格隆汇 并购重组 收购</t>
         </is>
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225313994.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxPSlNJalJBMmZHZTNkMnNiUlVybjRtaUpuM3Fvby1TUEVnZWxVV0tyRkhiVkpaTTJhY0gyTklzRTFNeW11ZER5SXhKemZFS3haUExkX1J2UnFTeGsyYWxmLXNRUExGV2dMajVVLVBUd2FRZVM0Mnk1VkZjd3dNc2pKSg?oc=5</t>
         </is>
       </c>
       <c r="G116" s="5" t="inlineStr">
         <is>
-          <t>证券简称：中金公司</t>
+          <t>a股异动丨终止重大资产重组，延江股份20cm跌停 新浪财经</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>中金公司董事会关于本次交易相关主体不存在《上市公司监管指引第7号——上市公司 重大 资产重组 相关股票异常交易监管》第十二条及《上海证券交易所上市公司自律监管指引第6号—— 重大 资产重组 》第三十条情形的说明</t>
+          <t>300658，终止重大资产重组 - 新浪财经</t>
         </is>
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>中国新闻广域 - Google News RSS / 新浪财经</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T11:08:53+08:00</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
@@ -6337,71 +7642,71 @@
       </c>
       <c r="E117" s="5" t="inlineStr">
         <is>
-          <t>重大资产重组</t>
+          <t>中国 并购重组 收购 重大资产重组 交易完成</t>
         </is>
       </c>
       <c r="F117" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225313988.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMi2AJBVV95cUxQS2hYMVJtaEROMWtEYlpmMVNUc2xGRTY3MExJQTJMYi12ZGhZOUkzelpJWmFDODV2SExoWENEcjh6d0lWVHlHLWRuNlh2WkF1cVFlbzh5MHZORjFLRW5vWEstWUhMVVlHUzVzLWFZQlNBcXRmc09MOGhGbnFaSWRhMmE2YXJULUQzWDlGbXEyc3RYWFlWQzZZODZKUXZHU0xTTFhadmxfYlB3SzVpa3JGNzA1UHF0QnlUVHo0WWt4VE1zelp3T05Tb1BXeGV6MmNDaU5HOWgxNjktRDZDMU5maWZQbmlaZVJGNUxZaDVsa0RMZ3pTZUVSbnBYZndlM01WMEpQcTltSW80Q1diejRfeFhQODBUUWMyYzNobHV2MFlyZ2JnVWs4azlCbXV4TUdNWnExYVNEVG9PWW80ZUN3dVpLbExJSHhWZEN1MVVCeE5hdTNjM0tmNw?oc=5</t>
         </is>
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>证券简称：中金公司</t>
+          <t>300658，终止重大资产重组 新浪财经</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>兴业证券股份有限公司关于本次交易相关主体不存在不得参与任何上市公司 重大 资产重组 情形的核查意见</t>
+          <t>the next phase of china’s beauty expansion - arc group</t>
         </is>
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>Google News - Global M&amp;A / arc group</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T10:58:37+08:00</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>全球</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>重大资产重组</t>
+          <t>cross-border acquisition Chinese company announced</t>
         </is>
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225313981.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMiYkFVX3lxTE81WEU3TnNfUzhKWmpyUU5BZlJKUmJZVHNuVmduejV4bGFVdm9ldXFsVnlrZnRIRmlNc1RHRERlalZPZDByanZ1LXREdTJFRDQzLUxDNmJmdFN3aFpITElXV1h3?oc=5</t>
         </is>
       </c>
       <c r="G118" s="5" t="inlineStr">
         <is>
-          <t>证券简称：中金公司</t>
+          <t>the next phase of china’s beauty expansion arc group</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>关于筹划 发行 股份 购买 资产 并募集配套资金事项的股票停牌进展公告</t>
+          <t>先导电科为何难卖？ - 新浪财经</t>
         </is>
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>财经媒体/专业资讯 - 中国并购 / 新浪财经</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T10:48:00+08:00</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
@@ -6411,34 +7716,34 @@
       </c>
       <c r="E119" s="5" t="inlineStr">
         <is>
-          <t>发行股份购买资产</t>
+          <t>每日经济新闻 并购重组 收购</t>
         </is>
       </c>
       <c r="F119" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225317328.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMidEFVX3lxTFBhLVlNWlFwUFR5c2hGVlZDNWJUc3ZObkVYX1U0cVl6R25TOHdfSzBYZFNnc1VUaHFUN3AtM2RBdV9yS1BaNGR6cUFNMVNDcjZPSVRabXdrY0pyeUh4M05COFJGRlZXYVBPaEFvZVlicHZ1cFlp?oc=5</t>
         </is>
       </c>
       <c r="G119" s="5" t="inlineStr">
         <is>
-          <t>证券简称：华洋赛车</t>
+          <t>先导电科为何难卖？ 新浪财经</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>关于筹划 发行 股份 购买 资产 并募集配套资金事项的进展公告</t>
+          <t>德国商业银行建议股东拒绝裕信银行收购邀约 - 新浪财经</t>
         </is>
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>中国新闻广域 - Google News RSS / 新浪财经</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T10:30:59+08:00</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
@@ -6448,34 +7753,34 @@
       </c>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>发行股份购买资产</t>
+          <t>中国 (并购 OR 收购 OR 合并 OR 股权转让 OR 交易完成)</t>
         </is>
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225312110.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMingJBVV95cUxQQzVvWFlDa3FROWpDajdSUE9sTjcxdW1Za1M2Y1N3UkoxdTJlVUliQkQtQ1NQa21IaVBtZWxkcnZQd1ZmWnQxZS1xZDhnZWtxcWhGT1RydkZvdEtqME8yNWdqRE1UZkxvbmQ2UXVXZ1RZSnBaR2xzQlZ0M084N3g1bkltRzdUejJpaVNzaURTR3B6ZnBkWl81R3k5dDJjb3ZYbm1rZm5DTzJZRy1tWG40U3hzVzhLZWdjY1N3WXhmb3JqMFFRN04tRm5MN3NNS2NDRmNMc1hZMFRKdnBtclA4dG11UWd0Y24yak1qeXYtV3BzTDdYNUxmd1Ywazd6VTdncm9iY0JfWUZIM0ZndWtMQmlvRVJhbklnS2VnX1Jn?oc=5</t>
         </is>
       </c>
       <c r="G120" s="5" t="inlineStr">
         <is>
-          <t>证券简称：洁美科技</t>
+          <t>德国商业银行建议股东拒绝裕信银行收购邀约 新浪财经</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>关于筹划发行股份 购买 资产 并募集配套资金事项的股票停牌进展公告</t>
+          <t>并购与扩产的“一停一启”：恩捷股份终止并购与40亿扩产背后的投资逻辑 - 新华报业网</t>
         </is>
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>财经媒体/专业资讯 - 中国并购 / 新华报业网</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T10:25:00+08:00</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
@@ -6485,34 +7790,34 @@
       </c>
       <c r="E121" s="5" t="inlineStr">
         <is>
-          <t>购买资产</t>
+          <t>界面新闻 并购 收购</t>
         </is>
       </c>
       <c r="F121" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225317328.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTFBPdk5mUll2SzI4TzZWaVJ5MnJwUlU4T1I0LWtxMWJqWGRKclVzMkk1UzZaTjVCM1lWU3dsTkhtQm9jRUxmSzlBbURGMWFDZHpvMTM2ODRURDJ2SUFuY2ZPT1hpQjBvYXk4VG1r?oc=5</t>
         </is>
       </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
-          <t>证券简称：华洋赛车</t>
+          <t>并购与扩产的“一停一启”：恩捷股份终止并购与40亿扩产背后的投资逻辑 新华报业网</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>中银国际证券股份有限公司关于信达证券股份有限公司在本次交易前十二个月内 购买 、出售 资产 的核查意见</t>
+          <t>科技创新呼唤耐心资本并购重组迈向深度整合 - 中国财富网</t>
         </is>
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>中国新闻广域 - Google News RSS / 中国财富网</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T10:22:00+08:00</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
@@ -6522,34 +7827,34 @@
       </c>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>购买资产</t>
+          <t>产业整合 并购 收购 中国</t>
         </is>
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225314601.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE9McG5JaTdDcVRJelZ6ZkdVMTJXaWtPaXJUNFBRSFRrRmEtcm1KaGRCX1lDQ3Z5ZnVpYWhXVXFvSmtJMTZ5bzNPa0t1QjdTcFpVVTZxWVBFVmFVREc0?oc=5</t>
         </is>
       </c>
       <c r="G122" s="5" t="inlineStr">
         <is>
-          <t>证券简称：信达证券</t>
+          <t>科技创新呼唤耐心资本并购重组迈向深度整合 中国财富网</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>信达证券董事会关于本次交易前12个月内 购买 、出售 资产 情况的说明</t>
+          <t>重大资产重组，终止 - 新浪财经</t>
         </is>
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>财经媒体/专业资讯 - 中国并购 / 新浪财经</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T10:15:00+08:00</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
@@ -6559,34 +7864,34 @@
       </c>
       <c r="E123" s="5" t="inlineStr">
         <is>
-          <t>购买资产</t>
+          <t>第一财经 并购 收购 重组</t>
         </is>
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225314590.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE1XNWRKcDQ0bjRMQWtsUkNza0ZrYjAyMmNNZEx5MFNnY3pZSEtsR3NNei1IaFJUVXlwQ0NZdWdnUVpsalVuZVlEbHE2VVYyNzZHeVpOMWV4TTZIZHNLUzI1bzFGakdKTGc0U09LbFhTUUt3enBQS1E?oc=5</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>证券简称：信达证券</t>
+          <t>重大资产重组，终止 新浪财经</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>东兴证券董事会关于在本次交易前12个月内 购买 、出售 资产 情况的说明</t>
+          <t>中国化工收购瑞士先正达 收购价创新纪录 - 朝鮮日報中文版</t>
         </is>
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>中国新闻广域 - Google News RSS / 朝鮮日報中文版</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T09:48:25+08:00</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
@@ -6596,71 +7901,71 @@
       </c>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t>购买资产</t>
+          <t>中国 (并购 OR 收购 OR 合并 OR 股权转让 OR 交易完成)</t>
         </is>
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225314257.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPNkotejV5WGt4MXhDUDRkWUZXRzVrc3M2SEZSZlNaQm9zOFpQWG1IclR0SEpmd0pfZG5uWGI2ZjIxX3ZoZ09HQk91VHNTVXM2LWhwVmxVZU9MYkkwakNLck16d0ZRSVlMYWtwcDU2ZmNBaFBFdGVEUjNwU2ZjRm94QV9CdmRqTDQ3b3RENnVHWXdmbmxBZDJzUg?oc=5</t>
         </is>
       </c>
       <c r="G124" s="5" t="inlineStr">
         <is>
-          <t>证券简称：东兴证券</t>
+          <t>中国化工收购瑞士先正达 收购价创新纪录 朝鮮日報中文版</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="5" t="inlineStr">
         <is>
-          <t>国投证券股份有限公司关于东兴证券股份有限公司在本次交易前12个月内 购买 、出售 资产 的核查意见</t>
+          <t>featuring, a global sns data analysis company, announced on the 19th that it has attracted 15.3 bill.. - 매일경제</t>
         </is>
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>Google News - Global M&amp;A / 매일경제</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T09:38:42+08:00</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>全球</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
         <is>
-          <t>购买资产</t>
+          <t>cross-border acquisition Chinese company announced</t>
         </is>
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225314242.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMiS0FVX3lxTE5MTTF4c1lHLW5pUzFfUUZzZVRGWTBZc0VhbW96RnUtZldrcUdNV2R4X2Rsa3ZWT1FCR3BnU2VqRm1SNDBtWDZQQzlPUQ?oc=5</t>
         </is>
       </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
-          <t>证券简称：东兴证券</t>
+          <t>featuring, a global sns data analysis company, announced on the 19th that it has attracted 15.3 bill.. 매일경제</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>兴业证券股份有限公司关于中国国际金融股份有限公司在本次交易前十二个月内 购买 、出售 资产 的核查意见</t>
+          <t>南方财经全媒体集团 - 南方财经</t>
         </is>
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>财经媒体/专业资讯 - 中国并购 / 南方财经</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T09:25:23+08:00</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
@@ -6670,34 +7975,34 @@
       </c>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>购买资产</t>
+          <t>21世纪经济报道 并购 收购 重组</t>
         </is>
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225314026.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTFBkcDdhZTNWX1E5SlMtb3ZrRlcxVkphQThaeTBOVHFXd1JHRlpaVlM0WS1OYWZYbmpndk9weUxxaGlNeUphVXlNSkxRLS1jc3ozSjAzMUdQVjBBSV9tU096cTBsRVdzQQ?oc=5</t>
         </is>
       </c>
       <c r="G126" s="5" t="inlineStr">
         <is>
-          <t>证券简称：中金公司</t>
+          <t>南方财经全媒体集团 南方财经</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="inlineStr">
         <is>
-          <t>中金公司董事会关于本次交易前12个月内 购买 、出售 资产 情况的说明</t>
+          <t>中芯国际406亿元全资收购中芯北方，创科创板最大股份购买资产案 - 虎嗅</t>
         </is>
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>中国新闻广域 - Google News RSS / 虎嗅</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T09:17:22+08:00</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
@@ -6707,34 +8012,34 @@
       </c>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>购买资产</t>
+          <t>产业整合 并购 收购 中国</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225313989.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOell5eVZkZkVOV1VTcnFOV2ZYRDZndGVSR0RFVnZxa3pyVjlRdW9iOVJ1dzZNWWdXQjltUWc3aTV3dmVScVZsQzZDN0ZuNjVxWWZrbVhKaUI5b1lJVlc5ZlE0ZVVtcmJOM3c4SXNKeTl0em5ldzEwaXh3X25SYXBBOVdXbWFleUFUTHA0?oc=5</t>
         </is>
       </c>
       <c r="G127" s="5" t="inlineStr">
         <is>
-          <t>证券简称：中金公司</t>
+          <t>中芯国际406亿元全资收购中芯北方，创科创板最大股份购买资产案 虎嗅</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>关于筹划发行股份 购买 资产 并募集配套资金事项的进展公告</t>
+          <t>300658，跨界并购重大重组终止！ - 新浪财经</t>
         </is>
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>财经媒体/专业资讯 - 中国并购 / 新浪财经</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T08:08:00+08:00</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
@@ -6744,34 +8049,34 @@
       </c>
       <c r="E128" s="5" t="inlineStr">
         <is>
-          <t>购买资产</t>
+          <t>21世纪经济报道 并购 收购 重组</t>
         </is>
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225312110.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE9hMjNlaXQtLVRoZXNIRDBIVE5QU0dfUGFuOEc0NFR3dTEwQmpFVFdpUk5iYllrc1B2OVBPYjAyNVR4Y0I0MnNUbXpOVldQUHpaSWJYLUN5Y3BpZjFwMlFyaWNYellTN3R4UjN1QVBqRFpXejdEQVE?oc=5</t>
         </is>
       </c>
       <c r="G128" s="5" t="inlineStr">
         <is>
-          <t>证券简称：洁美科技</t>
+          <t>300658，跨界并购重大重组终止！ 新浪财经</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="5" t="inlineStr">
         <is>
-          <t>中银国际证券股份有限公司关于信达证券股份有限公司在本次交易前十二个月内购买、 出售 资产 的核查意见</t>
+          <t>科技早报 | 腾讯以186亿元完成收购喜马拉雅；iphone 17 pro系列直降1000元引发抢购潮 - jiemian.com</t>
         </is>
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>财经媒体/专业资讯 - 中国并购 / jiemian.com</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T08:05:33+08:00</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
@@ -6781,34 +8086,34 @@
       </c>
       <c r="E129" s="5" t="inlineStr">
         <is>
-          <t>出售资产</t>
+          <t>界面新闻 并购 收购</t>
         </is>
       </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225314601.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMiWEFVX3lxTE45T21Rd3RLTVRic2c1dlJITVIyU0FwRVdCaDVZUzdhVTQ0ZWhnQlhuWUlnSzkwQ1pVTktWZGlEVWFwZGJCcUNkZWduVlF0ZlpvOUR1cjE5ejI?oc=5</t>
         </is>
       </c>
       <c r="G129" s="5" t="inlineStr">
         <is>
-          <t>证券简称：信达证券</t>
+          <t>科技早报 | 腾讯以186亿元完成收购喜马拉雅；iphone 17 pro系列直降1000元引发抢购潮 jiemian.com</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>信达证券董事会关于本次交易前12个月内购买、 出售 资产 情况的说明</t>
+          <t>美国电力航母诞生！nextera以668亿美元并购dominion - 新浪财经</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>财经媒体/专业资讯 - 中国并购 / 新浪财经</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T07:54:03+08:00</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
@@ -6818,34 +8123,34 @@
       </c>
       <c r="E130" s="5" t="inlineStr">
         <is>
-          <t>出售资产</t>
+          <t>界面新闻 并购 收购</t>
         </is>
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225314590.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE5ONzl2cmlZWUtFTHVrRHpOaXNycXNxOVBlMURZVDU3SjNOVGZsWDB6RWxMWXA2dkFBX21DS1QzYmxIX2JHNVdaQ2d6MnAwWW1mMVFhbFkwSzhLSVdOSXhLOW93c2Ixd3N6N1RhblhR?oc=5</t>
         </is>
       </c>
       <c r="G130" s="5" t="inlineStr">
         <is>
-          <t>证券简称：信达证券</t>
+          <t>美国电力航母诞生！nextera以668亿美元并购dominion 新浪财经</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="5" t="inlineStr">
         <is>
-          <t>东兴证券董事会关于在本次交易前12个月内购买、 出售 资产 情况的说明</t>
+          <t>中国富豪王健林收购fifa比赛转播权 - 朝鮮日報中文版</t>
         </is>
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>中国新闻广域 - Google News RSS / 朝鮮日報中文版</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T07:46:20+08:00</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
@@ -6855,34 +8160,34 @@
       </c>
       <c r="E131" s="5" t="inlineStr">
         <is>
-          <t>出售资产</t>
+          <t>中国 (并购 OR 收购 OR 合并 OR 股权转让 OR 交易完成)</t>
         </is>
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225314257.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNSzMteDJSS2FBemFxNEJfVGZPN2tIWktxM1FGY1NDRUdVbGZyRnpScWlqa1JkdWFzbG9sdHFjb0dCb0ZoSlFiQUh3YzlDLU84cjhVNl9GNEtLUHFDc3RRUlJYRmtoSE02eDNrXzVTTm9CamVtdlMwREZlbzBqcS1Da1I5bTU5LTlOa05JU0l2Q3czZw?oc=5</t>
         </is>
       </c>
       <c r="G131" s="5" t="inlineStr">
         <is>
-          <t>证券简称：东兴证券</t>
+          <t>中国富豪王健林收购fifa比赛转播权 朝鮮日報中文版</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>国投证券股份有限公司关于东兴证券股份有限公司在本次交易前12个月内购买、 出售 资产 的核查意见</t>
+          <t>中金公司“三合一”吸并草案出炉，合并后将跻身“百亿净利俱乐部” - 新浪财经</t>
         </is>
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>财经媒体/专业资讯 - 中国并购 / 新浪财经</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T07:43:34+08:00</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
@@ -6892,34 +8197,34 @@
       </c>
       <c r="E132" s="5" t="inlineStr">
         <is>
-          <t>出售资产</t>
+          <t>第一财经 并购 收购 重组</t>
         </is>
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225314242.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxPUTJvMWVfODFyemNGbDBwVF9PTWtOMGE2T0hCLTlQbDU4ZVI4NU1MZnhIUjM0QVh3a1h5WVFMTHlKVWpWd01CeE1qRmJrc1MzOVRZZExWVERLNGZtZ1hyYUpGc1J4WkpHcmgtWTJNVXl4V3pwdUVLcGYybjQ4UlhLSlR3dUR6TzAzS1JBUUNR?oc=5</t>
         </is>
       </c>
       <c r="G132" s="5" t="inlineStr">
         <is>
-          <t>证券简称：东兴证券</t>
+          <t>中金公司“三合一”吸并草案出炉，合并后将跻身“百亿净利俱乐部” 新浪财经</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="5" t="inlineStr">
         <is>
-          <t>兴业证券股份有限公司关于中国国际金融股份有限公司在本次交易前十二个月内购买、 出售 资产 的核查意见</t>
+          <t>1.5：1！提高置换标准 鼓励兼并重组 钢铁行业产能置换新规落地 - 财联社</t>
         </is>
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>中国新闻广域 - Google News RSS / 财联社</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T07:43:00+08:00</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
@@ -6929,219 +8234,219 @@
       </c>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>出售资产</t>
+          <t>产业整合 并购 收购 中国</t>
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225314026.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMiRkFVX3lxTE84MllCSFIxbU9tekQ0MmZKTDk2ZjdIQ3QxTkFzR0x2Y2l5d3VlMzMyeUV0RnRHTXhaZG8tUFA2bUhNMnM3TGc?oc=5</t>
         </is>
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>证券简称：中金公司</t>
+          <t>1.5：1！提高置换标准 鼓励兼并重组 钢铁行业产能置换新规落地 财联社</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>中金公司董事会关于本次交易前12个月内购买、 出售 资产 情况的说明</t>
+          <t>south carolina customers included in dominion, nextera merger proposal - wach.com</t>
         </is>
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>Google News - Global M&amp;A / wach.com</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T06:38:58+08:00</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>全球</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
         <is>
-          <t>出售资产</t>
+          <t>takeover offer acquisition announced</t>
         </is>
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225313989.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQVUp4TXJzeDFiUXJZZGRnN3Frem5LVGI1R1RLSUNwNEdXb2Ruc1k1dHZ0MGFYVEdQUkR5ZEhnWVd5aVNUbURxX0JYVVU0bGJWMEF2WnMyMFJ0STYzSGpIQS1hOU5OTFg2YlBnWk0xUXgxQ25kanRleEpoZk9NUlZ5Z1FOR3pvN0ZIT3Y2eTZBZUdJUy1wYWRZTTFma3ZlOHdGYU9Ua3d0c01nZ3pV?oc=5</t>
         </is>
       </c>
       <c r="G134" s="5" t="inlineStr">
         <is>
-          <t>证券简称：中金公司</t>
+          <t>south carolina customers included in dominion, nextera merger proposal wach.com</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t>北投科技关于控股股东对重大 资产 置换 置入 资产 2025年度应收账款承诺实现情况的公告</t>
+          <t>why you should care about 2 power companies merging. hint: affordability - npr</t>
         </is>
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>Google News - Global M&amp;A / npr</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T06:00:12+08:00</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>全球</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
         <is>
-          <t>资产置换</t>
+          <t>takeover offer acquisition announced</t>
         </is>
       </c>
       <c r="F135" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225315043.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQV2NOekpiWDItV2pLWERWY3RHY0ZremVibVdlNENvTURadmZ4cGlzU2VmcTRobDBxaG0xOUVkU0VrMXFaZ1NmT0Y1N2RWZzBNWUFGYnFIRUpsd3NZY2UtY0FNUG9WS0xmT0gxQ240NjFxQjVaRzhMUTlFdTkzaGR2Ty15SnlpYVZFeHJDOVJKeG45aGtEYmVEVmwtVGpEQQ?oc=5</t>
         </is>
       </c>
       <c r="G135" s="5" t="inlineStr">
         <is>
-          <t>证券简称：北投科技</t>
+          <t>why you should care about 2 power companies merging. hint: affordability npr</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>信达证券董事会关于本次交易符合《上市公司重大 资产重组 管理办法》第十一条规定的说明</t>
+          <t>swamped by data center demands, dominion energy just opted for a megamerger - the washington post</t>
         </is>
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>Google News - Global M&amp;A / the washington post</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T05:36:35+08:00</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>全球</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
         <is>
-          <t>资产重组</t>
+          <t>takeover offer acquisition announced</t>
         </is>
       </c>
       <c r="F136" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225314643.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOMVZHY1I4blV2ZjJMcTFqOXBvUU5ua2pjVnJOQ00yc3ZQQTZSOUE2RG5vd1pST1NZbVdOTm9YNWQ3aDhLaFRKMkQ3aWxwUDlYT1NxMW9wMDhNMVpKRG5oTzlwbWw4dGFXbnhITnc3M1prU1E1RzdMSTNZOVI1UDQwUlFtOHpPTXNxUjNQMlpPd1QyTkJHN0NKRHJuM0JMTFNYc0VJeHRLaXZnZVpEczJ5aUxGMmNucXh3SExRUXJndW5OaDJ6aFJKdGhjLWhvUQ?oc=5</t>
         </is>
       </c>
       <c r="G136" s="5" t="inlineStr">
         <is>
-          <t>证券简称：信达证券</t>
+          <t>swamped by data center demands, dominion energy just opted for a megamerger the washington post</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="5" t="inlineStr">
         <is>
-          <t>信达证券董事会关于本次交易符合《上市公司监管指引第9号——上市公司筹划和实施重大 资产重组 的监管要求》第四条规定的说明</t>
+          <t>what nextera and dominion’s giant utility merger means for your electric bill - marketwatch</t>
         </is>
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>Google News - Global M&amp;A / marketwatch</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T05:12:00+08:00</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>全球</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
         <is>
-          <t>资产重组</t>
+          <t>takeover offer acquisition announced</t>
         </is>
       </c>
       <c r="F137" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225314608.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxOQ29nc1prWUd1VFJTRGRlMC1ubGw2cTBiR0pmNEU4VS1JRGlnRDJVNmtPdk9zbjIwTkVXMS15OHdjU2dOWk1MNGdqQW15NnZGLWtvWHFLMTZVRFpDSnpERGJPN3hSckZGeG9meHdyQXZZZkx3cFZqOHhaWXZ2aHVtMUplQjNqOERkSFEtM0U0ZW1aQzFNSmdyR3EzSkoyYnBlbk9SMGFvUklKWXVzTkN6Mnd4eWN0RTJNdWZV?oc=5</t>
         </is>
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>证券简称：信达证券</t>
+          <t>what nextera and dominion’s giant utility merger means for your electric bill marketwatch</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>中银国际证券股份有限公司关于本次交易相关主体不存在不得参与任何上市公司重大 资产重组 情形的核查意见</t>
+          <t>your portfolio &amp; the nextera dominion merger - etf database</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>Google News - Global M&amp;A / etf database</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T05:07:50+08:00</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>全球</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
         <is>
-          <t>资产重组</t>
+          <t>takeover offer acquisition announced</t>
         </is>
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225314605.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxPRDFaaDRvX2VJUEpaYVpwTWp0dW1nWGtFNnUyV2NzRlJMVGVXOTk3NE40aFVyN1FEMlFrVE9VTjR6ZkdpclVFTGFTVFpvX29VRnNBWkQ5Y3FzS3c3RkZtem9INnZ2MFVDRGFrb2tIN2VfSzlyb2JJdmd0YW16QV81dEhKeW41dmZKUm16TFAtMThqOWF3?oc=5</t>
         </is>
       </c>
       <c r="G138" s="5" t="inlineStr">
         <is>
-          <t>证券简称：信达证券</t>
+          <t>your portfolio &amp; the nextera dominion merger etf database</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="5" t="inlineStr">
         <is>
-          <t>信达证券董事会关于本次交易构成《上市公司重大 资产重组 管理办法》第十二条规定的重大 资产重组 但不构成第十三条规定的重组上市情形的说明</t>
+          <t>特斯拉推进收购中国电动汽车企业比亚迪20%的股份 - 朝鮮日報中文版</t>
         </is>
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>中国新闻广域 - Google News RSS / 朝鮮日報中文版</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T05:07:03+08:00</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
@@ -7151,145 +8456,145 @@
       </c>
       <c r="E139" s="5" t="inlineStr">
         <is>
-          <t>资产重组</t>
+          <t>中国 (并购 OR 收购 OR 合并 OR 股权转让 OR 交易完成)</t>
         </is>
       </c>
       <c r="F139" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225314597.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQVG1BNmNkempjX3phTjVtcEU5TnRTaHVpdHJMNTJodkJBdVFDcFQzbUpFUk9jTVJnbmdLSnVlNFprREtRLTdodmpXUkFUa0xqekxOUWFyY0ptbDg5T1BwaF9NVjdBU1BsNjlJZG11azhmM0NNNW8tVlg0QVFJVU9jME1QWXhVQjlobkxZMW0tWkRhdw?oc=5</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
-          <t>证券简称：信达证券</t>
+          <t>特斯拉推进收购中国电动汽车企业比亚迪20%的股份 朝鮮日報中文版</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t>信达证券董事会关于本次交易相关主体不存在《上市公司监管指引第7号——上市公司重大 资产重组 相关股票异常交易监管》第十二条及《上海证券交易所上市公司自律监管指引第6号——重大 资产重组 》第三十条情形的说明</t>
+          <t>iron horse (irho) files s-4; amends merger agreement with electra (may 2026) - stock titan</t>
         </is>
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>Google News - Global M&amp;A / stock titan</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T04:32:44+08:00</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>全球</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
         <is>
-          <t>资产重组</t>
+          <t>M&amp;A acquisition merger deal announced last week</t>
         </is>
       </c>
       <c r="F140" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225314593.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxPMXJZNmd2UU5Vdl9QTmM0elI5VEt4RUp6aXZBRWJ3QlBZeDB3bDE4MF94UDNGUTlWMy1yQllTV2l4U2s3VlZ0OEhWTnNFV1pFaFJIMUhCcVZVcGxqZFQwcW5pOXFOVzk5dTlCaklOR1I5REZFeEZWa1dRUjlwT0ZYdEVHYS1tNXNXVGdkS09xdnVOLUxYVDdSM2RjY2V4UmtfNldyc19fQTdDbGJlaTlwYURlY1NYUHQyeVU0MTNZYmlSZzhpYk9CQ1pvSQ?oc=5</t>
         </is>
       </c>
       <c r="G140" s="5" t="inlineStr">
         <is>
-          <t>证券简称：信达证券</t>
+          <t>iron horse (irho) files s-4; amends merger agreement with electra (may 2026) stock titan</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="5" t="inlineStr">
         <is>
-          <t>信达证券股份有限公司关于披露重大 资产重组 报告书的一般风险提示公告</t>
+          <t>electra ai and iron horse (nasdaq: irho) advance $250m spac merger plan - stock titan</t>
         </is>
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>Google News - Global M&amp;A / stock titan</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T04:31:32+08:00</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>全球</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
         <is>
-          <t>资产重组</t>
+          <t>SPAC merger announced acquisition</t>
         </is>
       </c>
       <c r="F141" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225314586.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQUkFXWjVUUHhKeGdJbG1aaThKeWpNb0NnZE5CNjhvYnpET241TFpFUE05Qmp5Z3RHbnBiZmhPSEY0RFE3ZXZ1bmF6WUlUOEZ0V0xKZEFWV0UzWEpjXzZPdXNuM0UxT2d0Vjd0aFR2WjlNdDZWNE81VkZBbGtvNGctRzYzaVhpaVRUeFZsY3ZHdGVxZXQ4NjZXaHZTOHJsVFFpcGJ1bVgtNnBTV0NqTF9PWnVPOXY3dll4cUVj?oc=5</t>
         </is>
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>证券简称：信达证券</t>
+          <t>electra ai and iron horse (nasdaq: irho) advance $250m spac merger plan stock titan</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>东兴证券董事会关于本次交易相关主体不存在《上市公司监管指引第7号——上市公司重大 资产重组 相关股票异常交易监管》第十二条及《上海证券交易所上市公司自律监管指引第6号——重大 资产重组 》第三十条情形的说明</t>
+          <t>rb global (nyse: rba) closes bigiron deal to expand u.s. agriculture - stock titan</t>
         </is>
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>Google News - Global M&amp;A / stock titan</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T04:30:28+08:00</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>全球</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
         <is>
-          <t>资产重组</t>
+          <t>global merger acquisition announced company deal</t>
         </is>
       </c>
       <c r="F142" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225314256.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxOLXBvYkZJM1pRYUpJNm1JT1UxVlJtcnZObUtVbTN5NHpkZzVWZE9GMEF2ZFQ2WG51bTVVd1ZVZFNMaEJpZW1HM1JFMFJOSy00QUtHamdXdTBxNll6WTNoM3ladEdBcFF4VUpTcWxwNFBObXRnblgzX2lCN0NWWVdDSEVzY0Z3LW9BbGV5VDhXNHBUeXhNZ0x0UTg2d3U0Ym9SRWdv?oc=5</t>
         </is>
       </c>
       <c r="G142" s="5" t="inlineStr">
         <is>
-          <t>证券简称：东兴证券</t>
+          <t>rb global (nyse: rba) closes bigiron deal to expand u.s. agriculture stock titan</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="5" t="inlineStr">
         <is>
-          <t>国投证券股份有限公司关于本次交易相关主体不存在不得参与任何上市公司重大 资产重组 情形的核查意见</t>
+          <t>drake star：2026年第一季度管理服务提供商报告 - 新浪网</t>
         </is>
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>中国新闻广域 - Google News RSS / 新浪网</t>
         </is>
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T04:29:50+08:00</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
@@ -7299,219 +8604,219 @@
       </c>
       <c r="E143" s="5" t="inlineStr">
         <is>
-          <t>资产重组</t>
+          <t>产业整合 并购 收购 中国</t>
         </is>
       </c>
       <c r="F143" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225314234.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxObk0zR3FEVEhpY2d3N29rN1VOVC1lZzlCMlFPZUhCV2tPb25DUTltYXJ5eGlkc0czcHNsVW82QmdmelRMajJZbjdUT2FMLTNiemRJeFE3R0d5dVVud2VzZ3ozbmtIVGZHeUJCMHloQkFMa2JmTmZ2MFF1dmhfU0llVHozV2xmWjdXelg3TnFscWRHRlBMZm9pNUZIdG1zaUoxU2NFRU0yYmxnOUZQa0hDNkxINm9CYmZrY2hVcUVtdGVGMDNsM09GOGYxajlReUd4enFTMWlmcGlYbkR5OGlIel9YeTA0QmFrSmszVkhiQ0lFVG9nVnVTdGhGWERFUQ?oc=5</t>
         </is>
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
-          <t>证券简称：东兴证券</t>
+          <t>drake star：2026年第一季度管理服务提供商报告 新浪网</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="5" t="inlineStr">
         <is>
-          <t>东兴证券董事会关于本次交易符合《上市公司监管指引第9号——上市公司筹划和实施重大 资产重组 的监管要求》第四条规定的说明</t>
+          <t>nextera's $67 billion dominion takeover creates world's largest utility—just in time to win the ai data center power surge - fortune</t>
         </is>
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>Google News - Global M&amp;A / fortune</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T04:29:00+08:00</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>全球</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
         <is>
-          <t>资产重组</t>
+          <t>takeover offer acquisition announced</t>
         </is>
       </c>
       <c r="F144" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225314225.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxQTlBuZGtXdXpRbzE5Vm53LWI2X0JXMkphVnVCTklWejVZdDg4eGtmaEI0eXM5RWJIa3RhZ2JVLVFxZXdpVGJYN2hfRW5PUWJOcUdrd05LQkNZVUoxa2xiS0d5M1p2VndaSVJvSmZyWjY5aG5VcDY0dnFnWVpCbXhWT3hVSzJLcFozQTQ0ajFRcUxPbU9VejdTb0dvNEpRRWlfRW5fNVRB?oc=5</t>
         </is>
       </c>
       <c r="G144" s="5" t="inlineStr">
         <is>
-          <t>证券简称：东兴证券</t>
+          <t>nextera's $67 billion dominion takeover creates world's largest utility—just in time to win the ai data center power surge fortune</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>东兴证券董事会关于本次交易构成《上市公司重大 资产重组 管理办法》第十二条规定的重大 资产重组 但不构成第十三条规定的重组上市情形的说明</t>
+          <t>deal watch: kirkland, mcguirewoods guide $67b energy deal - law.com</t>
         </is>
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>Google News - Global M&amp;A / law.com</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T03:51:00+08:00</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>全球</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
         <is>
-          <t>资产重组</t>
+          <t>M&amp;A acquisition merger deal announced last week</t>
         </is>
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225314222.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxNOUU4b05mLWtUMGtKUWYyRGVnMktSMnE1RXVJeUhHX2FTYTBnQlQ4SEJFYXlSZ2YzalVFLTVSc0E3NFVaSjNpcWlwREF3dHpBZHU4enc5YWpvak9DbEs1WTZPdGc2TmowZGdLaEZhNTRvaTRwMzBDQmNwX3RVZmIyNThrR2RDdnA0WlJDVEZheTI1M0EwUWcydkpXeXNEQ2xiel9n?oc=5</t>
         </is>
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>证券简称：东兴证券</t>
+          <t>deal watch: kirkland, mcguirewoods guide $67b energy deal law.com</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="5" t="inlineStr">
         <is>
-          <t>东兴证券董事会关于本次交易符合《上市公司重大 资产重组 管理办法》第十一条规定的说明</t>
+          <t>nigerian oil firms hunt growth beyond home market - marketing edge</t>
         </is>
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>Google News - Global M&amp;A / marketing edge</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T03:41:21+08:00</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>全球</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
         <is>
-          <t>资产重组</t>
+          <t>cross-border acquisition Chinese company announced</t>
         </is>
       </c>
       <c r="F146" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225314214.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxQeE82azU3c1pKQWl2Q1BJYlBGdmhSanI4bVdTR1h6dDY4bDgxNk5ZRzRWNjZJdm5UYTNPNE5URnVoMFZYaWk2TUNUdGhpb2pDeFRVQUFuNUZuY0FobTZwdzhIZ3NEaWpEOVBLOUNmVTR6cWFXa1VCckNFMmtzRDN6blRjYUNnUQ?oc=5</t>
         </is>
       </c>
       <c r="G146" s="5" t="inlineStr">
         <is>
-          <t>证券简称：东兴证券</t>
+          <t>nigerian oil firms hunt growth beyond home market marketing edge</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="5" t="inlineStr">
         <is>
-          <t>东兴证券股份有限公司关于披露重大 资产重组 报告书的一般风险提示公告</t>
+          <t>merger - dominion energy</t>
         </is>
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>Google News - Global M&amp;A / dominion energy</t>
         </is>
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T03:38:02+08:00</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>全球</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
         <is>
-          <t>资产重组</t>
+          <t>takeover offer acquisition announced</t>
         </is>
       </c>
       <c r="F147" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225314207.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE40bFFBanVER3Q0WWw0N3ZLZHhQWW1TTlluYXJDb1NuUVl6c3BkUkZfNXpPbUxuZ0F0cjdkZUNESzhOMmRabG1mZ3VLbFYtZTRHNEVZckFudU1taUU?oc=5</t>
         </is>
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>证券简称：东兴证券</t>
+          <t>merger dominion energy</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="5" t="inlineStr">
         <is>
-          <t>中金公司董事会关于本次交易构成《上市公司重大 资产重组 管理办法》第十二条规定的重大 资产重组 但不构成第十三条规定的重组上市情形的说明</t>
+          <t>brodsky &amp; smith investigates fiduciary duty bre... | pluang – crypto, stocks, gold &amp; funds - pluang</t>
         </is>
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>Google News - Global M&amp;A / pluang</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T03:32:46+08:00</t>
         </is>
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>全球</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
         <is>
-          <t>资产重组</t>
+          <t>global merger acquisition announced company deal</t>
         </is>
       </c>
       <c r="F148" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225314014.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOS2J1elcxRWZfRHJ4V2JSLVAwR1drUG1qZnRLb2RuNl9jaTlHenlzYjdrNmdOTkktY2JsV3Q4Vl83elhLQ3dzTk1Ta0VuYU5NbC10UlVwRFdnR3JzbnZmQmJhdGVzX0RBX0ZTbE5aejVhS0I0TEtnX3hxS1RzQm10eWtoODhWU0l3XzN2bll1Qk56YkFuc1ozYVlBMVdMRU9oQmFtc2xtbl8?oc=5</t>
         </is>
       </c>
       <c r="G148" s="5" t="inlineStr">
         <is>
-          <t>证券简称：中金公司</t>
+          <t>brodsky &amp; smith investigates fiduciary duty bre... | pluang – crypto, stocks, gold &amp; funds pluang</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="5" t="inlineStr">
         <is>
-          <t>中金公司董事会关于本次交易符合《上市公司监管指引第9号——上市公司筹划和实施重大 资产重组 的监管要求》第四条规定的说明</t>
+          <t>中国人企业收购美国芯片企业…特朗普下令：180天内出售资产 - 朝鮮日報中文版</t>
         </is>
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>中国新闻广域 - Google News RSS / 朝鮮日報中文版</t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T03:20:42+08:00</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
@@ -7521,108 +8826,108 @@
       </c>
       <c r="E149" s="5" t="inlineStr">
         <is>
-          <t>资产重组</t>
+          <t>中国 (并购 OR 收购 OR 合并 OR 股权转让 OR 交易完成)</t>
         </is>
       </c>
       <c r="F149" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225314009.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxOVjdXdUdqLWFwTDJzOG81QW5IZ2lVQUhaMDNHM09TeTFmQ3ZGY0ZEQ0xWVmI0NGJXb19BNjNPSUx2aUJFRVVIeVhLeDZhY05Rb2JYeTV3dmVNbkR6akdvdnB1RmlScVl0Mk4teFBNU09pbmxuSW9zNlBMQWMzWXc1TjRpX0ZEQ0ZpeG93?oc=5</t>
         </is>
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
-          <t>证券简称：中金公司</t>
+          <t>中国人企业收购美国芯片企业…特朗普下令：180天内出售资产 朝鮮日報中文版</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="5" t="inlineStr">
         <is>
-          <t>中金公司关于披露重大 资产重组 报告书的一般风险提示公告</t>
+          <t>nextera energy, dominion energy announce all-stock merger to create world's largest regulated utility - corridor business journal</t>
         </is>
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>Google News - Global M&amp;A / corridor business journal</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T03:14:31+08:00</t>
         </is>
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>全球</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
         <is>
-          <t>资产重组</t>
+          <t>takeover offer acquisition announced</t>
         </is>
       </c>
       <c r="F150" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225313999.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxNdzA2c3FES2diZFZXNllBWGxBMGc4dnh6QTFaNnFuRVlySklsaWJ5YVRFRzBUQjBPdXVzWFRiWmd6UGx2YzRPUk81eWw0QmIzMnhyYVdoV1NPMmNIZDNTdEo5SHp6djlXVVhDRy1OSlBRQUVXclNZR25HdE5Yb0lnQ3NVN0F6WURFbnhieUxIOU5JSUlyTGY2YlRCVVY5X0xWbGY0WG1qWHpBNUhMU2dPbjZaTWxOUjZ3SGxRYlhuLTFvVU5KUnlrLQ?oc=5</t>
         </is>
       </c>
       <c r="G150" s="5" t="inlineStr">
         <is>
-          <t>证券简称：中金公司</t>
+          <t>nextera energy, dominion energy announce all-stock merger to create world's largest regulated utility corridor business journal</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="5" t="inlineStr">
         <is>
-          <t>中金公司董事会关于本次交易符合《上市公司重大 资产重组 管理办法》第十一条、第四十三条和第四十四条规定的说明</t>
+          <t>starry sea acquisition ends proposed merger with forever young international - investing.com</t>
         </is>
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>Google News - Global M&amp;A / investing.com</t>
         </is>
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T03:02:00+08:00</t>
         </is>
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>全球</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
         <is>
-          <t>资产重组</t>
+          <t>global merger acquisition announced company deal</t>
         </is>
       </c>
       <c r="F151" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225313994.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxPUV9NSzY1NFE4aFV6LTdYNWE0bzBrOUZnQVhCN1pIb0MtU3JkdnVJbmhxQlRRZWtRUnpZNm0ySDV4Si1NNzRLeERVSFBLRnpEcWNQUUlfNVVXMUF1S3djVkx6YlVIOGRNeDFUbHZ6Q3phNUNQZ2lUMmFxUVBTamZyUjBIb2QxWlhGZXAtTXh2SUFna2laSEY5M3p2WTdoTU8yZGUyeGVLU1B0RmttS0NwUVJRbDNTMC13UWtuNTlNZGQ5SkVyN2lpX1pIVkFHU253UTlkTGg2cw?oc=5</t>
         </is>
       </c>
       <c r="G151" s="5" t="inlineStr">
         <is>
-          <t>证券简称：中金公司</t>
+          <t>starry sea acquisition ends proposed merger with forever young international investing.com</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="5" t="inlineStr">
         <is>
-          <t>中金公司董事会关于本次交易相关主体不存在《上市公司监管指引第7号——上市公司重大 资产重组 相关股票异常交易监管》第十二条及《上海证券交易所上市公司自律监管指引第6号——重大 资产重组 》第三十条情形的说明</t>
+          <t>关键条款未谈妥 延江股份终止收购集成电路资产 - 东方财富</t>
         </is>
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>财经媒体/专业资讯 - 中国并购 / 东方财富</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T02:49:55+08:00</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
@@ -7632,34 +8937,34 @@
       </c>
       <c r="E152" s="5" t="inlineStr">
         <is>
-          <t>资产重组</t>
+          <t>东方财富 并购重组 收购</t>
         </is>
       </c>
       <c r="F152" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225313988.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTFBzZC00dzY0alVZOTJ4bVF0cEZhOU5IeHFHSml1dmVxeENWQl9LYWhiSW5nT2NvRnVOb19xTGdsMFVpZ29ib3VBMzhCU0FsT0h3VE5mUG5KaDF6bzJaeWFFOQ?oc=5</t>
         </is>
       </c>
       <c r="G152" s="5" t="inlineStr">
         <is>
-          <t>证券简称：中金公司</t>
+          <t>关键条款未谈妥 延江股份终止收购集成电路资产 东方财富</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="5" t="inlineStr">
         <is>
-          <t>兴业证券股份有限公司关于本次交易相关主体不存在不得参与任何上市公司重大 资产重组 情形的核查意见</t>
+          <t>科技创新呼唤耐心资本 并购重组迈向深度整合 - 上海证券报电子版</t>
         </is>
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>财经媒体/专业资讯 - 中国并购 / 上海证券报电子版</t>
         </is>
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T02:36:21+08:00</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
@@ -7669,34 +8974,34 @@
       </c>
       <c r="E153" s="5" t="inlineStr">
         <is>
-          <t>资产重组</t>
+          <t>上海证券报 并购重组 资产重组 收购</t>
         </is>
       </c>
       <c r="F153" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225313981.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE9BV1hxdUprclRfU3BvdVRTTk9SeUcyeTFKVWJuR0lKd2x5TDAwRnJOeXdpUXgydW5KS1JTcjR2QVVKenJXbW5ydXVTNWFSU1BnS2ZTb0owVmRpTFhSeGdhVk92bDlmOFZfV1lLLXdn?oc=5</t>
         </is>
       </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
-          <t>证券简称：中金公司</t>
+          <t>科技创新呼唤耐心资本 并购重组迈向深度整合 上海证券报电子版</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="5" t="inlineStr">
         <is>
-          <t>中银国际证券股份有限公司关于中国国际金融股份有限公司换股 吸收 合并 东兴证券股份有限公司、信达证券股份有限公司之独立财务顾问报告</t>
+          <t>中国国际金融股份有限公司换股吸收合并东兴证券股份有限公司、信达证券股份有限公司报告书（草案）摘要 - 上海证券报电子版</t>
         </is>
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>中国新闻广域 - Google News RSS / 上海证券报电子版</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T02:22:13+08:00</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr">
@@ -7706,34 +9011,34 @@
       </c>
       <c r="E154" s="5" t="inlineStr">
         <is>
-          <t>吸收合并</t>
+          <t>中国 (并购 OR 收购 OR 合并 OR 股权转让 OR 交易完成)</t>
         </is>
       </c>
       <c r="F154" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225314642.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE1OdkhQT2ZmUmtJdk9uQnJXZXlKZnExclZQbjlMZDRsM1NtU25ZU0dfYWxOQmFEaS10NnUwWkQ3NXBiY21JRFlIRE8yX3Vmc2lueEs1VGx0SzRQUU81M3VXeUYzUkJGQzVPSG4zUHZR?oc=5</t>
         </is>
       </c>
       <c r="G154" s="5" t="inlineStr">
         <is>
-          <t>证券简称：信达证券</t>
+          <t>中国国际金融股份有限公司换股吸收合并东兴证券股份有限公司、信达证券股份有限公司报告书（草案）摘要 上海证券报电子版</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="5" t="inlineStr">
         <is>
-          <t>北京市金杜律师事务所关于中国国际金融股份有限公司换股 吸收 合并 信达证券股份有限公司的法律意见书</t>
+          <t>万亿中金将至，“三合一”换股价敲定，多项重要排名进阶 - 财联社</t>
         </is>
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>财经媒体/专业资讯 - 中国并购 / 财联社</t>
         </is>
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T01:22:51+08:00</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr">
@@ -7743,182 +9048,182 @@
       </c>
       <c r="E155" s="5" t="inlineStr">
         <is>
-          <t>吸收合并</t>
+          <t>财联社 并购重组 收购</t>
         </is>
       </c>
       <c r="F155" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225314611.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMiRkFVX3lxTE9ocEhVaXlabW5RTF9GWGVFbVp5STdDcklwU2NUQ1B3bVY1Z1hHTlJOa3dzNHBWZENJNmtZTm5iNGxvTDlTUFE?oc=5</t>
         </is>
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
-          <t>证券简称：信达证券</t>
+          <t>万亿中金将至，“三合一”换股价敲定，多项重要排名进阶 财联社</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="5" t="inlineStr">
         <is>
-          <t>中银国际证券股份有限公司关于中国国际金融股份有限公司换股 吸收 合并 东兴证券股份有限公司、信达证券股份有限公司之估值报告</t>
+          <t>neurocrine biosciences: $2.9 billion soleno therapeutics acquisition expands rare disease portfolio - pulse 2.0</t>
         </is>
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>Google News - Global M&amp;A / pulse 2.0</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T01:14:29+08:00</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>全球</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
         <is>
-          <t>吸收合并</t>
+          <t>takeover offer acquisition announced</t>
         </is>
       </c>
       <c r="F156" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225314606.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNNl9HQkJxcDZCN3lTLWVnZVpaWUFmM2MyUWtJaFZyNFpNa1RZcVlRWnBNM0w5VWpUM0pzMHFDT2pvNHM0Z0VkWkJuV3ZhMHZrZlY0bmtyTXdUYkszVjFINzZ6RXAwOE1CYjZ2czFLOVVJLWVac3FyQ1pIR0hvWldNUExEYVJ5NHFjSmg0VXh2RjRwTHluVFRUNllWQUVIalJKYWhmRmwxV0dRRFFUQjBoTVVYSy1xc2pG0gG-AUFVX3lxTE55V3VTck9tMUZFVUctSEVKVWlJUUtOUF9ycHdiVU1icDdDVzNGOWlGT3JzbzNPdU5yTGlRWDVwZGkzRktiUDFDcm0xcUo2YUNFNkF5ejRlejdkT3QwVVVTWHBVdVlJM1dJUGRtRUl3dzVaenduMDM0dVpSWTY3Q1RyOXNmRG8zdWxBTzNUU1I5R05vS2pCaHRjWUYwcEExOFZNalJaREUzVHpPckY4aS1JeWZjenJlYUJyRFduMVE?oc=5</t>
         </is>
       </c>
       <c r="G156" s="5" t="inlineStr">
         <is>
-          <t>证券简称：信达证券</t>
+          <t>neurocrine biosciences: $2.9 billion soleno therapeutics acquisition expands rare disease portfolio pulse 2.0</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="5" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司换股 吸收 合并 东兴证券股份有限公司、信达证券股份有限公司报告书（草案）与预案差异情况对比表</t>
+          <t>dominion energy stock surges on a deal with nextera to make the world's biggest utility - business insider</t>
         </is>
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>Google News - Global M&amp;A / business insider</t>
         </is>
       </c>
       <c r="C157" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T00:49:00+08:00</t>
         </is>
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>全球</t>
         </is>
       </c>
       <c r="E157" s="5" t="inlineStr">
         <is>
-          <t>吸收合并</t>
+          <t>takeover offer acquisition announced</t>
         </is>
       </c>
       <c r="F157" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225314596.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQSjRxTWhSYTdNR3BNYVJuNUdWSmNzNVFvMUE4MkZsXzBabnRoN290LXkySlVVWTcyUHVUUnZDbW1zWldFakhQWWg1WWJBZ0tydExlaXZJSmN2M1d2bVlhRlk4VEVtbzl3clp4bS1JWGVXejMydlRmTEhyMDJiRGVoaWhUSjk1TnNNOEdRZFZicnJOZm5NWGIwRXZXZWpLZmlkTTJMbGpUTHI5Y2c?oc=5</t>
         </is>
       </c>
       <c r="G157" s="5" t="inlineStr">
         <is>
-          <t>证券简称：信达证券</t>
+          <t>dominion energy stock surges on a deal with nextera to make the world's biggest utility business insider</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司换股 吸收 合并 东兴证券股份有限公司、信达证券股份有限公司报告书（草案）</t>
+          <t>nextera to buy dominion in $67bn deal creating us utility giant - the guardian</t>
         </is>
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>Google News - Global M&amp;A / the guardian</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T00:31:00+08:00</t>
         </is>
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>全球</t>
         </is>
       </c>
       <c r="E158" s="5" t="inlineStr">
         <is>
-          <t>吸收合并</t>
+          <t>global merger acquisition announced company deal</t>
         </is>
       </c>
       <c r="F158" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225314592.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNZkJfaDgwZ1I4dU1NZDgwbGk5Zk01Xzh6SWRDQnMxQUdlZF9ZdUZ4Qkk4LThodmRnSkw0aHMwQ1B0YW90LUM1eTl3Rzk3dnpfSXZIRUZ0aUxEVlZfRGhXTlg1ZGFBRUZyWnlhQzVjdzdPRUdSUTBEVG5KSjJPb2JjeWhDdWtHUWFRMmc?oc=5</t>
         </is>
       </c>
       <c r="G158" s="5" t="inlineStr">
         <is>
-          <t>证券简称：信达证券</t>
+          <t>nextera to buy dominion in $67bn deal creating us utility giant the guardian</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="5" t="inlineStr">
         <is>
-          <t>中银国际证券股份有限公司关于中国国际金融股份有限公司换股 吸收 合并 东兴证券股份有限公司、信达证券股份有限公司产业政策和交易类型之独立财务顾问核查意见</t>
+          <t>dominion energy stock soars on $67 billion deal to be acquired by nextera - investopedia</t>
         </is>
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>Google News - Global M&amp;A / investopedia</t>
         </is>
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T00:25:20+08:00</t>
         </is>
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>全球</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
         <is>
-          <t>吸收合并</t>
+          <t>M&amp;A acquisition merger deal announced last week</t>
         </is>
       </c>
       <c r="F159" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225314591.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxPVG1rdWdjam0yMDk3Slk4azFPVWVORGw0TzZJd3p6RE5hM0hCZ3hDUTlvcFNTNHlwZzA0ZVM0bDV1WEl6d251amN0QXFUZlJ4dldYbzYzWDVUNm1KZnJBQmJVZkF1ZWtuSHpGYUtNT3NtQ1VBSzBzMjdVcC1rMHBoQnQ4OURnWEFZdy1PaWtuSThucDUxMFRVTXZuZVZ1MkxiNXdoUXBDZlNGZDlqZnBPTEpYVGpzdmVUbWpV?oc=5</t>
         </is>
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>证券简称：信达证券</t>
+          <t>dominion energy stock soars on $67 billion deal to be acquired by nextera investopedia</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="5" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司换股 吸收 合并 东兴证券股份有限公司、信达证券股份有限公司报告书（草案）摘要</t>
+          <t>最新官宣！中金公司并购东兴、信达证券 交易价格定了 - 东方财富</t>
         </is>
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>财经媒体/专业资讯 - 中国并购 / 东方财富</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T00:17:02+08:00</t>
         </is>
       </c>
       <c r="D160" s="5" t="inlineStr">
@@ -7928,54 +9233,54 @@
       </c>
       <c r="E160" s="5" t="inlineStr">
         <is>
-          <t>吸收合并</t>
+          <t>东方财富 并购重组 收购</t>
         </is>
       </c>
       <c r="F160" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225314587.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMiYEFVX3lxTE9hOS1CU21IeGoyRDFQd0JINjQ5YmZCWFBWbHpnZjRyNFRHb0xsczFTV2R1QlBGbmZ6X3B0U1ZMRWJXMncwMERVbjh2SWdyXzdSdlNwdDZpck5renVaeXhVQg?oc=5</t>
         </is>
       </c>
       <c r="G160" s="5" t="inlineStr">
         <is>
-          <t>证券简称：信达证券</t>
+          <t>最新官宣！中金公司并购东兴、信达证券 交易价格定了 东方财富</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="5" t="inlineStr">
         <is>
-          <t>国投证券股份有限公司关于中国国际金融股份有限公司换股 吸收 合并 东兴证券股份有限公司、信达证券股份有限公司之独立财务顾问报告</t>
+          <t>dominion, nextera announce merger plan - cardinal news</t>
         </is>
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>巨潮资讯网 - 全市场公告入口</t>
+          <t>Google News - Global M&amp;A / cardinal news</t>
         </is>
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>2026-05-19T00:00:00+08:00</t>
+          <t>2026-05-19T00:15:49+08:00</t>
         </is>
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>中国</t>
+          <t>全球</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
         <is>
-          <t>吸收合并</t>
+          <t>takeover offer acquisition announced</t>
         </is>
       </c>
       <c r="F161" s="5" t="inlineStr">
         <is>
-          <t>https://static.cninfo.com.cn/finalpage/2026-05-19/1225314258.PDF</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxOZUlEU1hVVWV5QkVvSV83UmJVdG5wWUJEelhwNVE4VWZ5dXFLTF9KYzVBWlBfQXRBOUNTNTJfT3A1alU4WDhLVzFsWTdWcnhfX3lnYzJfaHNzRVVfZ0dPemlHdDQ4X1dlMjJueGpJVmZ4dktOU1JveC1SNkxBbUVJNQ?oc=5</t>
         </is>
       </c>
       <c r="G161" s="5" t="inlineStr">
         <is>
-          <t>证券简称：东兴证券</t>
+          <t>dominion, nextera announce merger plan cardinal news</t>
         </is>
       </c>
     </row>
